--- a/manuscript_v6/Online_Resource_2.xlsx
+++ b/manuscript_v6/Online_Resource_2.xlsx
@@ -540,7 +540,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Kept images: the clinical sets exclude 8 FUSeg test images that duplicate FUSeg training images and 47 control images that are crops of FUSeg photographs (Online Resource 1, Table S9). FUSeg at 256 px uses the FUSeg exclusions. Synthetic sets have no exclusions.</t>
+          <t>Kept images: the clinical sets exclude 8 FUSeg test images that duplicate FUSeg training images and 73 control images that are crops of FUSeg photographs (Online Resource 1, Table S9). FUSeg at 256 px uses the FUSeg exclusions. Synthetic sets have no exclusions.</t>
         </is>
       </c>
     </row>
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="E5" s="7" t="n">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F5" s="7" t="n">
         <v>118</v>
@@ -1039,10 +1039,10 @@
         </is>
       </c>
       <c r="E13" s="7" t="n">
-        <v>103</v>
+        <v>77</v>
       </c>
       <c r="F13" s="7" t="n">
-        <v>89</v>
+        <v>70</v>
       </c>
     </row>
     <row r="14">
@@ -1945,7 +1945,7 @@
         <v>0.07682153032087875</v>
       </c>
       <c r="I2" s="8" t="n">
-        <v>0.2600647709664428</v>
+        <v>0.2588008144541861</v>
       </c>
       <c r="J2" s="8" t="n">
         <v>0.09497325697011014</v>
@@ -1969,7 +1969,7 @@
         <v>0.1535290750468949</v>
       </c>
       <c r="Q2" s="8" t="n">
-        <v>0.2220398839261665</v>
+        <v>0.2222005938138165</v>
       </c>
       <c r="R2" s="8" t="n">
         <v>0.0674316222584832</v>
@@ -2070,7 +2070,7 @@
         <v>0.06592578430367686</v>
       </c>
       <c r="I3" s="8" t="n">
-        <v>0.2321349580353582</v>
+        <v>0.2303064343500833</v>
       </c>
       <c r="J3" s="8" t="n">
         <v>0.128601491471499</v>
@@ -2094,7 +2094,7 @@
         <v>0.201080030054395</v>
       </c>
       <c r="Q3" s="8" t="n">
-        <v>0.1871103033695235</v>
+        <v>0.1821785981853472</v>
       </c>
       <c r="R3" s="8" t="n">
         <v>0.05308719755132929</v>
@@ -2195,7 +2195,7 @@
         <v>0.02914883137340489</v>
       </c>
       <c r="I4" s="8" t="n">
-        <v>0.2689112480970367</v>
+        <v>0.269335778761376</v>
       </c>
       <c r="J4" s="8" t="n">
         <v>0.1895072505135003</v>
@@ -2219,7 +2219,7 @@
         <v>0.130807458497252</v>
       </c>
       <c r="Q4" s="8" t="n">
-        <v>0.2347911238062955</v>
+        <v>0.2492779766460385</v>
       </c>
       <c r="R4" s="8" t="n">
         <v>0.03005587760387811</v>
@@ -2320,7 +2320,7 @@
         <v>0.02902288130607475</v>
       </c>
       <c r="I5" s="8" t="n">
-        <v>0.2812384413477074</v>
+        <v>0.280388489144777</v>
       </c>
       <c r="J5" s="8" t="n">
         <v>0.3812952976287026</v>
@@ -2344,7 +2344,7 @@
         <v>0.1204483306228492</v>
       </c>
       <c r="Q5" s="8" t="n">
-        <v>0.2409263525237283</v>
+        <v>0.2539749700421903</v>
       </c>
       <c r="R5" s="8" t="n">
         <v>0.03098081805381342</v>
@@ -2445,7 +2445,7 @@
         <v>0.0407448152772415</v>
       </c>
       <c r="I6" s="8" t="n">
-        <v>0.2934160825962978</v>
+        <v>0.2930134460216746</v>
       </c>
       <c r="J6" s="8" t="n">
         <v>0.2960321308292411</v>
@@ -2469,7 +2469,7 @@
         <v>0.1204483306228492</v>
       </c>
       <c r="Q6" s="8" t="n">
-        <v>0.2587431804957083</v>
+        <v>0.2739027279750244</v>
       </c>
       <c r="R6" s="8" t="n">
         <v>0.04029225860863984</v>
@@ -2570,7 +2570,7 @@
         <v>0.07153082149419596</v>
       </c>
       <c r="I7" s="8" t="n">
-        <v>0.3184959519147892</v>
+        <v>0.316772852352072</v>
       </c>
       <c r="J7" s="8" t="n">
         <v>0.1397935372756789</v>
@@ -2594,7 +2594,7 @@
         <v>0</v>
       </c>
       <c r="Q7" s="8" t="n">
-        <v>0.2628443941783342</v>
+        <v>0.2718412671702208</v>
       </c>
       <c r="R7" s="8" t="n">
         <v>0.07219640047248964</v>
@@ -2695,7 +2695,7 @@
         <v>0.1239275578989933</v>
       </c>
       <c r="I8" s="8" t="n">
-        <v>0.2429731660543403</v>
+        <v>0.2354800250108081</v>
       </c>
       <c r="J8" s="8" t="n">
         <v>0.2941500108756854</v>
@@ -2719,7 +2719,7 @@
         <v>0.1902868104613332</v>
       </c>
       <c r="Q8" s="8" t="n">
-        <v>0.1512255563120689</v>
+        <v>0.1147492243545643</v>
       </c>
       <c r="R8" s="8" t="n">
         <v>0.1235325540436604</v>
@@ -2820,7 +2820,7 @@
         <v>0.003158468947285306</v>
       </c>
       <c r="I9" s="8" t="n">
-        <v>0.2884547689275805</v>
+        <v>0.2898128442028527</v>
       </c>
       <c r="J9" s="8" t="n">
         <v>0.08029245323897029</v>
@@ -2844,7 +2844,7 @@
         <v>0.0629266652059481</v>
       </c>
       <c r="Q9" s="8" t="n">
-        <v>0.255358530189251</v>
+        <v>0.2747523443045181</v>
       </c>
       <c r="R9" s="8" t="n">
         <v>0.0007649724376343082</v>
@@ -2945,7 +2945,7 @@
         <v>0.05346377559558578</v>
       </c>
       <c r="I10" s="8" t="n">
-        <v>0.314597640868597</v>
+        <v>0.3135032064498777</v>
       </c>
       <c r="J10" s="8" t="n">
         <v>0.07653680132354547</v>
@@ -2969,7 +2969,7 @@
         <v>0</v>
       </c>
       <c r="Q10" s="8" t="n">
-        <v>0.2663751829828979</v>
+        <v>0.2802228500017804</v>
       </c>
       <c r="R10" s="8" t="n">
         <v>0.05324162692394873</v>
@@ -3070,7 +3070,7 @@
         <v>0.03126728337027847</v>
       </c>
       <c r="I11" s="8" t="n">
-        <v>0.2878513548961699</v>
+        <v>0.2872156406134461</v>
       </c>
       <c r="J11" s="8" t="n">
         <v>0.3238613215065393</v>
@@ -3094,7 +3094,7 @@
         <v>0.1692217759656329</v>
       </c>
       <c r="Q11" s="8" t="n">
-        <v>0.2445846179258273</v>
+        <v>0.2581957197433875</v>
       </c>
       <c r="R11" s="8" t="n">
         <v>0.03122830743934095</v>
@@ -3195,7 +3195,7 @@
         <v>0.02922976277257348</v>
       </c>
       <c r="I12" s="8" t="n">
-        <v>0.2922448527288981</v>
+        <v>0.2920887689037795</v>
       </c>
       <c r="J12" s="8" t="n">
         <v>0.306540588078779</v>
@@ -3219,7 +3219,7 @@
         <v>0.182926248445727</v>
       </c>
       <c r="Q12" s="8" t="n">
-        <v>0.2543400790633614</v>
+        <v>0.2709726948017909</v>
       </c>
       <c r="R12" s="8" t="n">
         <v>0.02948611318972862</v>
@@ -3320,7 +3320,7 @@
         <v>0.05314690616465095</v>
       </c>
       <c r="I13" s="8" t="n">
-        <v>0.437515337095903</v>
+        <v>0.4382772529821747</v>
       </c>
       <c r="J13" s="8" t="n">
         <v>0.3038330334460154</v>
@@ -3344,7 +3344,7 @@
         <v>0.1591889594558804</v>
       </c>
       <c r="Q13" s="8" t="n">
-        <v>0.3220827360090838</v>
+        <v>0.3245544429169268</v>
       </c>
       <c r="R13" s="8" t="n">
         <v>0.05642784528241643</v>
@@ -3445,7 +3445,7 @@
         <v>0.06711757997426586</v>
       </c>
       <c r="I14" s="8" t="n">
-        <v>0.3068923166385865</v>
+        <v>0.3052773949238478</v>
       </c>
       <c r="J14" s="8" t="n">
         <v>0.1188141332968656</v>
@@ -3469,7 +3469,7 @@
         <v>0</v>
       </c>
       <c r="Q14" s="8" t="n">
-        <v>0.2703630396181377</v>
+        <v>0.2841218754377101</v>
       </c>
       <c r="R14" s="8" t="n">
         <v>0.06500922867994562</v>
@@ -3570,7 +3570,7 @@
         <v>0.07648402541532619</v>
       </c>
       <c r="I15" s="8" t="n">
-        <v>0.2666126873432231</v>
+        <v>0.2630222133721049</v>
       </c>
       <c r="J15" s="8" t="n">
         <v>0.359077508567882</v>
@@ -3594,7 +3594,7 @@
         <v>0</v>
       </c>
       <c r="Q15" s="8" t="n">
-        <v>0.1925305091549722</v>
+        <v>0.1854044553252107</v>
       </c>
       <c r="R15" s="8" t="n">
         <v>0.07522282961840202</v>
@@ -3695,7 +3695,7 @@
         <v>0.05658359149586913</v>
       </c>
       <c r="I16" s="8" t="n">
-        <v>0.3696003317755189</v>
+        <v>0.3665193738649404</v>
       </c>
       <c r="J16" s="8" t="n">
         <v>0.3540719866342907</v>
@@ -3719,7 +3719,7 @@
         <v>0.008212025400279706</v>
       </c>
       <c r="Q16" s="8" t="n">
-        <v>0.330148215220628</v>
+        <v>0.3335154453726568</v>
       </c>
       <c r="R16" s="8" t="n">
         <v>0.06734133785052378</v>
@@ -3820,7 +3820,7 @@
         <v>0.02131169906111717</v>
       </c>
       <c r="I17" s="8" t="n">
-        <v>0.108402913739202</v>
+        <v>0.1091960262470553</v>
       </c>
       <c r="J17" s="8" t="n">
         <v>0.2589586078131168</v>
@@ -3844,7 +3844,7 @@
         <v>0.1902868104613332</v>
       </c>
       <c r="Q17" s="8" t="n">
-        <v>0.08789183970810699</v>
+        <v>0.08705814051040492</v>
       </c>
       <c r="R17" s="8" t="n">
         <v>0.0213193557062846</v>
@@ -3945,7 +3945,7 @@
         <v>0.07190569187107652</v>
       </c>
       <c r="I18" s="8" t="n">
-        <v>0.2891906566963793</v>
+        <v>0.2869809204337536</v>
       </c>
       <c r="J18" s="8" t="n">
         <v>0.321054565119029</v>
@@ -3969,7 +3969,7 @@
         <v>0.06864356532638348</v>
       </c>
       <c r="Q18" s="8" t="n">
-        <v>0.2238238288367554</v>
+        <v>0.221898116805753</v>
       </c>
       <c r="R18" s="8" t="n">
         <v>0.07372571776612899</v>
@@ -4070,7 +4070,7 @@
         <v>0.1980421337302072</v>
       </c>
       <c r="I19" s="8" t="n">
-        <v>0.4918541964406851</v>
+        <v>0.4955278296067979</v>
       </c>
       <c r="J19" s="8" t="n">
         <v>0.09625829583878925</v>
@@ -4094,7 +4094,7 @@
         <v>0.07405875637983987</v>
       </c>
       <c r="Q19" s="8" t="n">
-        <v>0.3943336960217101</v>
+        <v>0.4093249092539533</v>
       </c>
       <c r="R19" s="8" t="n">
         <v>0.1706836352650273</v>
@@ -4195,7 +4195,7 @@
         <v>0.3612449568671795</v>
       </c>
       <c r="I20" s="8" t="n">
-        <v>0.4689545933407127</v>
+        <v>0.4694481329416557</v>
       </c>
       <c r="J20" s="8" t="n">
         <v>0.306849867917477</v>
@@ -4219,7 +4219,7 @@
         <v>0</v>
       </c>
       <c r="Q20" s="8" t="n">
-        <v>0.3870955960986875</v>
+        <v>0.3836694759372772</v>
       </c>
       <c r="R20" s="8" t="n">
         <v>0.3038640666076861</v>
@@ -4320,7 +4320,7 @@
         <v>0.4840028781078786</v>
       </c>
       <c r="I21" s="8" t="n">
-        <v>0.5734014667131363</v>
+        <v>0.5715291029952395</v>
       </c>
       <c r="J21" s="8" t="n">
         <v>0.3581199853240211</v>
@@ -4344,7 +4344,7 @@
         <v>0</v>
       </c>
       <c r="Q21" s="8" t="n">
-        <v>0.531027692093171</v>
+        <v>0.5405830191353553</v>
       </c>
       <c r="R21" s="8" t="n">
         <v>0.3913973308138089</v>
@@ -4445,7 +4445,7 @@
         <v>0.2791342122048749</v>
       </c>
       <c r="I22" s="8" t="n">
-        <v>0.3816916340423984</v>
+        <v>0.3827909427171838</v>
       </c>
       <c r="J22" s="8" t="n">
         <v>0.2973652997107525</v>
@@ -4469,7 +4469,7 @@
         <v>0</v>
       </c>
       <c r="Q22" s="8" t="n">
-        <v>0.2372398310572365</v>
+        <v>0.2245045031979623</v>
       </c>
       <c r="R22" s="8" t="n">
         <v>0.2248984830396033</v>
@@ -4570,7 +4570,7 @@
         <v>0.615705393526933</v>
       </c>
       <c r="I23" s="8" t="n">
-        <v>0.4903932410630287</v>
+        <v>0.4933349331938441</v>
       </c>
       <c r="J23" s="8" t="n">
         <v>0.09098437975875928</v>
@@ -4594,7 +4594,7 @@
         <v>0</v>
       </c>
       <c r="Q23" s="8" t="n">
-        <v>0.3868750083435854</v>
+        <v>0.3390232757955702</v>
       </c>
       <c r="R23" s="8" t="n">
         <v>0.5865519335856998</v>
@@ -4695,7 +4695,7 @@
         <v>0.5895188556708524</v>
       </c>
       <c r="I24" s="8" t="n">
-        <v>0.4200258793953427</v>
+        <v>0.4227251363898635</v>
       </c>
       <c r="J24" s="8" t="n">
         <v>0.1169767706156979</v>
@@ -4719,7 +4719,7 @@
         <v>0</v>
       </c>
       <c r="Q24" s="8" t="n">
-        <v>0.3034937498732732</v>
+        <v>0.2220878957621663</v>
       </c>
       <c r="R24" s="8" t="n">
         <v>0.5420780003054783</v>
@@ -4820,7 +4820,7 @@
         <v>0.5561627965220372</v>
       </c>
       <c r="I25" s="8" t="n">
-        <v>0.4635724710089937</v>
+        <v>0.4684228652600532</v>
       </c>
       <c r="J25" s="8" t="n">
         <v>0.08558725920021756</v>
@@ -4844,7 +4844,7 @@
         <v>0.07008184233626284</v>
       </c>
       <c r="Q25" s="8" t="n">
-        <v>0.3538982622124542</v>
+        <v>0.2870534277466352</v>
       </c>
       <c r="R25" s="8" t="n">
         <v>0.5301061077643351</v>
@@ -4945,7 +4945,7 @@
         <v>0.5759329532582764</v>
       </c>
       <c r="I26" s="8" t="n">
-        <v>0.5145364363494003</v>
+        <v>0.5181576637622629</v>
       </c>
       <c r="J26" s="8" t="n">
         <v>0.03307197154563031</v>
@@ -4969,7 +4969,7 @@
         <v>0.003827610032270321</v>
       </c>
       <c r="Q26" s="8" t="n">
-        <v>0.4178258057278063</v>
+        <v>0.34550746826306</v>
       </c>
       <c r="R26" s="8" t="n">
         <v>0.5606714951692212</v>
@@ -5070,7 +5070,7 @@
         <v>0.5973444999276875</v>
       </c>
       <c r="I27" s="8" t="n">
-        <v>0.3573070499048754</v>
+        <v>0.3580592586196705</v>
       </c>
       <c r="J27" s="8" t="n">
         <v>0.01420349424261558</v>
@@ -5094,7 +5094,7 @@
         <v>0.0004942557236135218</v>
       </c>
       <c r="Q27" s="8" t="n">
-        <v>0.2634716875505285</v>
+        <v>0.2107429996617773</v>
       </c>
       <c r="R27" s="8" t="n">
         <v>0.5934752675131713</v>
@@ -5195,7 +5195,7 @@
         <v>0.4925937839437214</v>
       </c>
       <c r="I28" s="8" t="n">
-        <v>0.3200013365025554</v>
+        <v>0.322106992020689</v>
       </c>
       <c r="J28" s="8" t="n">
         <v>0.007717688780782552</v>
@@ -5219,7 +5219,7 @@
         <v>0.003196116378944724</v>
       </c>
       <c r="Q28" s="8" t="n">
-        <v>0.2074597514294624</v>
+        <v>0.1568377315753973</v>
       </c>
       <c r="R28" s="8" t="n">
         <v>0.4735116731220889</v>
@@ -5320,7 +5320,7 @@
         <v>0.5919023500485407</v>
       </c>
       <c r="I29" s="8" t="n">
-        <v>0.3187106170331858</v>
+        <v>0.3227055278028361</v>
       </c>
       <c r="J29" s="8" t="n">
         <v>0.01759717640512861</v>
@@ -5344,7 +5344,7 @@
         <v>0.001080459770114942</v>
       </c>
       <c r="Q29" s="8" t="n">
-        <v>0.2270199449830936</v>
+        <v>0.1810626419720419</v>
       </c>
       <c r="R29" s="8" t="n">
         <v>0.5817281233031705</v>
@@ -5445,7 +5445,7 @@
         <v>0.5818017989380707</v>
       </c>
       <c r="I30" s="8" t="n">
-        <v>0.334534053722944</v>
+        <v>0.3371002818429862</v>
       </c>
       <c r="J30" s="8" t="n">
         <v>0.02721049147158843</v>
@@ -5469,7 +5469,7 @@
         <v>0.007461200197087401</v>
       </c>
       <c r="Q30" s="8" t="n">
-        <v>0.2535906376709611</v>
+        <v>0.2136150856490995</v>
       </c>
       <c r="R30" s="8" t="n">
         <v>0.5502689131338785</v>
@@ -5570,7 +5570,7 @@
         <v>0.5212916627063727</v>
       </c>
       <c r="I31" s="8" t="n">
-        <v>0.3233809764872677</v>
+        <v>0.3231003320989843</v>
       </c>
       <c r="J31" s="8" t="n">
         <v>0.166652397354054</v>
@@ -5594,7 +5594,7 @@
         <v>0.01245559684623291</v>
       </c>
       <c r="Q31" s="8" t="n">
-        <v>0.2823862435905811</v>
+        <v>0.2426746668588748</v>
       </c>
       <c r="R31" s="8" t="n">
         <v>0.5127686203016907</v>
@@ -5695,7 +5695,7 @@
         <v>0.5784440895923193</v>
       </c>
       <c r="I32" s="8" t="n">
-        <v>0.3883448165802855</v>
+        <v>0.3879697026401987</v>
       </c>
       <c r="J32" s="8" t="n">
         <v>0.1154941554898443</v>
@@ -5719,7 +5719,7 @@
         <v>0</v>
       </c>
       <c r="Q32" s="8" t="n">
-        <v>0.3020453718994595</v>
+        <v>0.2361718888806929</v>
       </c>
       <c r="R32" s="8" t="n">
         <v>0.5436311745428103</v>
@@ -5820,7 +5820,7 @@
         <v>0.6050289703473958</v>
       </c>
       <c r="I33" s="8" t="n">
-        <v>0.5197100678108484</v>
+        <v>0.5182317077108026</v>
       </c>
       <c r="J33" s="8" t="n">
         <v>0.1366621402722183</v>
@@ -5844,7 +5844,7 @@
         <v>0.002871160844947126</v>
       </c>
       <c r="Q33" s="8" t="n">
-        <v>0.4432853527100533</v>
+        <v>0.3903838361108923</v>
       </c>
       <c r="R33" s="8" t="n">
         <v>0.59743348510692</v>
@@ -5945,7 +5945,7 @@
         <v>0.04995279353985525</v>
       </c>
       <c r="I34" s="8" t="n">
-        <v>0.3003531901228467</v>
+        <v>0.2987173997068586</v>
       </c>
       <c r="J34" s="8" t="n">
         <v>0.4397248388139633</v>
@@ -5969,7 +5969,7 @@
         <v>0.002297347278070735</v>
       </c>
       <c r="Q34" s="8" t="n">
-        <v>0.2493545426304302</v>
+        <v>0.2566678535882071</v>
       </c>
       <c r="R34" s="6" t="n"/>
       <c r="S34" s="8" t="n">
@@ -6068,7 +6068,7 @@
         <v>0.08610701077350245</v>
       </c>
       <c r="I35" s="8" t="n">
-        <v>0.297700055931894</v>
+        <v>0.294257587102398</v>
       </c>
       <c r="J35" s="8" t="n">
         <v>0.4957765970741662</v>
@@ -6092,7 +6092,7 @@
         <v>0</v>
       </c>
       <c r="Q35" s="8" t="n">
-        <v>0.2496670661508497</v>
+        <v>0.2540653111847259</v>
       </c>
       <c r="R35" s="6" t="n"/>
       <c r="S35" s="8" t="n">
@@ -6191,7 +6191,7 @@
         <v>0.04774581714398502</v>
       </c>
       <c r="I36" s="8" t="n">
-        <v>0.1292809913636021</v>
+        <v>0.1275336932182636</v>
       </c>
       <c r="J36" s="8" t="n">
         <v>0.4255827491387117</v>
@@ -6215,7 +6215,7 @@
         <v>5.674966304887565e-06</v>
       </c>
       <c r="Q36" s="8" t="n">
-        <v>0.1322693112881368</v>
+        <v>0.1401104632509271</v>
       </c>
       <c r="R36" s="6" t="n"/>
       <c r="S36" s="8" t="n">
@@ -6314,7 +6314,7 @@
         <v>0.07093203293879712</v>
       </c>
       <c r="I37" s="8" t="n">
-        <v>0.2610917710388703</v>
+        <v>0.2628279374221738</v>
       </c>
       <c r="J37" s="8" t="n">
         <v>0.5730718861679345</v>
@@ -6338,7 +6338,7 @@
         <v>0.004734980010675086</v>
       </c>
       <c r="Q37" s="8" t="n">
-        <v>0.1857129530928069</v>
+        <v>0.1804975475838712</v>
       </c>
       <c r="R37" s="8" t="n">
         <v>0.07341473214285714</v>
@@ -6439,7 +6439,7 @@
         <v>0.06656250250063231</v>
       </c>
       <c r="I38" s="8" t="n">
-        <v>0.1828334702442257</v>
+        <v>0.1813080714608584</v>
       </c>
       <c r="J38" s="8" t="n">
         <v>0.7254992929302121</v>
@@ -6463,7 +6463,7 @@
         <v>0.003883947067313284</v>
       </c>
       <c r="Q38" s="8" t="n">
-        <v>0.1215765370803109</v>
+        <v>0.1180296847854978</v>
       </c>
       <c r="R38" s="8" t="n">
         <v>0.06718821428571428</v>
@@ -6564,7 +6564,7 @@
         <v>0.06394063032027927</v>
       </c>
       <c r="I39" s="8" t="n">
-        <v>0.2062521127157661</v>
+        <v>0.2057975932419831</v>
       </c>
       <c r="J39" s="8" t="n">
         <v>0.7157628548054292</v>
@@ -6588,7 +6588,7 @@
         <v>0.1558533871980653</v>
       </c>
       <c r="Q39" s="8" t="n">
-        <v>0.1599607422485594</v>
+        <v>0.1643498769760758</v>
       </c>
       <c r="R39" s="8" t="n">
         <v>0.06263669642857143</v>
@@ -6689,7 +6689,7 @@
         <v>0.08759380268068874</v>
       </c>
       <c r="I40" s="8" t="n">
-        <v>0.2131390490049534</v>
+        <v>0.2134190314084203</v>
       </c>
       <c r="J40" s="8" t="n">
         <v>0.7498758330400573</v>
@@ -6713,7 +6713,7 @@
         <v>0.1839780286489686</v>
       </c>
       <c r="Q40" s="8" t="n">
-        <v>0.1604494162619163</v>
+        <v>0.1588515237374003</v>
       </c>
       <c r="R40" s="8" t="n">
         <v>0.0881675</v>
@@ -6814,7 +6814,7 @@
         <v>0.08707747578392815</v>
       </c>
       <c r="I41" s="8" t="n">
-        <v>0.1316067591096966</v>
+        <v>0.1317542994634667</v>
       </c>
       <c r="J41" s="8" t="n">
         <v>0.7105777265732514</v>
@@ -6838,7 +6838,7 @@
         <v>0.134348311533427</v>
       </c>
       <c r="Q41" s="8" t="n">
-        <v>0.1021921869619785</v>
+        <v>0.1149379572832894</v>
       </c>
       <c r="R41" s="8" t="n">
         <v>0.08746723214285715</v>
@@ -6939,7 +6939,7 @@
         <v>0.09967570734611027</v>
       </c>
       <c r="I42" s="8" t="n">
-        <v>0.1461315555985361</v>
+        <v>0.1423290362414266</v>
       </c>
       <c r="J42" s="8" t="n">
         <v>0.654829407281354</v>
@@ -6963,7 +6963,7 @@
         <v>0.112359051697847</v>
       </c>
       <c r="Q42" s="8" t="n">
-        <v>0.1298581750725149</v>
+        <v>0.1179654762576029</v>
       </c>
       <c r="R42" s="8" t="n">
         <v>0.1004651785714286</v>
@@ -7064,7 +7064,7 @@
         <v>0.09021942111871566</v>
       </c>
       <c r="I43" s="8" t="n">
-        <v>0.172832099890751</v>
+        <v>0.1704108202966669</v>
       </c>
       <c r="J43" s="8" t="n">
         <v>0.7135946379603642</v>
@@ -7088,7 +7088,7 @@
         <v>0.0180289329996563</v>
       </c>
       <c r="Q43" s="8" t="n">
-        <v>0.1629344558350371</v>
+        <v>0.1615295451531813</v>
       </c>
       <c r="R43" s="8" t="n">
         <v>0.08885544642857142</v>
@@ -7189,7 +7189,7 @@
         <v>0.09090695503428134</v>
       </c>
       <c r="I44" s="8" t="n">
-        <v>0.2510514344511225</v>
+        <v>0.2501513176903043</v>
       </c>
       <c r="J44" s="8" t="n">
         <v>0.7127331858199215</v>
@@ -7213,7 +7213,7 @@
         <v>0.01440440648375724</v>
       </c>
       <c r="Q44" s="8" t="n">
-        <v>0.1819872452111254</v>
+        <v>0.1750517740906742</v>
       </c>
       <c r="R44" s="8" t="n">
         <v>0.09066205357142858</v>
@@ -7314,7 +7314,7 @@
         <v>0.06803519701929768</v>
       </c>
       <c r="I45" s="8" t="n">
-        <v>0.2204769143483211</v>
+        <v>0.2214171237268341</v>
       </c>
       <c r="J45" s="8" t="n">
         <v>0.709056713948459</v>
@@ -7338,7 +7338,7 @@
         <v>0.1589020285951069</v>
       </c>
       <c r="Q45" s="8" t="n">
-        <v>0.1712058468280536</v>
+        <v>0.1759912125791871</v>
       </c>
       <c r="R45" s="8" t="n">
         <v>0.06732964285714285</v>
@@ -7439,7 +7439,7 @@
         <v>0.06651923813614578</v>
       </c>
       <c r="I46" s="8" t="n">
-        <v>0.1246464818479319</v>
+        <v>0.1231427717818399</v>
       </c>
       <c r="J46" s="8" t="n">
         <v>0.5731825163934416</v>
@@ -7463,7 +7463,7 @@
         <v>0.1885439184965282</v>
       </c>
       <c r="Q46" s="8" t="n">
-        <v>0.1066877005591809</v>
+        <v>0.1124810432396046</v>
       </c>
       <c r="R46" s="8" t="n">
         <v>0.06696026785714285</v>
@@ -7564,7 +7564,7 @@
         <v>0.08695957982449913</v>
       </c>
       <c r="I47" s="8" t="n">
-        <v>0.1186528568416371</v>
+        <v>0.1150820776693585</v>
       </c>
       <c r="J47" s="8" t="n">
         <v>0.729876437662668</v>
@@ -7588,7 +7588,7 @@
         <v>0.03785526569536701</v>
       </c>
       <c r="Q47" s="8" t="n">
-        <v>0.1440688140786628</v>
+        <v>0.1426584688189552</v>
       </c>
       <c r="R47" s="8" t="n">
         <v>0.0890999107142857</v>
@@ -7693,7 +7693,7 @@
         <v>0.8136883140137644</v>
       </c>
       <c r="I48" s="8" t="n">
-        <v>0.5759325511457223</v>
+        <v>0.5677001876231041</v>
       </c>
       <c r="J48" s="8" t="n">
         <v>0.06843563942598777</v>
@@ -7717,7 +7717,7 @@
         <v>0</v>
       </c>
       <c r="Q48" s="8" t="n">
-        <v>0.4962717085428747</v>
+        <v>0.3995122178248695</v>
       </c>
       <c r="R48" s="8" t="n">
         <v>0.8007416964285714</v>
@@ -7822,7 +7822,7 @@
         <v>0.8008900985549825</v>
       </c>
       <c r="I49" s="8" t="n">
-        <v>0.5900794664251808</v>
+        <v>0.582296626539144</v>
       </c>
       <c r="J49" s="8" t="n">
         <v>0.1518578451701466</v>
@@ -7846,7 +7846,7 @@
         <v>0.004935323383084577</v>
       </c>
       <c r="Q49" s="8" t="n">
-        <v>0.4905030879040984</v>
+        <v>0.3897722946156296</v>
       </c>
       <c r="R49" s="8" t="n">
         <v>0.7875364285714286</v>
@@ -7951,7 +7951,7 @@
         <v>0.8046617201642861</v>
       </c>
       <c r="I50" s="8" t="n">
-        <v>0.5740639090496125</v>
+        <v>0.5657929223633436</v>
       </c>
       <c r="J50" s="8" t="n">
         <v>0.09653349738250395</v>
@@ -7975,7 +7975,7 @@
         <v>0.00761997433469837</v>
       </c>
       <c r="Q50" s="8" t="n">
-        <v>0.4948243076906235</v>
+        <v>0.4011950032714341</v>
       </c>
       <c r="R50" s="8" t="n">
         <v>0.7857409821428571</v>
@@ -8080,7 +8080,7 @@
         <v>0.8177672497375904</v>
       </c>
       <c r="I51" s="8" t="n">
-        <v>0.5970712609902272</v>
+        <v>0.5894784721933289</v>
       </c>
       <c r="J51" s="8" t="n">
         <v>0.1318340404310156</v>
@@ -8104,7 +8104,7 @@
         <v>0.003058766028405497</v>
       </c>
       <c r="Q51" s="8" t="n">
-        <v>0.5524580325425931</v>
+        <v>0.4568852954805017</v>
       </c>
       <c r="R51" s="8" t="n">
         <v>0.8055594642857142</v>
@@ -8209,7 +8209,7 @@
         <v>0.8074176529682655</v>
       </c>
       <c r="I52" s="8" t="n">
-        <v>0.5766584557699114</v>
+        <v>0.5684695756320907</v>
       </c>
       <c r="J52" s="8" t="n">
         <v>0.0652769349736944</v>
@@ -8233,7 +8233,7 @@
         <v>0.00405586941638501</v>
       </c>
       <c r="Q52" s="8" t="n">
-        <v>0.5656924066456906</v>
+        <v>0.4861186438751759</v>
       </c>
       <c r="R52" s="8" t="n">
         <v>0.7923371428571429</v>
@@ -8338,7 +8338,7 @@
         <v>0.8183742533273459</v>
       </c>
       <c r="I53" s="8" t="n">
-        <v>0.5822070606951332</v>
+        <v>0.5740481497785984</v>
       </c>
       <c r="J53" s="8" t="n">
         <v>0.08555815308261105</v>
@@ -8362,7 +8362,7 @@
         <v>0.008347225733710573</v>
       </c>
       <c r="Q53" s="8" t="n">
-        <v>0.5382075424550951</v>
+        <v>0.4443938205386393</v>
       </c>
       <c r="R53" s="8" t="n">
         <v>0.8104016071428572</v>
@@ -8467,7 +8467,7 @@
         <v>0.7850781213419332</v>
       </c>
       <c r="I54" s="8" t="n">
-        <v>0.505313242309862</v>
+        <v>0.4997868493479093</v>
       </c>
       <c r="J54" s="8" t="n">
         <v>0.1011723300738118</v>
@@ -8491,7 +8491,7 @@
         <v>0.01254178611919385</v>
       </c>
       <c r="Q54" s="8" t="n">
-        <v>0.4413148588677</v>
+        <v>0.3465323671325427</v>
       </c>
       <c r="R54" s="8" t="n">
         <v>0.7770362500000001</v>
@@ -8596,7 +8596,7 @@
         <v>0.8027353461390259</v>
       </c>
       <c r="I55" s="8" t="n">
-        <v>0.5107824404121427</v>
+        <v>0.5066063215411988</v>
       </c>
       <c r="J55" s="8" t="n">
         <v>0.08789435255941758</v>
@@ -8620,7 +8620,7 @@
         <v>0.0003526364168129021</v>
       </c>
       <c r="Q55" s="8" t="n">
-        <v>0.4251717523288531</v>
+        <v>0.3237045438840803</v>
       </c>
       <c r="R55" s="8" t="n">
         <v>0.78134875</v>
@@ -8725,7 +8725,7 @@
         <v>0.7846345092371497</v>
       </c>
       <c r="I56" s="8" t="n">
-        <v>0.5086744975105195</v>
+        <v>0.5028120402090405</v>
       </c>
       <c r="J56" s="8" t="n">
         <v>0.1263195474865841</v>
@@ -8749,7 +8749,7 @@
         <v>0.01661136270260715</v>
       </c>
       <c r="Q56" s="8" t="n">
-        <v>0.4212002165161201</v>
+        <v>0.3161481235148116</v>
       </c>
       <c r="R56" s="8" t="n">
         <v>0.773245267857143</v>
@@ -8854,7 +8854,7 @@
         <v>0.7987928798489364</v>
       </c>
       <c r="I57" s="8" t="n">
-        <v>0.5696456027853507</v>
+        <v>0.562373146594247</v>
       </c>
       <c r="J57" s="8" t="n">
         <v>0.1430780838456736</v>
@@ -8878,7 +8878,7 @@
         <v>0.001269233966977597</v>
       </c>
       <c r="Q57" s="8" t="n">
-        <v>0.5100572269161704</v>
+        <v>0.4121226766188843</v>
       </c>
       <c r="R57" s="8" t="n">
         <v>0.7873627678571429</v>
@@ -8983,7 +8983,7 @@
         <v>0.7878103803819503</v>
       </c>
       <c r="I58" s="8" t="n">
-        <v>0.574821091977986</v>
+        <v>0.5681619289108625</v>
       </c>
       <c r="J58" s="8" t="n">
         <v>0.07608381872174343</v>
@@ -9007,7 +9007,7 @@
         <v>0</v>
       </c>
       <c r="Q58" s="8" t="n">
-        <v>0.5266539849654469</v>
+        <v>0.442521591726699</v>
       </c>
       <c r="R58" s="8" t="n">
         <v>0.7723658035714285</v>
@@ -9112,7 +9112,7 @@
         <v>0.7832563977537006</v>
       </c>
       <c r="I59" s="8" t="n">
-        <v>0.5806072640904526</v>
+        <v>0.5733737446801712</v>
       </c>
       <c r="J59" s="8" t="n">
         <v>0.08916882076919723</v>
@@ -9136,7 +9136,7 @@
         <v>0.00131006596370109</v>
       </c>
       <c r="Q59" s="8" t="n">
-        <v>0.5229633130554673</v>
+        <v>0.4306838127917891</v>
       </c>
       <c r="R59" s="8" t="n">
         <v>0.7708849107142858</v>
@@ -9241,7 +9241,7 @@
         <v>0.724032310214585</v>
       </c>
       <c r="I60" s="8" t="n">
-        <v>0.568604088405708</v>
+        <v>0.5643431677769046</v>
       </c>
       <c r="J60" s="8" t="n">
         <v>0.02367256121344071</v>
@@ -9265,7 +9265,7 @@
         <v>0</v>
       </c>
       <c r="Q60" s="8" t="n">
-        <v>0.5080374082500295</v>
+        <v>0.4330393273346904</v>
       </c>
       <c r="R60" s="8" t="n">
         <v>0.6971591071428571</v>
@@ -9370,7 +9370,7 @@
         <v>0.7423191810575347</v>
       </c>
       <c r="I61" s="8" t="n">
-        <v>0.5609395356736532</v>
+        <v>0.5575933380815636</v>
       </c>
       <c r="J61" s="8" t="n">
         <v>0.006603929133667553</v>
@@ -9394,7 +9394,7 @@
         <v>0</v>
       </c>
       <c r="Q61" s="8" t="n">
-        <v>0.4781215064207674</v>
+        <v>0.4001618274808598</v>
       </c>
       <c r="R61" s="8" t="n">
         <v>0.7245010714285716</v>
@@ -9499,7 +9499,7 @@
         <v>0.7466250410186623</v>
       </c>
       <c r="I62" s="8" t="n">
-        <v>0.5014150303913784</v>
+        <v>0.497296379549992</v>
       </c>
       <c r="J62" s="8" t="n">
         <v>0.008713288573196559</v>
@@ -9523,7 +9523,7 @@
         <v>0</v>
       </c>
       <c r="Q62" s="8" t="n">
-        <v>0.4181409397743939</v>
+        <v>0.3373475688918717</v>
       </c>
       <c r="R62" s="8" t="n">
         <v>0.7388534821428572</v>
@@ -9628,7 +9628,7 @@
         <v>0.7591967598179986</v>
       </c>
       <c r="I63" s="8" t="n">
-        <v>0.5845945784382918</v>
+        <v>0.5802859728263381</v>
       </c>
       <c r="J63" s="8" t="n">
         <v>0.1067027281166099</v>
@@ -9652,7 +9652,7 @@
         <v>0.02005630540548931</v>
       </c>
       <c r="Q63" s="8" t="n">
-        <v>0.5694146746472306</v>
+        <v>0.5011549055779692</v>
       </c>
       <c r="R63" s="8" t="n">
         <v>0.7485530357142858</v>
@@ -9757,7 +9757,7 @@
         <v>0.8081613016625111</v>
       </c>
       <c r="I64" s="8" t="n">
-        <v>0.529135163174509</v>
+        <v>0.5270415909363071</v>
       </c>
       <c r="J64" s="8" t="n">
         <v>0.02716211213156736</v>
@@ -9781,7 +9781,7 @@
         <v>0.01071374377797456</v>
       </c>
       <c r="Q64" s="8" t="n">
-        <v>0.4980285489997337</v>
+        <v>0.412754645828162</v>
       </c>
       <c r="R64" s="8" t="n">
         <v>0.8025205357142858</v>
@@ -9886,7 +9886,7 @@
         <v>0.8080634360623858</v>
       </c>
       <c r="I65" s="8" t="n">
-        <v>0.5883387627729049</v>
+        <v>0.5823537441242931</v>
       </c>
       <c r="J65" s="8" t="n">
         <v>0.1382213591732285</v>
@@ -9910,7 +9910,7 @@
         <v>0.001374289958110727</v>
       </c>
       <c r="Q65" s="8" t="n">
-        <v>0.5708928736249361</v>
+        <v>0.4871210940659988</v>
       </c>
       <c r="R65" s="8" t="n">
         <v>0.8061571428571428</v>
@@ -10015,7 +10015,7 @@
         <v>0.8260033540447934</v>
       </c>
       <c r="I66" s="8" t="n">
-        <v>0.6197455956394582</v>
+        <v>0.6128647388285027</v>
       </c>
       <c r="J66" s="8" t="n">
         <v>0.06804702171150975</v>
@@ -10039,7 +10039,7 @@
         <v>0</v>
       </c>
       <c r="Q66" s="8" t="n">
-        <v>0.5823309289450839</v>
+        <v>0.4989905663886519</v>
       </c>
       <c r="R66" s="8" t="n">
         <v>0.8155291964285715</v>
@@ -10144,7 +10144,7 @@
         <v>0.8142832408541916</v>
       </c>
       <c r="I67" s="8" t="n">
-        <v>0.5911933199916919</v>
+        <v>0.5835080372268966</v>
       </c>
       <c r="J67" s="8" t="n">
         <v>0.06927998835823129</v>
@@ -10168,7 +10168,7 @@
         <v>0.004200942246379051</v>
       </c>
       <c r="Q67" s="8" t="n">
-        <v>0.5357474084408544</v>
+        <v>0.4521332359173558</v>
       </c>
       <c r="R67" s="8" t="n">
         <v>0.7929608928571429</v>
@@ -10273,7 +10273,7 @@
         <v>0.7719087642390307</v>
       </c>
       <c r="I68" s="8" t="n">
-        <v>0.6104620428105837</v>
+        <v>0.6034973387284106</v>
       </c>
       <c r="J68" s="8" t="n">
         <v>0.0688994168344179</v>
@@ -10297,7 +10297,7 @@
         <v>0.006321653189577717</v>
       </c>
       <c r="Q68" s="8" t="n">
-        <v>0.6266377118519755</v>
+        <v>0.5690552875988325</v>
       </c>
       <c r="R68" s="8" t="n">
         <v>0.7600363392857142</v>
@@ -10402,7 +10402,7 @@
         <v>0.776610827246613</v>
       </c>
       <c r="I69" s="8" t="n">
-        <v>0.619345517780862</v>
+        <v>0.6129941113697178</v>
       </c>
       <c r="J69" s="8" t="n">
         <v>0.0340248026665468</v>
@@ -10426,7 +10426,7 @@
         <v>0</v>
       </c>
       <c r="Q69" s="8" t="n">
-        <v>0.6359802301262787</v>
+        <v>0.5931876444678675</v>
       </c>
       <c r="R69" s="8" t="n">
         <v>0.7662770535714285</v>
@@ -10531,7 +10531,7 @@
         <v>0.7790269189659813</v>
       </c>
       <c r="I70" s="8" t="n">
-        <v>0.6067700314070038</v>
+        <v>0.5995666076354507</v>
       </c>
       <c r="J70" s="8" t="n">
         <v>0.04029205514530446</v>
@@ -10555,7 +10555,7 @@
         <v>0.000149812734082397</v>
       </c>
       <c r="Q70" s="8" t="n">
-        <v>0.6377797130582632</v>
+        <v>0.5869023978538429</v>
       </c>
       <c r="R70" s="8" t="n">
         <v>0.7604810714285714</v>
@@ -10660,7 +10660,7 @@
         <v>0.8079783201645542</v>
       </c>
       <c r="I71" s="8" t="n">
-        <v>0.5315286027861645</v>
+        <v>0.5250716070519559</v>
       </c>
       <c r="J71" s="8" t="n">
         <v>0.1095537701527611</v>
@@ -10684,7 +10684,7 @@
         <v>6.595593094429736e-05</v>
       </c>
       <c r="Q71" s="8" t="n">
-        <v>0.4776345374735641</v>
+        <v>0.3927997149393511</v>
       </c>
       <c r="R71" s="8" t="n">
         <v>0.8022620535714287</v>
@@ -10789,7 +10789,7 @@
         <v>0.8080439942396026</v>
       </c>
       <c r="I72" s="8" t="n">
-        <v>0.5420926640650123</v>
+        <v>0.5353606262830574</v>
       </c>
       <c r="J72" s="8" t="n">
         <v>0.07646946695009843</v>
@@ -10813,7 +10813,7 @@
         <v>0.0003159842086885318</v>
       </c>
       <c r="Q72" s="8" t="n">
-        <v>0.4792229669629877</v>
+        <v>0.3931822210346516</v>
       </c>
       <c r="R72" s="8" t="n">
         <v>0.7921215178571428</v>
@@ -10918,7 +10918,7 @@
         <v>0.8066579191546218</v>
       </c>
       <c r="I73" s="8" t="n">
-        <v>0.5234283038727594</v>
+        <v>0.5165430434649504</v>
       </c>
       <c r="J73" s="8" t="n">
         <v>0.08840891323348574</v>
@@ -10942,7 +10942,7 @@
         <v>0.001497331031136089</v>
       </c>
       <c r="Q73" s="8" t="n">
-        <v>0.4389349384895086</v>
+        <v>0.3473583197445045</v>
       </c>
       <c r="R73" s="8" t="n">
         <v>0.7994815178571428</v>
@@ -11047,7 +11047,7 @@
         <v>0.807196324826161</v>
       </c>
       <c r="I74" s="8" t="n">
-        <v>0.5611355500637861</v>
+        <v>0.5542859382998745</v>
       </c>
       <c r="J74" s="8" t="n">
         <v>0.07595704545500902</v>
@@ -11071,7 +11071,7 @@
         <v>0.001484011043758873</v>
       </c>
       <c r="Q74" s="8" t="n">
-        <v>0.5586856876964804</v>
+        <v>0.4857987217680888</v>
       </c>
       <c r="R74" s="8" t="n">
         <v>0.7986346428571428</v>
@@ -11176,7 +11176,7 @@
         <v>0.8018423877331861</v>
       </c>
       <c r="I75" s="8" t="n">
-        <v>0.5591218290441597</v>
+        <v>0.5542848498148335</v>
       </c>
       <c r="J75" s="8" t="n">
         <v>0.0357950908936762</v>
@@ -11200,7 +11200,7 @@
         <v>0.0004638176893056378</v>
       </c>
       <c r="Q75" s="8" t="n">
-        <v>0.5413791369129337</v>
+        <v>0.4637893624987755</v>
       </c>
       <c r="R75" s="8" t="n">
         <v>0.794493125</v>
@@ -11305,7 +11305,7 @@
         <v>0.8102988933169905</v>
       </c>
       <c r="I76" s="8" t="n">
-        <v>0.5552634767325095</v>
+        <v>0.5499121044413375</v>
       </c>
       <c r="J76" s="8" t="n">
         <v>0.03510566492884772</v>
@@ -11329,7 +11329,7 @@
         <v>0.0008152070940517736</v>
       </c>
       <c r="Q76" s="8" t="n">
-        <v>0.5134358586982574</v>
+        <v>0.4315251566748189</v>
       </c>
       <c r="R76" s="8" t="n">
         <v>0.78678875</v>
@@ -11434,7 +11434,7 @@
         <v>0.8125800689370167</v>
       </c>
       <c r="I77" s="8" t="n">
-        <v>0.5612978921190001</v>
+        <v>0.5574877401058459</v>
       </c>
       <c r="J77" s="8" t="n">
         <v>0.05454555880851487</v>
@@ -11458,7 +11458,7 @@
         <v>0.006449941991512317</v>
       </c>
       <c r="Q77" s="8" t="n">
-        <v>0.5317930488762742</v>
+        <v>0.4449461121112313</v>
       </c>
       <c r="R77" s="8" t="n">
         <v>0.8087842857142855</v>
@@ -11563,7 +11563,7 @@
         <v>0.8203811702704832</v>
       </c>
       <c r="I78" s="8" t="n">
-        <v>0.5796972249523359</v>
+        <v>0.5713134386813186</v>
       </c>
       <c r="J78" s="8" t="n">
         <v>0.04584005081342078</v>
@@ -11587,7 +11587,7 @@
         <v>0.006459678435354935</v>
       </c>
       <c r="Q78" s="8" t="n">
-        <v>0.521333459742873</v>
+        <v>0.432487548854247</v>
       </c>
       <c r="R78" s="8" t="n">
         <v>0.8009373214285714</v>
@@ -11692,7 +11692,7 @@
         <v>0.8068609125620857</v>
       </c>
       <c r="I79" s="8" t="n">
-        <v>0.5862760281837283</v>
+        <v>0.5787487532991539</v>
       </c>
       <c r="J79" s="8" t="n">
         <v>0.08610317020504957</v>
@@ -11716,7 +11716,7 @@
         <v>0.0003227608466265284</v>
       </c>
       <c r="Q79" s="8" t="n">
-        <v>0.536109428765156</v>
+        <v>0.4542503183027353</v>
       </c>
       <c r="R79" s="8" t="n">
         <v>0.7937219642857142</v>
@@ -11821,7 +11821,7 @@
         <v>0.7909214855624073</v>
       </c>
       <c r="I80" s="8" t="n">
-        <v>0.5350656555762138</v>
+        <v>0.5272849308935762</v>
       </c>
       <c r="J80" s="8" t="n">
         <v>0.05117535251021859</v>
@@ -11845,7 +11845,7 @@
         <v>0.009962357468149012</v>
       </c>
       <c r="Q80" s="8" t="n">
-        <v>0.4826811927006752</v>
+        <v>0.3875404988114614</v>
       </c>
       <c r="R80" s="8" t="n">
         <v>0.7743558035714287</v>
@@ -11950,7 +11950,7 @@
         <v>0.7944625734401212</v>
       </c>
       <c r="I81" s="8" t="n">
-        <v>0.5864127079902813</v>
+        <v>0.5799628648130626</v>
       </c>
       <c r="J81" s="8" t="n">
         <v>0.03569924434488574</v>
@@ -11974,7 +11974,7 @@
         <v>0.008672438672438672</v>
       </c>
       <c r="Q81" s="8" t="n">
-        <v>0.5259309831647893</v>
+        <v>0.4504084551688125</v>
       </c>
       <c r="R81" s="8" t="n">
         <v>0.7764807142857143</v>
@@ -12079,7 +12079,7 @@
         <v>0.7852092277087438</v>
       </c>
       <c r="I82" s="8" t="n">
-        <v>0.5154254354564081</v>
+        <v>0.5099456629267393</v>
       </c>
       <c r="J82" s="8" t="n">
         <v>0.05778374136625384</v>
@@ -12103,7 +12103,7 @@
         <v>0.01052962244736297</v>
       </c>
       <c r="Q82" s="8" t="n">
-        <v>0.4528582359077729</v>
+        <v>0.3531300739692544</v>
       </c>
       <c r="R82" s="8" t="n">
         <v>0.7652291071428571</v>
@@ -12208,7 +12208,7 @@
         <v>0.802332762554315</v>
       </c>
       <c r="I83" s="8" t="n">
-        <v>0.5701615514062759</v>
+        <v>0.5632011704613772</v>
       </c>
       <c r="J83" s="8" t="n">
         <v>0.02894704456371488</v>
@@ -12232,7 +12232,7 @@
         <v>0.002144602558574098</v>
       </c>
       <c r="Q83" s="8" t="n">
-        <v>0.56659384879815</v>
+        <v>0.5019390909219841</v>
       </c>
       <c r="R83" s="8" t="n">
         <v>0.7805198214285713</v>
@@ -12337,7 +12337,7 @@
         <v>0.8017231677739327</v>
       </c>
       <c r="I84" s="8" t="n">
-        <v>0.6250702681755422</v>
+        <v>0.6185781486884153</v>
       </c>
       <c r="J84" s="8" t="n">
         <v>0.07050689481185976</v>
@@ -12361,7 +12361,7 @@
         <v>0.02889535822376695</v>
       </c>
       <c r="Q84" s="8" t="n">
-        <v>0.5787827939935262</v>
+        <v>0.4959229561518971</v>
       </c>
       <c r="R84" s="8" t="n">
         <v>0.7958074107142856</v>
@@ -12466,7 +12466,7 @@
         <v>0.8098944936789222</v>
       </c>
       <c r="I85" s="8" t="n">
-        <v>0.6384177790261105</v>
+        <v>0.6325450829226833</v>
       </c>
       <c r="J85" s="8" t="n">
         <v>0.07215013312676115</v>
@@ -12490,7 +12490,7 @@
         <v>0.03593662217078809</v>
       </c>
       <c r="Q85" s="8" t="n">
-        <v>0.6335042779534008</v>
+        <v>0.5690121686974039</v>
       </c>
       <c r="R85" s="8" t="n">
         <v>0.8054017857142858</v>
@@ -12595,7 +12595,7 @@
         <v>0.8154722186221396</v>
       </c>
       <c r="I86" s="8" t="n">
-        <v>0.6528606601913812</v>
+        <v>0.6463983000708395</v>
       </c>
       <c r="J86" s="8" t="n">
         <v>0.01412613712731523</v>
@@ -12619,7 +12619,7 @@
         <v>0.003891478103437678</v>
       </c>
       <c r="Q86" s="8" t="n">
-        <v>0.6862260839053274</v>
+        <v>0.6389372781840088</v>
       </c>
       <c r="R86" s="8" t="n">
         <v>0.8110401785714286</v>
@@ -12724,7 +12724,7 @@
         <v>0.7937043628428023</v>
       </c>
       <c r="I87" s="8" t="n">
-        <v>0.6972152902481864</v>
+        <v>0.6927623516413072</v>
       </c>
       <c r="J87" s="8" t="n">
         <v>0.03196491042965036</v>
@@ -12748,7 +12748,7 @@
         <v>0.04082205439410184</v>
       </c>
       <c r="Q87" s="8" t="n">
-        <v>0.7353143754678678</v>
+        <v>0.7059090727872862</v>
       </c>
       <c r="R87" s="8" t="n">
         <v>0.7770739285714284</v>
@@ -12853,7 +12853,7 @@
         <v>0.8106330989119989</v>
       </c>
       <c r="I88" s="8" t="n">
-        <v>0.5684555847632055</v>
+        <v>0.5602589527640662</v>
       </c>
       <c r="J88" s="8" t="n">
         <v>0.03447085752486733</v>
@@ -12877,7 +12877,7 @@
         <v>0.01051798834852288</v>
       </c>
       <c r="Q88" s="8" t="n">
-        <v>0.6320799904845684</v>
+        <v>0.5709542939441643</v>
       </c>
       <c r="R88" s="8" t="n">
         <v>0.7981780357142857</v>
@@ -12982,7 +12982,7 @@
         <v>0.803663398507837</v>
       </c>
       <c r="I89" s="8" t="n">
-        <v>0.7002086849544603</v>
+        <v>0.6952891811909947</v>
       </c>
       <c r="J89" s="8" t="n">
         <v>0.02421404040403512</v>
@@ -13006,7 +13006,7 @@
         <v>0</v>
       </c>
       <c r="Q89" s="8" t="n">
-        <v>0.7092521131298584</v>
+        <v>0.667395581830474</v>
       </c>
       <c r="R89" s="8" t="n">
         <v>0.7946043749999999</v>
@@ -13111,7 +13111,7 @@
         <v>0.8046581135438252</v>
       </c>
       <c r="I90" s="8" t="n">
-        <v>0.7408928204866355</v>
+        <v>0.7367189199744395</v>
       </c>
       <c r="J90" s="8" t="n">
         <v>0.01673568471978871</v>
@@ -13135,7 +13135,7 @@
         <v>0.003205828779599271</v>
       </c>
       <c r="Q90" s="8" t="n">
-        <v>0.725264833834969</v>
+        <v>0.6883520483973673</v>
       </c>
       <c r="R90" s="8" t="n">
         <v>0.7902633035714286</v>
@@ -13240,7 +13240,7 @@
         <v>0.8105423666353707</v>
       </c>
       <c r="I91" s="8" t="n">
-        <v>0.6982492210256002</v>
+        <v>0.6932477068469824</v>
       </c>
       <c r="J91" s="8" t="n">
         <v>0.07898980487286597</v>
@@ -13264,7 +13264,7 @@
         <v>0.04705233202069463</v>
       </c>
       <c r="Q91" s="8" t="n">
-        <v>0.6955268547387148</v>
+        <v>0.6546121752193964</v>
       </c>
       <c r="R91" s="8" t="n">
         <v>0.7999282142857143</v>
@@ -13369,7 +13369,7 @@
         <v>0.7913140384685188</v>
       </c>
       <c r="I92" s="8" t="n">
-        <v>0.5993238874379559</v>
+        <v>0.5943061303318548</v>
       </c>
       <c r="J92" s="8" t="n">
         <v>0.06881769814511572</v>
@@ -13393,7 +13393,7 @@
         <v>0.004346528953832573</v>
       </c>
       <c r="Q92" s="8" t="n">
-        <v>0.5711655704417249</v>
+        <v>0.4979688829524154</v>
       </c>
       <c r="R92" s="8" t="n">
         <v>0.756064375</v>
@@ -13498,7 +13498,7 @@
         <v>0.7884249556013048</v>
       </c>
       <c r="I93" s="8" t="n">
-        <v>0.5185345614460228</v>
+        <v>0.5150621886614886</v>
       </c>
       <c r="J93" s="8" t="n">
         <v>0.07225782553606122</v>
@@ -13522,7 +13522,7 @@
         <v>0.01187895671141915</v>
       </c>
       <c r="Q93" s="8" t="n">
-        <v>0.5103166693386231</v>
+        <v>0.4125629866365502</v>
       </c>
       <c r="R93" s="8" t="n">
         <v>0.7651364285714285</v>
@@ -13627,7 +13627,7 @@
         <v>0.7873291286096589</v>
       </c>
       <c r="I94" s="8" t="n">
-        <v>0.5663211442984184</v>
+        <v>0.5640846943846688</v>
       </c>
       <c r="J94" s="8" t="n">
         <v>0.0356630230072891</v>
@@ -13651,7 +13651,7 @@
         <v>0.002005830196930449</v>
       </c>
       <c r="Q94" s="8" t="n">
-        <v>0.5030373428227701</v>
+        <v>0.4170880930353669</v>
       </c>
       <c r="R94" s="8" t="n">
         <v>0.7685273214285714</v>
@@ -13756,7 +13756,7 @@
         <v>0.7832234042565666</v>
       </c>
       <c r="I95" s="8" t="n">
-        <v>0.6895741051856792</v>
+        <v>0.6847420464299229</v>
       </c>
       <c r="J95" s="8" t="n">
         <v>0.04658806644957037</v>
@@ -13780,7 +13780,7 @@
         <v>0.009057872841522173</v>
       </c>
       <c r="Q95" s="8" t="n">
-        <v>0.6888923561263408</v>
+        <v>0.6285586857172731</v>
       </c>
       <c r="R95" s="8" t="n">
         <v>0.7746989285714285</v>
@@ -13885,7 +13885,7 @@
         <v>0.7922220908051374</v>
       </c>
       <c r="I96" s="8" t="n">
-        <v>0.5862258748943201</v>
+        <v>0.5803723886802834</v>
       </c>
       <c r="J96" s="8" t="n">
         <v>0.05252575701830051</v>
@@ -13909,7 +13909,7 @@
         <v>0.00783933982805028</v>
       </c>
       <c r="Q96" s="8" t="n">
-        <v>0.5707753292145937</v>
+        <v>0.5034845014659326</v>
       </c>
       <c r="R96" s="8" t="n">
         <v>0.7835608928571428</v>
@@ -14014,7 +14014,7 @@
         <v>0.796141646300728</v>
       </c>
       <c r="I97" s="8" t="n">
-        <v>0.6150654894136304</v>
+        <v>0.6112323305772208</v>
       </c>
       <c r="J97" s="8" t="n">
         <v>0.04464076836848481</v>
@@ -14038,7 +14038,7 @@
         <v>0.004938775527889998</v>
       </c>
       <c r="Q97" s="8" t="n">
-        <v>0.5437123847894159</v>
+        <v>0.4539036546041266</v>
       </c>
       <c r="R97" s="8" t="n">
         <v>0.7697315178571429</v>
@@ -14143,7 +14143,7 @@
         <v>0.8272180332345072</v>
       </c>
       <c r="I98" s="8" t="n">
-        <v>0.5949036822379344</v>
+        <v>0.5889533106472011</v>
       </c>
       <c r="J98" s="8" t="n">
         <v>0.05030686032832345</v>
@@ -14167,7 +14167,7 @@
         <v>0.0235360447337475</v>
       </c>
       <c r="Q98" s="8" t="n">
-        <v>0.5484644964076669</v>
+        <v>0.4652508991689386</v>
       </c>
       <c r="R98" s="8" t="n">
         <v>0.82203375</v>
@@ -14272,7 +14272,7 @@
         <v>0.8064133775776777</v>
       </c>
       <c r="I99" s="8" t="n">
-        <v>0.5800253088735051</v>
+        <v>0.5719299121751972</v>
       </c>
       <c r="J99" s="8" t="n">
         <v>0.1056089939928795</v>
@@ -14296,7 +14296,7 @@
         <v>0.004185099239260983</v>
       </c>
       <c r="Q99" s="8" t="n">
-        <v>0.4938663680458654</v>
+        <v>0.3968265052373111</v>
       </c>
       <c r="R99" s="8" t="n">
         <v>0.7913397023809523</v>
@@ -14401,7 +14401,7 @@
         <v>0.8145197186777343</v>
       </c>
       <c r="I100" s="8" t="n">
-        <v>0.5853122591517572</v>
+        <v>0.5773320658680059</v>
       </c>
       <c r="J100" s="8" t="n">
         <v>0.09422304282910703</v>
@@ -14425,7 +14425,7 @@
         <v>0.005153953726167027</v>
       </c>
       <c r="Q100" s="8" t="n">
-        <v>0.5521193272144596</v>
+        <v>0.4624659199647722</v>
       </c>
       <c r="R100" s="8" t="n">
         <v>0.8027660714285714</v>
@@ -14530,7 +14530,7 @@
         <v>0.7908159922393697</v>
       </c>
       <c r="I101" s="8" t="n">
-        <v>0.5082567267441747</v>
+        <v>0.503068403699383</v>
       </c>
       <c r="J101" s="8" t="n">
         <v>0.1051287433732711</v>
@@ -14554,7 +14554,7 @@
         <v>0.009835261746204632</v>
       </c>
       <c r="Q101" s="8" t="n">
-        <v>0.4292289425708912</v>
+        <v>0.3287950115104782</v>
       </c>
       <c r="R101" s="8" t="n">
         <v>0.7772100892857142</v>
@@ -14659,7 +14659,7 @@
         <v>0.7899532193281963</v>
       </c>
       <c r="I102" s="8" t="n">
-        <v>0.5750246529512633</v>
+        <v>0.567969606728427</v>
       </c>
       <c r="J102" s="8" t="n">
         <v>0.1027769077788714</v>
@@ -14683,7 +14683,7 @@
         <v>0.0008597666435595623</v>
       </c>
       <c r="Q102" s="8" t="n">
-        <v>0.5198915083123615</v>
+        <v>0.4284426937124575</v>
       </c>
       <c r="R102" s="8" t="n">
         <v>0.7768711607142859</v>
@@ -14788,7 +14788,7 @@
         <v>0.7376588440969273</v>
       </c>
       <c r="I103" s="8" t="n">
-        <v>0.54365288482358</v>
+        <v>0.5397442951361536</v>
       </c>
       <c r="J103" s="8" t="n">
         <v>0.01299659297343494</v>
@@ -14812,7 +14812,7 @@
         <v>0</v>
       </c>
       <c r="Q103" s="8" t="n">
-        <v>0.4680999514817301</v>
+        <v>0.390182907902474</v>
       </c>
       <c r="R103" s="8" t="n">
         <v>0.7201712202380952</v>
@@ -14917,7 +14917,7 @@
         <v>0.791807165847632</v>
       </c>
       <c r="I104" s="8" t="n">
-        <v>0.5673561681285686</v>
+        <v>0.5632271026289793</v>
       </c>
       <c r="J104" s="8" t="n">
         <v>0.09069539980713533</v>
@@ -14941,7 +14941,7 @@
         <v>0.0107147797138582</v>
       </c>
       <c r="Q104" s="8" t="n">
-        <v>0.546112032423967</v>
+        <v>0.4670102151573765</v>
       </c>
       <c r="R104" s="8" t="n">
         <v>0.7857435714285713</v>
@@ -15046,7 +15046,7 @@
         <v>0.8201432974494925</v>
       </c>
       <c r="I105" s="8" t="n">
-        <v>0.6054694578155752</v>
+        <v>0.5981863880276997</v>
       </c>
       <c r="J105" s="8" t="n">
         <v>0.06866350503487051</v>
@@ -15070,7 +15070,7 @@
         <v>0.002100471123189525</v>
       </c>
       <c r="Q105" s="8" t="n">
-        <v>0.5590391686929693</v>
+        <v>0.475561901153004</v>
       </c>
       <c r="R105" s="8" t="n">
         <v>0.8042450446428572</v>
@@ -15175,7 +15175,7 @@
         <v>0.7758488368172084</v>
       </c>
       <c r="I106" s="8" t="n">
-        <v>0.6121925306661499</v>
+        <v>0.6053526859111931</v>
       </c>
       <c r="J106" s="8" t="n">
         <v>0.04773875821542305</v>
@@ -15199,7 +15199,7 @@
         <v>0.002157155307886705</v>
       </c>
       <c r="Q106" s="8" t="n">
-        <v>0.6334658850121725</v>
+        <v>0.5830484433068477</v>
       </c>
       <c r="R106" s="8" t="n">
         <v>0.7622648214285714</v>
@@ -15304,7 +15304,7 @@
         <v>0.8075600778529262</v>
       </c>
       <c r="I107" s="8" t="n">
-        <v>0.5323498569079788</v>
+        <v>0.5256584255999878</v>
       </c>
       <c r="J107" s="8" t="n">
         <v>0.09147738344544838</v>
@@ -15328,7 +15328,7 @@
         <v>0.0006264237235896394</v>
       </c>
       <c r="Q107" s="8" t="n">
-        <v>0.4652641476420201</v>
+        <v>0.3777800852395025</v>
       </c>
       <c r="R107" s="8" t="n">
         <v>0.7979550297619049</v>
@@ -15433,7 +15433,7 @@
         <v>0.8064458686254461</v>
       </c>
       <c r="I108" s="8" t="n">
-        <v>0.5585069519468181</v>
+        <v>0.5528276308520148</v>
       </c>
       <c r="J108" s="8" t="n">
         <v>0.0489526004258443</v>
@@ -15457,7 +15457,7 @@
         <v>0.0009210119423720949</v>
       </c>
       <c r="Q108" s="8" t="n">
-        <v>0.5378335611025574</v>
+        <v>0.4603710803138943</v>
       </c>
       <c r="R108" s="8" t="n">
         <v>0.7933055059523808</v>
@@ -15562,7 +15562,7 @@
         <v>0.8132740505898612</v>
       </c>
       <c r="I109" s="8" t="n">
-        <v>0.5757570484183548</v>
+        <v>0.5691833106954396</v>
       </c>
       <c r="J109" s="8" t="n">
         <v>0.06216292660899509</v>
@@ -15586,7 +15586,7 @@
         <v>0.00441079375783126</v>
       </c>
       <c r="Q109" s="8" t="n">
-        <v>0.5297453124614345</v>
+        <v>0.4438946597560713</v>
       </c>
       <c r="R109" s="8" t="n">
         <v>0.8011478571428571</v>
@@ -15691,7 +15691,7 @@
         <v>0.790197762237091</v>
       </c>
       <c r="I110" s="8" t="n">
-        <v>0.5456345996743013</v>
+        <v>0.5390644862111262</v>
       </c>
       <c r="J110" s="8" t="n">
         <v>0.04821944607378605</v>
@@ -15715,7 +15715,7 @@
         <v>0.009721472862650215</v>
       </c>
       <c r="Q110" s="8" t="n">
-        <v>0.4871568039244125</v>
+        <v>0.3970263426498428</v>
       </c>
       <c r="R110" s="8" t="n">
         <v>0.772021875</v>
@@ -15820,7 +15820,7 @@
         <v>0.8046501413357232</v>
       </c>
       <c r="I111" s="8" t="n">
-        <v>0.6112165328693099</v>
+        <v>0.6047748006908256</v>
       </c>
       <c r="J111" s="8" t="n">
         <v>0.0572013575007786</v>
@@ -15844,7 +15844,7 @@
         <v>0.02232552765104305</v>
       </c>
       <c r="Q111" s="8" t="n">
-        <v>0.5929603069150258</v>
+        <v>0.5222914052570951</v>
       </c>
       <c r="R111" s="8" t="n">
         <v>0.7939096726190475</v>
@@ -15949,7 +15949,7 @@
         <v>0.8066032267923132</v>
       </c>
       <c r="I112" s="8" t="n">
-        <v>0.6395105117342578</v>
+        <v>0.6331398681587377</v>
       </c>
       <c r="J112" s="8" t="n">
         <v>0.02685396836061098</v>
@@ -15973,7 +15973,7 @@
         <v>0.01841050694868746</v>
       </c>
       <c r="Q112" s="8" t="n">
-        <v>0.6845401499525878</v>
+        <v>0.6386002149718198</v>
       </c>
       <c r="R112" s="8" t="n">
         <v>0.7954307142857143</v>
@@ -16078,7 +16078,7 @@
         <v>0.8062879595623446</v>
       </c>
       <c r="I113" s="8" t="n">
-        <v>0.7131169088222323</v>
+        <v>0.7084186026708059</v>
       </c>
       <c r="J113" s="8" t="n">
         <v>0.03997984333222994</v>
@@ -16102,7 +16102,7 @@
         <v>0.01675272026676463</v>
       </c>
       <c r="Q113" s="8" t="n">
-        <v>0.7100146005678475</v>
+        <v>0.6701199351490792</v>
       </c>
       <c r="R113" s="8" t="n">
         <v>0.7949319642857142</v>
@@ -16207,7 +16207,7 @@
         <v>0.7890227075598272</v>
       </c>
       <c r="I114" s="8" t="n">
-        <v>0.5613931977274651</v>
+        <v>0.5578176711260033</v>
       </c>
       <c r="J114" s="8" t="n">
         <v>0.05891284889615536</v>
@@ -16231,7 +16231,7 @@
         <v>0.006077105287394056</v>
       </c>
       <c r="Q114" s="8" t="n">
-        <v>0.5281731942010394</v>
+        <v>0.4425399875414441</v>
       </c>
       <c r="R114" s="8" t="n">
         <v>0.7632427083333333</v>
@@ -16336,7 +16336,7 @@
         <v>0.7905290471208108</v>
       </c>
       <c r="I115" s="8" t="n">
-        <v>0.6302884898312097</v>
+        <v>0.6254489218958088</v>
       </c>
       <c r="J115" s="8" t="n">
         <v>0.04791819727878524</v>
@@ -16360,7 +16360,7 @@
         <v>0.007278662732487485</v>
       </c>
       <c r="Q115" s="8" t="n">
-        <v>0.6011266900434499</v>
+        <v>0.5286489472624439</v>
       </c>
       <c r="R115" s="8" t="n">
         <v>0.7759971130952381</v>
@@ -16465,7 +16465,7 @@
         <v>0.8272180332345072</v>
       </c>
       <c r="I116" s="8" t="n">
-        <v>0.5949036822379344</v>
+        <v>0.5889533106472011</v>
       </c>
       <c r="J116" s="8" t="n">
         <v>0.05030686032832345</v>
@@ -16489,7 +16489,7 @@
         <v>0.0235360447337475</v>
       </c>
       <c r="Q116" s="8" t="n">
-        <v>0.5484644964076669</v>
+        <v>0.4652508991689386</v>
       </c>
       <c r="R116" s="8" t="n">
         <v>0.82203375</v>
@@ -16594,7 +16594,7 @@
         <v>0.7942797564971539</v>
       </c>
       <c r="I117" s="8" t="n">
-        <v>0.6314807448949575</v>
+        <v>0.6272606776470103</v>
       </c>
       <c r="J117" s="8" t="n">
         <v>0.04443066148812647</v>
@@ -16618,7 +16618,7 @@
         <v>0.1398602752408019</v>
       </c>
       <c r="Q117" s="8" t="n">
-        <v>0.5475988619400174</v>
+        <v>0.5381655348058438</v>
       </c>
       <c r="R117" s="8" t="n">
         <v>0.7177010714285714</v>
@@ -16719,7 +16719,7 @@
         <v>0.8959222235892376</v>
       </c>
       <c r="I118" s="8" t="n">
-        <v>0.9075190850547454</v>
+        <v>0.9072263749536278</v>
       </c>
       <c r="J118" s="8" t="n">
         <v>0.9318939126764294</v>
@@ -16743,7 +16743,7 @@
         <v>0.7644024037205064</v>
       </c>
       <c r="Q118" s="8" t="n">
-        <v>0.8867592616151539</v>
+        <v>0.874055963534469</v>
       </c>
       <c r="R118" s="6" t="n"/>
       <c r="S118" s="8" t="n">
@@ -16842,7 +16842,7 @@
         <v>0.7518137490894196</v>
       </c>
       <c r="I119" s="8" t="n">
-        <v>0.5847105954805879</v>
+        <v>0.5796082572876943</v>
       </c>
       <c r="J119" s="8" t="n">
         <v>0.7919109055339778</v>
@@ -16866,7 +16866,7 @@
         <v>0.7470589120291248</v>
       </c>
       <c r="Q119" s="8" t="n">
-        <v>0.5585332577704186</v>
+        <v>0.5516984836214431</v>
       </c>
       <c r="R119" s="6" t="n"/>
       <c r="S119" s="8" t="n">
@@ -16965,7 +16965,7 @@
         <v>0.7278893057443788</v>
       </c>
       <c r="I120" s="8" t="n">
-        <v>0.6644575734341185</v>
+        <v>0.6677820824148514</v>
       </c>
       <c r="J120" s="8" t="n">
         <v>0.8391426828670993</v>
@@ -16989,7 +16989,7 @@
         <v>0.6980045409074486</v>
       </c>
       <c r="Q120" s="8" t="n">
-        <v>0.6604127798323016</v>
+        <v>0.6613864009759849</v>
       </c>
       <c r="R120" s="8" t="n">
         <v>0.7176579241249404</v>
@@ -17048,7 +17048,7 @@
         <v>0.8000126874428909</v>
       </c>
       <c r="I121" s="8" t="n">
-        <v>0.6405764633983241</v>
+        <v>0.6371922644869658</v>
       </c>
       <c r="J121" s="8" t="n">
         <v>0.04114019762908028</v>
@@ -17072,7 +17072,7 @@
         <v>0.1313456954621252</v>
       </c>
       <c r="Q121" s="8" t="n">
-        <v>0.5487726055177905</v>
+        <v>0.5263511819312418</v>
       </c>
       <c r="R121" s="8" t="n">
         <v>0.7468196618020178</v>
@@ -17131,7 +17131,7 @@
         <v>0.6530288763623192</v>
       </c>
       <c r="I122" s="8" t="n">
-        <v>0.5180928464399907</v>
+        <v>0.5182029344304583</v>
       </c>
       <c r="J122" s="8" t="n">
         <v>0.04205368567186192</v>
@@ -17155,7 +17155,7 @@
         <v>0.1086457129404901</v>
       </c>
       <c r="Q122" s="8" t="n">
-        <v>0.504931977553852</v>
+        <v>0.4919834277126756</v>
       </c>
       <c r="R122" s="8" t="n">
         <v>0.6201914443389586</v>
@@ -17466,7 +17466,7 @@
         <v>0.04990835509347659</v>
       </c>
       <c r="I2" s="8" t="n">
-        <v>0.2427233325695092</v>
+        <v>0.24136929465429</v>
       </c>
       <c r="J2" s="8" t="n">
         <v>0.1651016494551747</v>
@@ -17490,7 +17490,7 @@
         <v>0.0709732763447761</v>
       </c>
       <c r="Q2" s="8" t="n">
-        <v>0.2332291973151244</v>
+        <v>0.2460999366314558</v>
       </c>
       <c r="R2" s="8" t="n">
         <v>0.05640403176265536</v>
@@ -17549,7 +17549,7 @@
         <v>0.03787865062446977</v>
       </c>
       <c r="I3" s="8" t="n">
-        <v>0.2209863051879042</v>
+        <v>0.2204962706434024</v>
       </c>
       <c r="J3" s="8" t="n">
         <v>0.1424883539034489</v>
@@ -17573,7 +17573,7 @@
         <v>0.07197367573025126</v>
       </c>
       <c r="Q3" s="8" t="n">
-        <v>0.2071602258702863</v>
+        <v>0.2169603093781073</v>
       </c>
       <c r="R3" s="8" t="n">
         <v>0.04600058907506197</v>
@@ -17632,7 +17632,7 @@
         <v>0.03270724644567177</v>
       </c>
       <c r="I4" s="8" t="n">
-        <v>0.1037181068554084</v>
+        <v>0.1060207538537816</v>
       </c>
       <c r="J4" s="8" t="n">
         <v>0.1428727426375395</v>
@@ -17656,7 +17656,7 @@
         <v>0.1013381596248</v>
       </c>
       <c r="Q4" s="8" t="n">
-        <v>0.08355291655227695</v>
+        <v>0.09666432912867864</v>
       </c>
       <c r="R4" s="8" t="n">
         <v>0.03901692424007801</v>
@@ -17715,7 +17715,7 @@
         <v>0.02921878153357475</v>
       </c>
       <c r="I5" s="8" t="n">
-        <v>0.07074855497417852</v>
+        <v>0.07212168399207612</v>
       </c>
       <c r="J5" s="8" t="n">
         <v>0.1382120159800949</v>
@@ -17739,7 +17739,7 @@
         <v>0.08923233913392366</v>
       </c>
       <c r="Q5" s="8" t="n">
-        <v>0.07406612325827884</v>
+        <v>0.08536470766048453</v>
       </c>
       <c r="R5" s="8" t="n">
         <v>0.03071704269738726</v>
@@ -17798,7 +17798,7 @@
         <v>0.01017122568936063</v>
       </c>
       <c r="I6" s="8" t="n">
-        <v>0.03635244832729571</v>
+        <v>0.03704999167372648</v>
       </c>
       <c r="J6" s="8" t="n">
         <v>0.009826179527486413</v>
@@ -17822,7 +17822,7 @@
         <v>0.08921825214677805</v>
       </c>
       <c r="Q6" s="8" t="n">
-        <v>0.02717356291433685</v>
+        <v>0.03567018510264893</v>
       </c>
       <c r="R6" s="8" t="n">
         <v>0.01348060686559685</v>
@@ -17881,7 +17881,7 @@
         <v>0.05019439810717106</v>
       </c>
       <c r="I7" s="8" t="n">
-        <v>0.19094899418235</v>
+        <v>0.1913933135265935</v>
       </c>
       <c r="J7" s="8" t="n">
         <v>0.07129821365583239</v>
@@ -17905,7 +17905,7 @@
         <v>0</v>
       </c>
       <c r="Q7" s="8" t="n">
-        <v>0.1894253904685528</v>
+        <v>0.2082773684437784</v>
       </c>
       <c r="R7" s="8" t="n">
         <v>0.07918026640218072</v>
@@ -17964,7 +17964,7 @@
         <v>0.08750836152879489</v>
       </c>
       <c r="I8" s="8" t="n">
-        <v>0.1771769293363595</v>
+        <v>0.1730206358745413</v>
       </c>
       <c r="J8" s="8" t="n">
         <v>0.1261365489182314</v>
@@ -17988,7 +17988,7 @@
         <v>0.02932493871661401</v>
       </c>
       <c r="Q8" s="8" t="n">
-        <v>0.1243123227383536</v>
+        <v>0.0857517240130158</v>
       </c>
       <c r="R8" s="8" t="n">
         <v>0.1228886487593337</v>
@@ -18047,7 +18047,7 @@
         <v>0.001316080698040322</v>
       </c>
       <c r="I9" s="8" t="n">
-        <v>0.03622725364791872</v>
+        <v>0.03692136700313368</v>
       </c>
       <c r="J9" s="8" t="n">
         <v>0.02942409780641992</v>
@@ -18071,7 +18071,7 @@
         <v>0.01254243495847271</v>
       </c>
       <c r="Q9" s="8" t="n">
-        <v>0.02396516851626257</v>
+        <v>0.03137843675197816</v>
       </c>
       <c r="R9" s="8" t="n">
         <v>0.0001903112899296294</v>
@@ -18130,7 +18130,7 @@
         <v>0.02074739682719436</v>
       </c>
       <c r="I10" s="8" t="n">
-        <v>0.1078938997349513</v>
+        <v>0.1081111241397304</v>
       </c>
       <c r="J10" s="8" t="n">
         <v>0.01873375769351653</v>
@@ -18154,7 +18154,7 @@
         <v>0</v>
       </c>
       <c r="Q10" s="8" t="n">
-        <v>0.06083497977557103</v>
+        <v>0.0699428043188345</v>
       </c>
       <c r="R10" s="8" t="n">
         <v>0.02401876890006331</v>
@@ -18213,7 +18213,7 @@
         <v>0.02148516919149653</v>
       </c>
       <c r="I11" s="8" t="n">
-        <v>0.04984245151953304</v>
+        <v>0.05088313876259357</v>
       </c>
       <c r="J11" s="8" t="n">
         <v>0.09822628866148429</v>
@@ -18237,7 +18237,7 @@
         <v>0.08773010347233899</v>
       </c>
       <c r="Q11" s="8" t="n">
-        <v>0.05793081217300923</v>
+        <v>0.07010036017584804</v>
       </c>
       <c r="R11" s="8" t="n">
         <v>0.02673243633751243</v>
@@ -18296,7 +18296,7 @@
         <v>0.01295495543057854</v>
       </c>
       <c r="I12" s="8" t="n">
-        <v>0.03573661397699182</v>
+        <v>0.03639094162994746</v>
       </c>
       <c r="J12" s="8" t="n">
         <v>0.05992100751523671</v>
@@ -18320,7 +18320,7 @@
         <v>0.06673042951276378</v>
       </c>
       <c r="Q12" s="8" t="n">
-        <v>0.03184945978664993</v>
+        <v>0.03975462505861868</v>
       </c>
       <c r="R12" s="8" t="n">
         <v>0.0170107322757607</v>
@@ -18379,7 +18379,7 @@
         <v>0.05141590429144721</v>
       </c>
       <c r="I13" s="8" t="n">
-        <v>0.4161957310460271</v>
+        <v>0.4173072917956677</v>
       </c>
       <c r="J13" s="8" t="n">
         <v>0.1268372213542156</v>
@@ -18403,7 +18403,7 @@
         <v>0.07137064832054631</v>
       </c>
       <c r="Q13" s="8" t="n">
-        <v>0.3310854967884796</v>
+        <v>0.3510668317749883</v>
       </c>
       <c r="R13" s="8" t="n">
         <v>0.06749110469574181</v>
@@ -18462,7 +18462,7 @@
         <v>0.04463283601463012</v>
       </c>
       <c r="I14" s="8" t="n">
-        <v>0.1207455496064723</v>
+        <v>0.1231664922688636</v>
       </c>
       <c r="J14" s="8" t="n">
         <v>0.08704903818095842</v>
@@ -18486,7 +18486,7 @@
         <v>0</v>
       </c>
       <c r="Q14" s="8" t="n">
-        <v>0.1013806913264369</v>
+        <v>0.1124581609994154</v>
       </c>
       <c r="R14" s="8" t="n">
         <v>0.04545599371948712</v>
@@ -18545,7 +18545,7 @@
         <v>0.07268796640461568</v>
       </c>
       <c r="I15" s="8" t="n">
-        <v>0.1830228734728463</v>
+        <v>0.1808815717062796</v>
       </c>
       <c r="J15" s="8" t="n">
         <v>0.1809874726982358</v>
@@ -18569,7 +18569,7 @@
         <v>0</v>
       </c>
       <c r="Q15" s="8" t="n">
-        <v>0.1630897043041842</v>
+        <v>0.170300032454485</v>
       </c>
       <c r="R15" s="8" t="n">
         <v>0.09244996661387721</v>
@@ -18628,7 +18628,7 @@
         <v>0.01106011474104511</v>
       </c>
       <c r="I16" s="8" t="n">
-        <v>0.2713784868079943</v>
+        <v>0.2721597051901665</v>
       </c>
       <c r="J16" s="8" t="n">
         <v>0.1738394467213027</v>
@@ -18652,7 +18652,7 @@
         <v>0.005678504434148568</v>
       </c>
       <c r="Q16" s="8" t="n">
-        <v>0.2611540899725091</v>
+        <v>0.2824977734969971</v>
       </c>
       <c r="R16" s="8" t="n">
         <v>0.02052185228376969</v>
@@ -18711,7 +18711,7 @@
         <v>0.005046630595348217</v>
       </c>
       <c r="I17" s="8" t="n">
-        <v>0.01732175507424382</v>
+        <v>0.01699148218724016</v>
       </c>
       <c r="J17" s="8" t="n">
         <v>0.02572295054136519</v>
@@ -18735,7 +18735,7 @@
         <v>0.02932493871661401</v>
       </c>
       <c r="Q17" s="8" t="n">
-        <v>0.01060528985870329</v>
+        <v>0.009936248410755275</v>
       </c>
       <c r="R17" s="8" t="n">
         <v>0.009441907273083297</v>
@@ -18794,7 +18794,7 @@
         <v>0.02665485317133601</v>
       </c>
       <c r="I18" s="8" t="n">
-        <v>0.1052661141388323</v>
+        <v>0.1050548512414114</v>
       </c>
       <c r="J18" s="8" t="n">
         <v>0.09186095665367737</v>
@@ -18818,7 +18818,7 @@
         <v>0.01417324815447297</v>
       </c>
       <c r="Q18" s="8" t="n">
-        <v>0.08146257279823317</v>
+        <v>0.09280852511763914</v>
       </c>
       <c r="R18" s="8" t="n">
         <v>0.04498377948776254</v>
@@ -18877,7 +18877,7 @@
         <v>0.128574666717113</v>
       </c>
       <c r="I19" s="8" t="n">
-        <v>0.4012050353400018</v>
+        <v>0.4031873184956425</v>
       </c>
       <c r="J19" s="8" t="n">
         <v>0.07872791790070818</v>
@@ -18901,7 +18901,7 @@
         <v>0.07999941972372833</v>
       </c>
       <c r="Q19" s="8" t="n">
-        <v>0.3168015301025539</v>
+        <v>0.3429633750095832</v>
       </c>
       <c r="R19" s="8" t="n">
         <v>0.13102174890476</v>
@@ -18960,7 +18960,7 @@
         <v>0.1737341768366931</v>
       </c>
       <c r="I20" s="8" t="n">
-        <v>0.2140635556721475</v>
+        <v>0.2139116207584647</v>
       </c>
       <c r="J20" s="8" t="n">
         <v>0.05681954725147566</v>
@@ -18984,7 +18984,7 @@
         <v>0</v>
       </c>
       <c r="Q20" s="8" t="n">
-        <v>0.1811455285071652</v>
+        <v>0.195908631495451</v>
       </c>
       <c r="R20" s="8" t="n">
         <v>0.143690298395415</v>
@@ -19043,7 +19043,7 @@
         <v>0.2551468687751897</v>
       </c>
       <c r="I21" s="8" t="n">
-        <v>0.3348582458036402</v>
+        <v>0.3361616363594365</v>
       </c>
       <c r="J21" s="8" t="n">
         <v>0.1043025261658386</v>
@@ -19067,7 +19067,7 @@
         <v>0</v>
       </c>
       <c r="Q21" s="8" t="n">
-        <v>0.3293345073346421</v>
+        <v>0.3526660031202123</v>
       </c>
       <c r="R21" s="8" t="n">
         <v>0.2337341575407921</v>
@@ -19126,7 +19126,7 @@
         <v>0.1527000406319095</v>
       </c>
       <c r="I22" s="8" t="n">
-        <v>0.2373686141024862</v>
+        <v>0.2393569065976253</v>
       </c>
       <c r="J22" s="8" t="n">
         <v>0.077734843336107</v>
@@ -19150,7 +19150,7 @@
         <v>0</v>
       </c>
       <c r="Q22" s="8" t="n">
-        <v>0.150585905940483</v>
+        <v>0.1590628686966813</v>
       </c>
       <c r="R22" s="8" t="n">
         <v>0.1687623578762665</v>
@@ -19209,7 +19209,7 @@
         <v>0.4064940957627569</v>
       </c>
       <c r="I23" s="8" t="n">
-        <v>0.3988061099890042</v>
+        <v>0.4019091117602966</v>
       </c>
       <c r="J23" s="8" t="n">
         <v>0.03594305860838964</v>
@@ -19233,7 +19233,7 @@
         <v>0</v>
       </c>
       <c r="Q23" s="8" t="n">
-        <v>0.3239034205593344</v>
+        <v>0.2803754429485701</v>
       </c>
       <c r="R23" s="8" t="n">
         <v>0.5450162011103236</v>
@@ -19292,7 +19292,7 @@
         <v>0.2478024711115418</v>
       </c>
       <c r="I24" s="8" t="n">
-        <v>0.3303110176163324</v>
+        <v>0.3359661193368092</v>
       </c>
       <c r="J24" s="8" t="n">
         <v>0.04844213820828983</v>
@@ -19316,7 +19316,7 @@
         <v>0</v>
       </c>
       <c r="Q24" s="8" t="n">
-        <v>0.2434504003983851</v>
+        <v>0.1933801447506609</v>
       </c>
       <c r="R24" s="8" t="n">
         <v>0.3288531980547284</v>
@@ -19375,7 +19375,7 @@
         <v>0.2912611321393012</v>
       </c>
       <c r="I25" s="8" t="n">
-        <v>0.3913769914381739</v>
+        <v>0.397634632979066</v>
       </c>
       <c r="J25" s="8" t="n">
         <v>0.0484347349419855</v>
@@ -19399,7 +19399,7 @@
         <v>0.01794613539247173</v>
       </c>
       <c r="Q25" s="8" t="n">
-        <v>0.2816442542601107</v>
+        <v>0.2414942029380952</v>
       </c>
       <c r="R25" s="8" t="n">
         <v>0.4121073691108227</v>
@@ -19458,7 +19458,7 @@
         <v>0.2672992768802246</v>
       </c>
       <c r="I26" s="8" t="n">
-        <v>0.3827728376253692</v>
+        <v>0.3871739006246203</v>
       </c>
       <c r="J26" s="8" t="n">
         <v>0.0220911899152893</v>
@@ -19482,7 +19482,7 @@
         <v>0.0004044630404463041</v>
       </c>
       <c r="Q26" s="8" t="n">
-        <v>0.323388955830003</v>
+        <v>0.2733545191098649</v>
       </c>
       <c r="R26" s="8" t="n">
         <v>0.4395080072723732</v>
@@ -19541,7 +19541,7 @@
         <v>0.2414432012101415</v>
       </c>
       <c r="I27" s="8" t="n">
-        <v>0.2316157486709178</v>
+        <v>0.2316080672289343</v>
       </c>
       <c r="J27" s="8" t="n">
         <v>0.009113091279341816</v>
@@ -19565,7 +19565,7 @@
         <v>0.0001646090534979424</v>
       </c>
       <c r="Q27" s="8" t="n">
-        <v>0.1801847289685821</v>
+        <v>0.1591853479284831</v>
       </c>
       <c r="R27" s="8" t="n">
         <v>0.4262694931026397</v>
@@ -19624,7 +19624,7 @@
         <v>0.1452291184931687</v>
       </c>
       <c r="I28" s="8" t="n">
-        <v>0.1931567908323373</v>
+        <v>0.1953713882295706</v>
       </c>
       <c r="J28" s="8" t="n">
         <v>0.004465679379268371</v>
@@ -19648,7 +19648,7 @@
         <v>0.001625741606523437</v>
       </c>
       <c r="Q28" s="8" t="n">
-        <v>0.1474423248197728</v>
+        <v>0.1193574520040558</v>
       </c>
       <c r="R28" s="8" t="n">
         <v>0.2430981535448466</v>
@@ -19707,7 +19707,7 @@
         <v>0.310587291077087</v>
       </c>
       <c r="I29" s="8" t="n">
-        <v>0.2673364253158227</v>
+        <v>0.2702287678936688</v>
       </c>
       <c r="J29" s="8" t="n">
         <v>0.01683613604313608</v>
@@ -19731,7 +19731,7 @@
         <v>0.001156773211567732</v>
       </c>
       <c r="Q29" s="8" t="n">
-        <v>0.2064514789912766</v>
+        <v>0.1731502375633484</v>
       </c>
       <c r="R29" s="8" t="n">
         <v>0.4560672383962358</v>
@@ -19790,7 +19790,7 @@
         <v>0.2648811013739815</v>
       </c>
       <c r="I30" s="8" t="n">
-        <v>0.2568979248504974</v>
+        <v>0.2604290300746948</v>
       </c>
       <c r="J30" s="8" t="n">
         <v>0.01732126855323074</v>
@@ -19814,7 +19814,7 @@
         <v>0.002332903290762867</v>
       </c>
       <c r="Q30" s="8" t="n">
-        <v>0.2209094556682897</v>
+        <v>0.1928732304211329</v>
       </c>
       <c r="R30" s="8" t="n">
         <v>0.3709805765991042</v>
@@ -19873,7 +19873,7 @@
         <v>0.2197397758979647</v>
       </c>
       <c r="I31" s="8" t="n">
-        <v>0.2094307367903695</v>
+        <v>0.2110856886308391</v>
       </c>
       <c r="J31" s="8" t="n">
         <v>0.07951387950247187</v>
@@ -19897,7 +19897,7 @@
         <v>0.004108212878657149</v>
       </c>
       <c r="Q31" s="8" t="n">
-        <v>0.2049153625861969</v>
+        <v>0.1886691086555711</v>
       </c>
       <c r="R31" s="8" t="n">
         <v>0.3520206903826635</v>
@@ -19956,7 +19956,7 @@
         <v>0.2530687198206366</v>
       </c>
       <c r="I32" s="8" t="n">
-        <v>0.2923840955012662</v>
+        <v>0.2933727419834508</v>
       </c>
       <c r="J32" s="8" t="n">
         <v>0.05229227776853289</v>
@@ -19980,7 +19980,7 @@
         <v>0</v>
       </c>
       <c r="Q32" s="8" t="n">
-        <v>0.2301782171279712</v>
+        <v>0.189296838193556</v>
       </c>
       <c r="R32" s="8" t="n">
         <v>0.3506877289542197</v>
@@ -20039,7 +20039,7 @@
         <v>0.34138241112302</v>
       </c>
       <c r="I33" s="8" t="n">
-        <v>0.423010619993301</v>
+        <v>0.4224242208433239</v>
       </c>
       <c r="J33" s="8" t="n">
         <v>0.04936621022852018</v>
@@ -20063,7 +20063,7 @@
         <v>0.001942075181661878</v>
       </c>
       <c r="Q33" s="8" t="n">
-        <v>0.3432790732354124</v>
+        <v>0.3042929468167084</v>
       </c>
       <c r="R33" s="8" t="n">
         <v>0.5190155778179397</v>
@@ -20122,7 +20122,7 @@
         <v>0.01842174154664755</v>
       </c>
       <c r="I34" s="8" t="n">
-        <v>0.09334407969796711</v>
+        <v>0.09144471070057257</v>
       </c>
       <c r="J34" s="8" t="n">
         <v>0.1513787888145696</v>
@@ -20146,7 +20146,7 @@
         <v>0.01333451884052067</v>
       </c>
       <c r="Q34" s="8" t="n">
-        <v>0.09589274352297467</v>
+        <v>0.1111699367874674</v>
       </c>
       <c r="R34" s="6" t="n"/>
       <c r="S34" s="8" t="n">
@@ -20245,7 +20245,7 @@
         <v>0.04786964704533366</v>
       </c>
       <c r="I35" s="8" t="n">
-        <v>0.1564274650232345</v>
+        <v>0.1559686526825609</v>
       </c>
       <c r="J35" s="8" t="n">
         <v>0.1589090590543649</v>
@@ -20269,7 +20269,7 @@
         <v>0</v>
       </c>
       <c r="Q35" s="8" t="n">
-        <v>0.1701348169069124</v>
+        <v>0.1818312005496534</v>
       </c>
       <c r="R35" s="6" t="n"/>
       <c r="S35" s="8" t="n">
@@ -20368,7 +20368,7 @@
         <v>0.03112887941629719</v>
       </c>
       <c r="I36" s="8" t="n">
-        <v>0.1032208824479481</v>
+        <v>0.1033247019995105</v>
       </c>
       <c r="J36" s="8" t="n">
         <v>0.1341812105567238</v>
@@ -20392,7 +20392,7 @@
         <v>0.0003448567904400223</v>
       </c>
       <c r="Q36" s="8" t="n">
-        <v>0.1136319957486328</v>
+        <v>0.1303624852224081</v>
       </c>
       <c r="R36" s="6" t="n"/>
       <c r="S36" s="8" t="n">
@@ -20491,7 +20491,7 @@
         <v>0.01845152839401328</v>
       </c>
       <c r="I37" s="8" t="n">
-        <v>0.1306848528078417</v>
+        <v>0.1324319422141483</v>
       </c>
       <c r="J37" s="8" t="n">
         <v>0.2342053322874795</v>
@@ -20515,7 +20515,7 @@
         <v>0.007749310717632068</v>
       </c>
       <c r="Q37" s="8" t="n">
-        <v>0.1080398468155174</v>
+        <v>0.1149557581026122</v>
       </c>
       <c r="R37" s="8" t="n">
         <v>0.03214785714285714</v>
@@ -20616,7 +20616,7 @@
         <v>0.0182451555469381</v>
       </c>
       <c r="I38" s="8" t="n">
-        <v>0.1091317518782346</v>
+        <v>0.1113210851593966</v>
       </c>
       <c r="J38" s="8" t="n">
         <v>0.413179679135879</v>
@@ -20640,7 +20640,7 @@
         <v>0.009981442488040754</v>
       </c>
       <c r="Q38" s="8" t="n">
-        <v>0.07805608953996468</v>
+        <v>0.09115644762687625</v>
       </c>
       <c r="R38" s="8" t="n">
         <v>0.03075642857142857</v>
@@ -20741,7 +20741,7 @@
         <v>0.01403329892869401</v>
       </c>
       <c r="I39" s="8" t="n">
-        <v>0.1288269278900438</v>
+        <v>0.1302822898955446</v>
       </c>
       <c r="J39" s="8" t="n">
         <v>0.4262648608862458</v>
@@ -20765,7 +20765,7 @@
         <v>0.06274333316126468</v>
       </c>
       <c r="Q39" s="8" t="n">
-        <v>0.114461224738829</v>
+        <v>0.1222598192787672</v>
       </c>
       <c r="R39" s="8" t="n">
         <v>0.02746133928571429</v>
@@ -20866,7 +20866,7 @@
         <v>0.02558850755644561</v>
       </c>
       <c r="I40" s="8" t="n">
-        <v>0.117767501372957</v>
+        <v>0.1196881135409138</v>
       </c>
       <c r="J40" s="8" t="n">
         <v>0.3933022435942183</v>
@@ -20890,7 +20890,7 @@
         <v>0.05150781195910271</v>
       </c>
       <c r="Q40" s="8" t="n">
-        <v>0.09197073970839405</v>
+        <v>0.09999660627433024</v>
       </c>
       <c r="R40" s="8" t="n">
         <v>0.04716875</v>
@@ -20991,7 +20991,7 @@
         <v>0.0181008396478935</v>
       </c>
       <c r="I41" s="8" t="n">
-        <v>0.08982237079140991</v>
+        <v>0.09164882205114815</v>
       </c>
       <c r="J41" s="8" t="n">
         <v>0.2436402656886979</v>
@@ -21015,7 +21015,7 @@
         <v>0.04497107931463769</v>
       </c>
       <c r="Q41" s="8" t="n">
-        <v>0.07169384230142054</v>
+        <v>0.08504356641736491</v>
       </c>
       <c r="R41" s="8" t="n">
         <v>0.03538526785714286</v>
@@ -21116,7 +21116,7 @@
         <v>0.02711559306085194</v>
       </c>
       <c r="I42" s="8" t="n">
-        <v>0.09580494106207904</v>
+        <v>0.09663428352966259</v>
       </c>
       <c r="J42" s="8" t="n">
         <v>0.1663610594413445</v>
@@ -21140,7 +21140,7 @@
         <v>0.02559130851092319</v>
       </c>
       <c r="Q42" s="8" t="n">
-        <v>0.09212832809918219</v>
+        <v>0.09277163802095381</v>
       </c>
       <c r="R42" s="8" t="n">
         <v>0.04539160714285715</v>
@@ -21241,7 +21241,7 @@
         <v>0.02139892112145408</v>
       </c>
       <c r="I43" s="8" t="n">
-        <v>0.08731508710921061</v>
+        <v>0.08767589098690091</v>
       </c>
       <c r="J43" s="8" t="n">
         <v>0.3804205531612806</v>
@@ -21265,7 +21265,7 @@
         <v>0.02137197164193866</v>
       </c>
       <c r="Q43" s="8" t="n">
-        <v>0.09223841089207903</v>
+        <v>0.1067895807898979</v>
       </c>
       <c r="R43" s="8" t="n">
         <v>0.04201946428571428</v>
@@ -21366,7 +21366,7 @@
         <v>0.02271971239782343</v>
       </c>
       <c r="I44" s="8" t="n">
-        <v>0.122366293501314</v>
+        <v>0.1228969521290504</v>
       </c>
       <c r="J44" s="8" t="n">
         <v>0.3711013138210016</v>
@@ -21390,7 +21390,7 @@
         <v>0.02165754531912849</v>
       </c>
       <c r="Q44" s="8" t="n">
-        <v>0.1123400688590837</v>
+        <v>0.1168712908663267</v>
       </c>
       <c r="R44" s="8" t="n">
         <v>0.03886874999999999</v>
@@ -21491,7 +21491,7 @@
         <v>0.01758716536031955</v>
       </c>
       <c r="I45" s="8" t="n">
-        <v>0.1092727419624312</v>
+        <v>0.1111384920199814</v>
       </c>
       <c r="J45" s="8" t="n">
         <v>0.3049244854286929</v>
@@ -21515,7 +21515,7 @@
         <v>0.06753596915184713</v>
       </c>
       <c r="Q45" s="8" t="n">
-        <v>0.09425368018224151</v>
+        <v>0.1027798906023725</v>
       </c>
       <c r="R45" s="8" t="n">
         <v>0.03292741071428572</v>
@@ -21616,7 +21616,7 @@
         <v>0.01026191310323485</v>
       </c>
       <c r="I46" s="8" t="n">
-        <v>0.08315612435059583</v>
+        <v>0.08399893050909193</v>
       </c>
       <c r="J46" s="8" t="n">
         <v>0.133876213446277</v>
@@ -21640,7 +21640,7 @@
         <v>0.06538168362159279</v>
       </c>
       <c r="Q46" s="8" t="n">
-        <v>0.07602570670862663</v>
+        <v>0.09306895252064445</v>
       </c>
       <c r="R46" s="8" t="n">
         <v>0.01855383928571428</v>
@@ -21741,7 +21741,7 @@
         <v>0.01888841721176742</v>
       </c>
       <c r="I47" s="8" t="n">
-        <v>0.08344712928956513</v>
+        <v>0.08226990108688684</v>
       </c>
       <c r="J47" s="8" t="n">
         <v>0.3562578517545224</v>
@@ -21765,7 +21765,7 @@
         <v>0.02554224901965693</v>
       </c>
       <c r="Q47" s="8" t="n">
-        <v>0.1135347764828273</v>
+        <v>0.1132883678444851</v>
       </c>
       <c r="R47" s="8" t="n">
         <v>0.03835616071428571</v>
@@ -21870,7 +21870,7 @@
         <v>0.6197173601653201</v>
       </c>
       <c r="I48" s="8" t="n">
-        <v>0.5257919479494384</v>
+        <v>0.5213558379683675</v>
       </c>
       <c r="J48" s="8" t="n">
         <v>0.03814628712866924</v>
@@ -21894,7 +21894,7 @@
         <v>0</v>
       </c>
       <c r="Q48" s="8" t="n">
-        <v>0.4665786667771793</v>
+        <v>0.3830490235757729</v>
       </c>
       <c r="R48" s="8" t="n">
         <v>0.7890352678571428</v>
@@ -21999,7 +21999,7 @@
         <v>0.6002185494499358</v>
       </c>
       <c r="I49" s="8" t="n">
-        <v>0.5443678363492598</v>
+        <v>0.5395090908485649</v>
       </c>
       <c r="J49" s="8" t="n">
         <v>0.06997777480853154</v>
@@ -22023,7 +22023,7 @@
         <v>0.00298989898989899</v>
       </c>
       <c r="Q49" s="8" t="n">
-        <v>0.4576714873000537</v>
+        <v>0.368651490847189</v>
       </c>
       <c r="R49" s="8" t="n">
         <v>0.7737891964285714</v>
@@ -22128,7 +22128,7 @@
         <v>0.6374421007654032</v>
       </c>
       <c r="I50" s="8" t="n">
-        <v>0.5224140340841601</v>
+        <v>0.516477849488116</v>
       </c>
       <c r="J50" s="8" t="n">
         <v>0.05523945210392189</v>
@@ -22152,7 +22152,7 @@
         <v>0.002639962835193143</v>
       </c>
       <c r="Q50" s="8" t="n">
-        <v>0.4513336329174328</v>
+        <v>0.3657195754860508</v>
       </c>
       <c r="R50" s="8" t="n">
         <v>0.7751773214285714</v>
@@ -22257,7 +22257,7 @@
         <v>0.6724439249547898</v>
       </c>
       <c r="I51" s="8" t="n">
-        <v>0.5386905021926737</v>
+        <v>0.5323175066485779</v>
       </c>
       <c r="J51" s="8" t="n">
         <v>0.08304653199713989</v>
@@ -22281,7 +22281,7 @@
         <v>0.001225614035087719</v>
       </c>
       <c r="Q51" s="8" t="n">
-        <v>0.5178629148820885</v>
+        <v>0.4365180596777994</v>
       </c>
       <c r="R51" s="8" t="n">
         <v>0.8118577678571428</v>
@@ -22386,7 +22386,7 @@
         <v>0.6083079638318868</v>
       </c>
       <c r="I52" s="8" t="n">
-        <v>0.5237262060924728</v>
+        <v>0.5172076996391266</v>
       </c>
       <c r="J52" s="8" t="n">
         <v>0.03503009711368322</v>
@@ -22410,7 +22410,7 @@
         <v>6.725514922236234e-05</v>
       </c>
       <c r="Q52" s="8" t="n">
-        <v>0.525644671376663</v>
+        <v>0.4525082191305842</v>
       </c>
       <c r="R52" s="8" t="n">
         <v>0.7708155357142858</v>
@@ -22515,7 +22515,7 @@
         <v>0.6590549302007008</v>
       </c>
       <c r="I53" s="8" t="n">
-        <v>0.5278049210059517</v>
+        <v>0.5216548296566563</v>
       </c>
       <c r="J53" s="8" t="n">
         <v>0.05730261073141978</v>
@@ -22539,7 +22539,7 @@
         <v>0.002897193983276043</v>
       </c>
       <c r="Q53" s="8" t="n">
-        <v>0.4959459212522103</v>
+        <v>0.4109981047211311</v>
       </c>
       <c r="R53" s="8" t="n">
         <v>0.8125394642857142</v>
@@ -22644,7 +22644,7 @@
         <v>0.5236347485651374</v>
       </c>
       <c r="I54" s="8" t="n">
-        <v>0.4026072262486021</v>
+        <v>0.4016368473978551</v>
       </c>
       <c r="J54" s="8" t="n">
         <v>0.04122808895577496</v>
@@ -22668,7 +22668,7 @@
         <v>0.003141874681609781</v>
       </c>
       <c r="Q54" s="8" t="n">
-        <v>0.3586309905547922</v>
+        <v>0.2846099707623837</v>
       </c>
       <c r="R54" s="8" t="n">
         <v>0.7263484821428571</v>
@@ -22773,7 +22773,7 @@
         <v>0.5439814412123791</v>
       </c>
       <c r="I55" s="8" t="n">
-        <v>0.435694378191531</v>
+        <v>0.4347412858748115</v>
       </c>
       <c r="J55" s="8" t="n">
         <v>0.03866330050028153</v>
@@ -22797,7 +22797,7 @@
         <v>0</v>
       </c>
       <c r="Q55" s="8" t="n">
-        <v>0.3614484592713509</v>
+        <v>0.275906524772198</v>
       </c>
       <c r="R55" s="8" t="n">
         <v>0.7278560714285714</v>
@@ -22902,7 +22902,7 @@
         <v>0.5279541919224681</v>
       </c>
       <c r="I56" s="8" t="n">
-        <v>0.422463146526208</v>
+        <v>0.4207851015273573</v>
       </c>
       <c r="J56" s="8" t="n">
         <v>0.05316942114803517</v>
@@ -22926,7 +22926,7 @@
         <v>0.008757287154434837</v>
       </c>
       <c r="Q56" s="8" t="n">
-        <v>0.3536143266705437</v>
+        <v>0.2713577705006411</v>
       </c>
       <c r="R56" s="8" t="n">
         <v>0.7221323214285713</v>
@@ -23031,7 +23031,7 @@
         <v>0.5370176402736818</v>
       </c>
       <c r="I57" s="8" t="n">
-        <v>0.470198804442655</v>
+        <v>0.4662635052990857</v>
       </c>
       <c r="J57" s="8" t="n">
         <v>0.05939694174303201</v>
@@ -23055,7 +23055,7 @@
         <v>0</v>
       </c>
       <c r="Q57" s="8" t="n">
-        <v>0.4322274142691078</v>
+        <v>0.3458749832242501</v>
       </c>
       <c r="R57" s="8" t="n">
         <v>0.7326652678571429</v>
@@ -23160,7 +23160,7 @@
         <v>0.5226301295374867</v>
       </c>
       <c r="I58" s="8" t="n">
-        <v>0.4383413882681435</v>
+        <v>0.4341404549568945</v>
       </c>
       <c r="J58" s="8" t="n">
         <v>0.02742984247911467</v>
@@ -23184,7 +23184,7 @@
         <v>0</v>
       </c>
       <c r="Q58" s="8" t="n">
-        <v>0.4236418026857169</v>
+        <v>0.3465055132392288</v>
       </c>
       <c r="R58" s="8" t="n">
         <v>0.7232839285714286</v>
@@ -23289,7 +23289,7 @@
         <v>0.5171681637018006</v>
       </c>
       <c r="I59" s="8" t="n">
-        <v>0.472627380935203</v>
+        <v>0.4686389725658145</v>
       </c>
       <c r="J59" s="8" t="n">
         <v>0.03981841303456089</v>
@@ -23313,7 +23313,7 @@
         <v>4.098360655737705e-05</v>
       </c>
       <c r="Q59" s="8" t="n">
-        <v>0.4454822674322583</v>
+        <v>0.3604713106556992</v>
       </c>
       <c r="R59" s="8" t="n">
         <v>0.7085040178571429</v>
@@ -23418,7 +23418,7 @@
         <v>0.3389525176159531</v>
       </c>
       <c r="I60" s="8" t="n">
-        <v>0.3927936640670453</v>
+        <v>0.3919676002153966</v>
       </c>
       <c r="J60" s="8" t="n">
         <v>0.006451209417647579</v>
@@ -23442,7 +23442,7 @@
         <v>0</v>
       </c>
       <c r="Q60" s="8" t="n">
-        <v>0.3652269204335081</v>
+        <v>0.3084042641831022</v>
       </c>
       <c r="R60" s="8" t="n">
         <v>0.4900364285714286</v>
@@ -23547,7 +23547,7 @@
         <v>0.4043900032061221</v>
       </c>
       <c r="I61" s="8" t="n">
-        <v>0.3920836525534895</v>
+        <v>0.3910912544881078</v>
       </c>
       <c r="J61" s="8" t="n">
         <v>0.002571102764566605</v>
@@ -23571,7 +23571,7 @@
         <v>0</v>
       </c>
       <c r="Q61" s="8" t="n">
-        <v>0.3496983966558048</v>
+        <v>0.2835449033802857</v>
       </c>
       <c r="R61" s="8" t="n">
         <v>0.5868183928571428</v>
@@ -23676,7 +23676,7 @@
         <v>0.4266875928711065</v>
       </c>
       <c r="I62" s="8" t="n">
-        <v>0.3498722510200865</v>
+        <v>0.3456597390782643</v>
       </c>
       <c r="J62" s="8" t="n">
         <v>0.002814735707153404</v>
@@ -23700,7 +23700,7 @@
         <v>0</v>
       </c>
       <c r="Q62" s="8" t="n">
-        <v>0.3079875074916305</v>
+        <v>0.2449129437844874</v>
       </c>
       <c r="R62" s="8" t="n">
         <v>0.6547046428571429</v>
@@ -23805,7 +23805,7 @@
         <v>0.4767609822168373</v>
       </c>
       <c r="I63" s="8" t="n">
-        <v>0.4451809009667058</v>
+        <v>0.4424768153188084</v>
       </c>
       <c r="J63" s="8" t="n">
         <v>0.05344987365679629</v>
@@ -23829,7 +23829,7 @@
         <v>0.0007405181778260567</v>
       </c>
       <c r="Q63" s="8" t="n">
-        <v>0.4503819415251462</v>
+        <v>0.3830834561771972</v>
       </c>
       <c r="R63" s="8" t="n">
         <v>0.6946808928571429</v>
@@ -23934,7 +23934,7 @@
         <v>0.5826925846900453</v>
       </c>
       <c r="I64" s="8" t="n">
-        <v>0.4523186143090938</v>
+        <v>0.4505763178649088</v>
       </c>
       <c r="J64" s="8" t="n">
         <v>0.01356986688462776</v>
@@ -23958,7 +23958,7 @@
         <v>0.005516783787507817</v>
       </c>
       <c r="Q64" s="8" t="n">
-        <v>0.4344756400583622</v>
+        <v>0.3618024375768054</v>
       </c>
       <c r="R64" s="8" t="n">
         <v>0.7836532142857143</v>
@@ -24063,7 +24063,7 @@
         <v>0.5720431079075262</v>
       </c>
       <c r="I65" s="8" t="n">
-        <v>0.5182942634312012</v>
+        <v>0.5137277929971071</v>
       </c>
       <c r="J65" s="8" t="n">
         <v>0.05780380216492152</v>
@@ -24087,7 +24087,7 @@
         <v>0</v>
       </c>
       <c r="Q65" s="8" t="n">
-        <v>0.4982537429008233</v>
+        <v>0.4250411556455678</v>
       </c>
       <c r="R65" s="8" t="n">
         <v>0.7877302678571428</v>
@@ -24192,7 +24192,7 @@
         <v>0.6608375357849547</v>
       </c>
       <c r="I66" s="8" t="n">
-        <v>0.5723006009116813</v>
+        <v>0.5684535925651359</v>
       </c>
       <c r="J66" s="8" t="n">
         <v>0.04792752474474962</v>
@@ -24216,7 +24216,7 @@
         <v>0</v>
       </c>
       <c r="Q66" s="8" t="n">
-        <v>0.5540444821071504</v>
+        <v>0.4837381246934497</v>
       </c>
       <c r="R66" s="8" t="n">
         <v>0.8117150000000001</v>
@@ -24321,7 +24321,7 @@
         <v>0.5789678416584275</v>
       </c>
       <c r="I67" s="8" t="n">
-        <v>0.5407490952905539</v>
+        <v>0.5365436591216205</v>
       </c>
       <c r="J67" s="8" t="n">
         <v>0.03969695005822606</v>
@@ -24345,7 +24345,7 @@
         <v>0.002381509789070211</v>
       </c>
       <c r="Q67" s="8" t="n">
-        <v>0.4856572239602343</v>
+        <v>0.4084582571991615</v>
       </c>
       <c r="R67" s="8" t="n">
         <v>0.7579207142857142</v>
@@ -24450,7 +24450,7 @@
         <v>0.4902261908581744</v>
       </c>
       <c r="I68" s="8" t="n">
-        <v>0.497782031401342</v>
+        <v>0.4946463058070371</v>
       </c>
       <c r="J68" s="8" t="n">
         <v>0.03096039876585259</v>
@@ -24474,7 +24474,7 @@
         <v>0.005899403239556692</v>
       </c>
       <c r="Q68" s="8" t="n">
-        <v>0.5085225173291152</v>
+        <v>0.4482430213942222</v>
       </c>
       <c r="R68" s="8" t="n">
         <v>0.6967322321428572</v>
@@ -24579,7 +24579,7 @@
         <v>0.5369900596018334</v>
       </c>
       <c r="I69" s="8" t="n">
-        <v>0.5032412552060779</v>
+        <v>0.4992580708562279</v>
       </c>
       <c r="J69" s="8" t="n">
         <v>0.0133592317046409</v>
@@ -24603,7 +24603,7 @@
         <v>0</v>
       </c>
       <c r="Q69" s="8" t="n">
-        <v>0.5520849601612042</v>
+        <v>0.4999074043067738</v>
       </c>
       <c r="R69" s="8" t="n">
         <v>0.7313498214285714</v>
@@ -24708,7 +24708,7 @@
         <v>0.5192417006097612</v>
       </c>
       <c r="I70" s="8" t="n">
-        <v>0.5005853783633906</v>
+        <v>0.4956462749131976</v>
       </c>
       <c r="J70" s="8" t="n">
         <v>0.02295844191511865</v>
@@ -24732,7 +24732,7 @@
         <v>0</v>
       </c>
       <c r="Q70" s="8" t="n">
-        <v>0.5461876019191665</v>
+        <v>0.4917345799521585</v>
       </c>
       <c r="R70" s="8" t="n">
         <v>0.7045620535714285</v>
@@ -24837,7 +24837,7 @@
         <v>0.6235462015816676</v>
       </c>
       <c r="I71" s="8" t="n">
-        <v>0.4568578159042599</v>
+        <v>0.4530436323529513</v>
       </c>
       <c r="J71" s="8" t="n">
         <v>0.05680238126016311</v>
@@ -24861,7 +24861,7 @@
         <v>0</v>
       </c>
       <c r="Q71" s="8" t="n">
-        <v>0.4268688224373637</v>
+        <v>0.3548384401180715</v>
       </c>
       <c r="R71" s="8" t="n">
         <v>0.792840625</v>
@@ -24966,7 +24966,7 @@
         <v>0.6075569724989673</v>
       </c>
       <c r="I72" s="8" t="n">
-        <v>0.4765719688845149</v>
+        <v>0.4732453444249429</v>
       </c>
       <c r="J72" s="8" t="n">
         <v>0.03918726272742715</v>
@@ -24990,7 +24990,7 @@
         <v>0</v>
       </c>
       <c r="Q72" s="8" t="n">
-        <v>0.4309887048409894</v>
+        <v>0.352802870765195</v>
       </c>
       <c r="R72" s="8" t="n">
         <v>0.7635611607142857</v>
@@ -25095,7 +25095,7 @@
         <v>0.6296657114739572</v>
       </c>
       <c r="I73" s="8" t="n">
-        <v>0.4445701606216719</v>
+        <v>0.4421022104041298</v>
       </c>
       <c r="J73" s="8" t="n">
         <v>0.04915004377870004</v>
@@ -25119,7 +25119,7 @@
         <v>5.727376861397481e-05</v>
       </c>
       <c r="Q73" s="8" t="n">
-        <v>0.3891267447835579</v>
+        <v>0.315042554014611</v>
       </c>
       <c r="R73" s="8" t="n">
         <v>0.7903000892857143</v>
@@ -25224,7 +25224,7 @@
         <v>0.593435905467765</v>
       </c>
       <c r="I74" s="8" t="n">
-        <v>0.4734892482122708</v>
+        <v>0.4688300900077827</v>
       </c>
       <c r="J74" s="8" t="n">
         <v>0.03883091879989484</v>
@@ -25248,7 +25248,7 @@
         <v>0</v>
       </c>
       <c r="Q74" s="8" t="n">
-        <v>0.4994572627398</v>
+        <v>0.4348292715902343</v>
       </c>
       <c r="R74" s="8" t="n">
         <v>0.7814742857142857</v>
@@ -25353,7 +25353,7 @@
         <v>0.5868028127951647</v>
       </c>
       <c r="I75" s="8" t="n">
-        <v>0.4604059844863801</v>
+        <v>0.4573218724701288</v>
       </c>
       <c r="J75" s="8" t="n">
         <v>0.02154984814928451</v>
@@ -25377,7 +25377,7 @@
         <v>0.0002403846153846154</v>
       </c>
       <c r="Q75" s="8" t="n">
-        <v>0.4677359321055795</v>
+        <v>0.4020687863859543</v>
       </c>
       <c r="R75" s="8" t="n">
         <v>0.7680964285714286</v>
@@ -25482,7 +25482,7 @@
         <v>0.6109908200449594</v>
       </c>
       <c r="I76" s="8" t="n">
-        <v>0.4757079211967147</v>
+        <v>0.4713207967547124</v>
       </c>
       <c r="J76" s="8" t="n">
         <v>0.01800865716726166</v>
@@ -25506,7 +25506,7 @@
         <v>0.0008211869679759588</v>
       </c>
       <c r="Q76" s="8" t="n">
-        <v>0.475097289328255</v>
+        <v>0.4047810489740315</v>
       </c>
       <c r="R76" s="8" t="n">
         <v>0.7635228571428571</v>
@@ -25611,7 +25611,7 @@
         <v>0.6606776918006348</v>
       </c>
       <c r="I77" s="8" t="n">
-        <v>0.5006710103343309</v>
+        <v>0.4971702104065557</v>
       </c>
       <c r="J77" s="8" t="n">
         <v>0.03272283334598512</v>
@@ -25635,7 +25635,7 @@
         <v>0.00659047619047619</v>
       </c>
       <c r="Q77" s="8" t="n">
-        <v>0.4822123334698492</v>
+        <v>0.4088115436965971</v>
       </c>
       <c r="R77" s="8" t="n">
         <v>0.8045805357142858</v>
@@ -25740,7 +25740,7 @@
         <v>0.6546601414291944</v>
       </c>
       <c r="I78" s="8" t="n">
-        <v>0.5067663957430275</v>
+        <v>0.4997934990745425</v>
       </c>
       <c r="J78" s="8" t="n">
         <v>0.02888194517756501</v>
@@ -25764,7 +25764,7 @@
         <v>0.003144654088050315</v>
       </c>
       <c r="Q78" s="8" t="n">
-        <v>0.468519682941403</v>
+        <v>0.3861147847281723</v>
       </c>
       <c r="R78" s="8" t="n">
         <v>0.8059149999999999</v>
@@ -25869,7 +25869,7 @@
         <v>0.6241902480082666</v>
       </c>
       <c r="I79" s="8" t="n">
-        <v>0.5239432433543644</v>
+        <v>0.5201754844615437</v>
       </c>
       <c r="J79" s="8" t="n">
         <v>0.04205953852549261</v>
@@ -25893,7 +25893,7 @@
         <v>0.001143056520772997</v>
       </c>
       <c r="Q79" s="8" t="n">
-        <v>0.4833785575120481</v>
+        <v>0.4087781765598041</v>
       </c>
       <c r="R79" s="8" t="n">
         <v>0.7819446428571428</v>
@@ -25998,7 +25998,7 @@
         <v>0.5248462863168825</v>
       </c>
       <c r="I80" s="8" t="n">
-        <v>0.4450355824887341</v>
+        <v>0.4418064489537664</v>
       </c>
       <c r="J80" s="8" t="n">
         <v>0.02896996161146349</v>
@@ -26022,7 +26022,7 @@
         <v>0.003870406610132637</v>
       </c>
       <c r="Q80" s="8" t="n">
-        <v>0.3999510909499557</v>
+        <v>0.3218468896338944</v>
       </c>
       <c r="R80" s="8" t="n">
         <v>0.7151841964285716</v>
@@ -26127,7 +26127,7 @@
         <v>0.5404857374730337</v>
       </c>
       <c r="I81" s="8" t="n">
-        <v>0.4985247886374723</v>
+        <v>0.4953105933671477</v>
       </c>
       <c r="J81" s="8" t="n">
         <v>0.02151644945960997</v>
@@ -26151,7 +26151,7 @@
         <v>0.004191616766467066</v>
       </c>
       <c r="Q81" s="8" t="n">
-        <v>0.461767493658939</v>
+        <v>0.4014572799787976</v>
       </c>
       <c r="R81" s="8" t="n">
         <v>0.729860892857143</v>
@@ -26256,7 +26256,7 @@
         <v>0.5009713496368294</v>
       </c>
       <c r="I82" s="8" t="n">
-        <v>0.4266873757550492</v>
+        <v>0.4263342781214726</v>
       </c>
       <c r="J82" s="8" t="n">
         <v>0.01655092757049011</v>
@@ -26280,7 +26280,7 @@
         <v>0.005957040035987404</v>
       </c>
       <c r="Q82" s="8" t="n">
-        <v>0.3871238251701459</v>
+        <v>0.3038738766580174</v>
       </c>
       <c r="R82" s="8" t="n">
         <v>0.6901176785714286</v>
@@ -26385,7 +26385,7 @@
         <v>0.5963757194017717</v>
       </c>
       <c r="I83" s="8" t="n">
-        <v>0.4221079787224675</v>
+        <v>0.4169736628314414</v>
       </c>
       <c r="J83" s="8" t="n">
         <v>0.011196303005708</v>
@@ -26409,7 +26409,7 @@
         <v>0</v>
       </c>
       <c r="Q83" s="8" t="n">
-        <v>0.4567436754292852</v>
+        <v>0.3971153067533936</v>
       </c>
       <c r="R83" s="8" t="n">
         <v>0.7729617857142858</v>
@@ -26514,7 +26514,7 @@
         <v>0.5878963639703786</v>
       </c>
       <c r="I84" s="8" t="n">
-        <v>0.5103461923527771</v>
+        <v>0.5042929148372023</v>
       </c>
       <c r="J84" s="8" t="n">
         <v>0.0201417088658098</v>
@@ -26538,7 +26538,7 @@
         <v>0.003582568994339973</v>
       </c>
       <c r="Q84" s="8" t="n">
-        <v>0.4912786950448985</v>
+        <v>0.4019716086383522</v>
       </c>
       <c r="R84" s="8" t="n">
         <v>0.7806161607142857</v>
@@ -26643,7 +26643,7 @@
         <v>0.5961814106645391</v>
       </c>
       <c r="I85" s="8" t="n">
-        <v>0.5362085993427325</v>
+        <v>0.530891486896274</v>
       </c>
       <c r="J85" s="8" t="n">
         <v>0.02302162840284278</v>
@@ -26667,7 +26667,7 @@
         <v>0.01195096047070307</v>
       </c>
       <c r="Q85" s="8" t="n">
-        <v>0.5519426018540587</v>
+        <v>0.4808512222482998</v>
       </c>
       <c r="R85" s="8" t="n">
         <v>0.7943291964285714</v>
@@ -26772,7 +26772,7 @@
         <v>0.6440861556698546</v>
       </c>
       <c r="I86" s="8" t="n">
-        <v>0.6002452420595892</v>
+        <v>0.5952632654468464</v>
       </c>
       <c r="J86" s="8" t="n">
         <v>0.01025614800548003</v>
@@ -26796,7 +26796,7 @@
         <v>0.0003973509933774834</v>
       </c>
       <c r="Q86" s="8" t="n">
-        <v>0.6296690165519913</v>
+        <v>0.5901055393896385</v>
       </c>
       <c r="R86" s="8" t="n">
         <v>0.8098241071428571</v>
@@ -26901,7 +26901,7 @@
         <v>0.5557218998273245</v>
       </c>
       <c r="I87" s="8" t="n">
-        <v>0.6472259636459003</v>
+        <v>0.6452536679093807</v>
       </c>
       <c r="J87" s="8" t="n">
         <v>0.01925679913841277</v>
@@ -26925,7 +26925,7 @@
         <v>0.02227071450468961</v>
       </c>
       <c r="Q87" s="8" t="n">
-        <v>0.67326318921692</v>
+        <v>0.6567766783583558</v>
       </c>
       <c r="R87" s="8" t="n">
         <v>0.7344976785714286</v>
@@ -27030,7 +27030,7 @@
         <v>0.6504053292605591</v>
       </c>
       <c r="I88" s="8" t="n">
-        <v>0.4936525685123727</v>
+        <v>0.4866275917379412</v>
       </c>
       <c r="J88" s="8" t="n">
         <v>0.01440524264475844</v>
@@ -27054,7 +27054,7 @@
         <v>0.002291779892303421</v>
       </c>
       <c r="Q88" s="8" t="n">
-        <v>0.567385975530041</v>
+        <v>0.5149477345546543</v>
       </c>
       <c r="R88" s="8" t="n">
         <v>0.8022863392857141</v>
@@ -27159,7 +27159,7 @@
         <v>0.5974438350040197</v>
       </c>
       <c r="I89" s="8" t="n">
-        <v>0.609654026599491</v>
+        <v>0.6065381296986974</v>
       </c>
       <c r="J89" s="8" t="n">
         <v>0.01082094093420772</v>
@@ -27183,7 +27183,7 @@
         <v>0</v>
       </c>
       <c r="Q89" s="8" t="n">
-        <v>0.6358590631543386</v>
+        <v>0.5923744093646952</v>
       </c>
       <c r="R89" s="8" t="n">
         <v>0.7812861607142858</v>
@@ -27288,7 +27288,7 @@
         <v>0.5801738586383113</v>
       </c>
       <c r="I90" s="8" t="n">
-        <v>0.6573781997854217</v>
+        <v>0.6555102889105536</v>
       </c>
       <c r="J90" s="8" t="n">
         <v>0.01017717543737723</v>
@@ -27312,7 +27312,7 @@
         <v>0.0002339181286549707</v>
       </c>
       <c r="Q90" s="8" t="n">
-        <v>0.629616566586475</v>
+        <v>0.595921596135317</v>
       </c>
       <c r="R90" s="8" t="n">
         <v>0.7520740178571429</v>
@@ -27417,7 +27417,7 @@
         <v>0.6067522664637803</v>
       </c>
       <c r="I91" s="8" t="n">
-        <v>0.5926722541190508</v>
+        <v>0.5892969979528555</v>
       </c>
       <c r="J91" s="8" t="n">
         <v>0.02846548692807865</v>
@@ -27441,7 +27441,7 @@
         <v>0.01572551269093842</v>
       </c>
       <c r="Q91" s="8" t="n">
-        <v>0.6244650137014877</v>
+        <v>0.5840148293978452</v>
       </c>
       <c r="R91" s="8" t="n">
         <v>0.7853808035714286</v>
@@ -27546,7 +27546,7 @@
         <v>0.5199335024237682</v>
       </c>
       <c r="I92" s="8" t="n">
-        <v>0.5391292513193598</v>
+        <v>0.5372381643288842</v>
       </c>
       <c r="J92" s="8" t="n">
         <v>0.0393246424171125</v>
@@ -27570,7 +27570,7 @@
         <v>0.001262145100672177</v>
       </c>
       <c r="Q92" s="8" t="n">
-        <v>0.4925968244819303</v>
+        <v>0.4307337116997502</v>
       </c>
       <c r="R92" s="8" t="n">
         <v>0.6756591071428572</v>
@@ -27675,7 +27675,7 @@
         <v>0.6028794333784946</v>
       </c>
       <c r="I93" s="8" t="n">
-        <v>0.4403522479887927</v>
+        <v>0.4364444454010342</v>
       </c>
       <c r="J93" s="8" t="n">
         <v>0.03991740305098244</v>
@@ -27699,7 +27699,7 @@
         <v>0.008157054828676843</v>
       </c>
       <c r="Q93" s="8" t="n">
-        <v>0.4421214858314675</v>
+        <v>0.354006050895644</v>
       </c>
       <c r="R93" s="8" t="n">
         <v>0.7467716964285714</v>
@@ -27804,7 +27804,7 @@
         <v>0.5302042121389221</v>
       </c>
       <c r="I94" s="8" t="n">
-        <v>0.5072708865275395</v>
+        <v>0.5070502451785444</v>
       </c>
       <c r="J94" s="8" t="n">
         <v>0.02652923604075203</v>
@@ -27828,7 +27828,7 @@
         <v>0.0007649217693644968</v>
       </c>
       <c r="Q94" s="8" t="n">
-        <v>0.4547862434734781</v>
+        <v>0.3917664782229266</v>
       </c>
       <c r="R94" s="8" t="n">
         <v>0.7143485714285714</v>
@@ -27933,7 +27933,7 @@
         <v>0.5301417312612735</v>
       </c>
       <c r="I95" s="8" t="n">
-        <v>0.5594490221199954</v>
+        <v>0.5553887362114691</v>
       </c>
       <c r="J95" s="8" t="n">
         <v>0.02107338490283438</v>
@@ -27957,7 +27957,7 @@
         <v>0.0006854302613467132</v>
       </c>
       <c r="Q95" s="8" t="n">
-        <v>0.5816290570186428</v>
+        <v>0.5129241309504774</v>
       </c>
       <c r="R95" s="8" t="n">
         <v>0.726355892857143</v>
@@ -28062,7 +28062,7 @@
         <v>0.5454926451933402</v>
       </c>
       <c r="I96" s="8" t="n">
-        <v>0.4350116283179945</v>
+        <v>0.4301829904639324</v>
       </c>
       <c r="J96" s="8" t="n">
         <v>0.01772269116182236</v>
@@ -28086,7 +28086,7 @@
         <v>0.0003540300984207143</v>
       </c>
       <c r="Q96" s="8" t="n">
-        <v>0.4298709829919716</v>
+        <v>0.3601238687640858</v>
       </c>
       <c r="R96" s="8" t="n">
         <v>0.7459971428571428</v>
@@ -28191,7 +28191,7 @@
         <v>0.4932165342775672</v>
       </c>
       <c r="I97" s="8" t="n">
-        <v>0.4925395755480188</v>
+        <v>0.4899665460427051</v>
       </c>
       <c r="J97" s="8" t="n">
         <v>0.02317597463932814</v>
@@ -28215,7 +28215,7 @@
         <v>0.0005420054200542005</v>
       </c>
       <c r="Q97" s="8" t="n">
-        <v>0.4433471396100877</v>
+        <v>0.3609095297032347</v>
       </c>
       <c r="R97" s="8" t="n">
         <v>0.6451945535714285</v>
@@ -28320,7 +28320,7 @@
         <v>0.6653365836374042</v>
       </c>
       <c r="I98" s="8" t="n">
-        <v>0.5397493255154182</v>
+        <v>0.5362202123419996</v>
       </c>
       <c r="J98" s="8" t="n">
         <v>0.03373129662156614</v>
@@ -28344,7 +28344,7 @@
         <v>0.01603154387530944</v>
       </c>
       <c r="Q98" s="8" t="n">
-        <v>0.5061311213293221</v>
+        <v>0.4300141499134637</v>
       </c>
       <c r="R98" s="8" t="n">
         <v>0.8266088392857142</v>
@@ -28449,7 +28449,7 @@
         <v>0.6191260034602195</v>
       </c>
       <c r="I99" s="8" t="n">
-        <v>0.5308579394609531</v>
+        <v>0.525780926101683</v>
       </c>
       <c r="J99" s="8" t="n">
         <v>0.05445450468037424</v>
@@ -28473,7 +28473,7 @@
         <v>0.001876620608364044</v>
       </c>
       <c r="Q99" s="8" t="n">
-        <v>0.4585279289982219</v>
+        <v>0.3724733633030042</v>
       </c>
       <c r="R99" s="8" t="n">
         <v>0.7793339285714286</v>
@@ -28578,7 +28578,7 @@
         <v>0.6466022729957926</v>
       </c>
       <c r="I100" s="8" t="n">
-        <v>0.5300738764303662</v>
+        <v>0.5237266786481203</v>
       </c>
       <c r="J100" s="8" t="n">
         <v>0.05845974661408098</v>
@@ -28602,7 +28602,7 @@
         <v>0.001396687722528708</v>
       </c>
       <c r="Q100" s="8" t="n">
-        <v>0.5131511691703207</v>
+        <v>0.4333414611765049</v>
       </c>
       <c r="R100" s="8" t="n">
         <v>0.798404255952381</v>
@@ -28707,7 +28707,7 @@
         <v>0.5318567938999947</v>
       </c>
       <c r="I101" s="8" t="n">
-        <v>0.4202549169887805</v>
+        <v>0.4190544116000081</v>
       </c>
       <c r="J101" s="8" t="n">
         <v>0.04435360353469722</v>
@@ -28731,7 +28731,7 @@
         <v>0.00396638727868154</v>
       </c>
       <c r="Q101" s="8" t="n">
-        <v>0.3578979254988957</v>
+        <v>0.277291422011741</v>
       </c>
       <c r="R101" s="8" t="n">
         <v>0.725445625</v>
@@ -28836,7 +28836,7 @@
         <v>0.5256053111709897</v>
       </c>
       <c r="I102" s="8" t="n">
-        <v>0.460389191215334</v>
+        <v>0.4563476442739319</v>
       </c>
       <c r="J102" s="8" t="n">
         <v>0.04221506575223585</v>
@@ -28860,7 +28860,7 @@
         <v>1.366120218579235e-05</v>
       </c>
       <c r="Q102" s="8" t="n">
-        <v>0.4337838281290278</v>
+        <v>0.3509506023730594</v>
       </c>
       <c r="R102" s="8" t="n">
         <v>0.7214844047619048</v>
@@ -28965,7 +28965,7 @@
         <v>0.3900100378977273</v>
       </c>
       <c r="I103" s="8" t="n">
-        <v>0.3782498558802071</v>
+        <v>0.3762395312605895</v>
       </c>
       <c r="J103" s="8" t="n">
         <v>0.003945682629789195</v>
@@ -28989,7 +28989,7 @@
         <v>0</v>
       </c>
       <c r="Q103" s="8" t="n">
-        <v>0.3409709415269812</v>
+        <v>0.2789540371159585</v>
       </c>
       <c r="R103" s="8" t="n">
         <v>0.5771864880952381</v>
@@ -29094,7 +29094,7 @@
         <v>0.5438322249381361</v>
       </c>
       <c r="I104" s="8" t="n">
-        <v>0.4719312595690004</v>
+        <v>0.4689269753936083</v>
       </c>
       <c r="J104" s="8" t="n">
         <v>0.04160784756878184</v>
@@ -29118,7 +29118,7 @@
         <v>0.002085767321777958</v>
       </c>
       <c r="Q104" s="8" t="n">
-        <v>0.4610371081614437</v>
+        <v>0.3899756831331901</v>
       </c>
       <c r="R104" s="8" t="n">
         <v>0.7553547916666667</v>
@@ -29223,7 +29223,7 @@
         <v>0.6199026887216913</v>
       </c>
       <c r="I105" s="8" t="n">
-        <v>0.5565248481011178</v>
+        <v>0.5524986258433784</v>
       </c>
       <c r="J105" s="8" t="n">
         <v>0.04381223740148785</v>
@@ -29247,7 +29247,7 @@
         <v>0.001190754894535105</v>
       </c>
       <c r="Q105" s="8" t="n">
-        <v>0.5198508530336924</v>
+        <v>0.4460981909463056</v>
       </c>
       <c r="R105" s="8" t="n">
         <v>0.7848178571428571</v>
@@ -29352,7 +29352,7 @@
         <v>0.515485983689923</v>
       </c>
       <c r="I106" s="8" t="n">
-        <v>0.5005362216569366</v>
+        <v>0.4965168838588207</v>
       </c>
       <c r="J106" s="8" t="n">
         <v>0.02242602412853738</v>
@@ -29376,7 +29376,7 @@
         <v>0.001966467746518897</v>
       </c>
       <c r="Q106" s="8" t="n">
-        <v>0.5355983598031623</v>
+        <v>0.4799616685510514</v>
       </c>
       <c r="R106" s="8" t="n">
         <v>0.710881369047619</v>
@@ -29481,7 +29481,7 @@
         <v>0.6202562951848641</v>
       </c>
       <c r="I107" s="8" t="n">
-        <v>0.4593333151368156</v>
+        <v>0.4561303957273414</v>
       </c>
       <c r="J107" s="8" t="n">
         <v>0.04837989592209675</v>
@@ -29505,7 +29505,7 @@
         <v>1.909125620465827e-05</v>
       </c>
       <c r="Q107" s="8" t="n">
-        <v>0.4156614240206369</v>
+        <v>0.3408946216326258</v>
       </c>
       <c r="R107" s="8" t="n">
         <v>0.7822339583333333</v>
@@ -29610,7 +29610,7 @@
         <v>0.5970765127692962</v>
       </c>
       <c r="I108" s="8" t="n">
-        <v>0.4698677179651217</v>
+        <v>0.4658242530775411</v>
       </c>
       <c r="J108" s="8" t="n">
         <v>0.02612980803881367</v>
@@ -29634,7 +29634,7 @@
         <v>0.0003538571944535247</v>
       </c>
       <c r="Q108" s="8" t="n">
-        <v>0.4807634947245448</v>
+        <v>0.4138930356500734</v>
       </c>
       <c r="R108" s="8" t="n">
         <v>0.7710311904761904</v>
@@ -29739,7 +29739,7 @@
         <v>0.646509360412699</v>
       </c>
       <c r="I109" s="8" t="n">
-        <v>0.5104602164772406</v>
+        <v>0.5057130646475471</v>
       </c>
       <c r="J109" s="8" t="n">
         <v>0.03455477234968091</v>
@@ -29763,7 +29763,7 @@
         <v>0.003626062266433168</v>
       </c>
       <c r="Q109" s="8" t="n">
-        <v>0.4780368579744335</v>
+        <v>0.4012348349948578</v>
       </c>
       <c r="R109" s="8" t="n">
         <v>0.7974800595238094</v>
@@ -29868,7 +29868,7 @@
         <v>0.5221011244755821</v>
       </c>
       <c r="I110" s="8" t="n">
-        <v>0.4567492489604185</v>
+        <v>0.4544837734807955</v>
       </c>
       <c r="J110" s="8" t="n">
         <v>0.02234577954718786</v>
@@ -29892,7 +29892,7 @@
         <v>0.004673021137529035</v>
       </c>
       <c r="Q110" s="8" t="n">
-        <v>0.41628080325968</v>
+        <v>0.3423926820902364</v>
       </c>
       <c r="R110" s="8" t="n">
         <v>0.7117209226190475</v>
@@ -29997,7 +29997,7 @@
         <v>0.5934844980122298</v>
       </c>
       <c r="I111" s="8" t="n">
-        <v>0.4895542568059926</v>
+        <v>0.4840526881883061</v>
       </c>
       <c r="J111" s="8" t="n">
         <v>0.01811988009145353</v>
@@ -30021,7 +30021,7 @@
         <v>0.005177843155014346</v>
       </c>
       <c r="Q111" s="8" t="n">
-        <v>0.4999883241094141</v>
+        <v>0.4266460458800153</v>
       </c>
       <c r="R111" s="8" t="n">
         <v>0.7826357142857142</v>
@@ -30126,7 +30126,7 @@
         <v>0.6167377949192462</v>
       </c>
       <c r="I112" s="8" t="n">
-        <v>0.5803745914059543</v>
+        <v>0.5757148416980563</v>
       </c>
       <c r="J112" s="8" t="n">
         <v>0.01463939659621708</v>
@@ -30150,7 +30150,7 @@
         <v>0.008319948463456836</v>
       </c>
       <c r="Q112" s="8" t="n">
-        <v>0.6234393937663174</v>
+        <v>0.5872766507675495</v>
       </c>
       <c r="R112" s="8" t="n">
         <v>0.7822027083333334</v>
@@ -30255,7 +30255,7 @@
         <v>0.5947899867020372</v>
       </c>
       <c r="I113" s="8" t="n">
-        <v>0.6199014935013213</v>
+        <v>0.6171151388540356</v>
       </c>
       <c r="J113" s="8" t="n">
         <v>0.01648786776655453</v>
@@ -30279,7 +30279,7 @@
         <v>0.005319810273197796</v>
       </c>
       <c r="Q113" s="8" t="n">
-        <v>0.629980214480767</v>
+        <v>0.590770278299286</v>
       </c>
       <c r="R113" s="8" t="n">
         <v>0.7729136607142857</v>
@@ -30384,7 +30384,7 @@
         <v>0.5510057159803949</v>
       </c>
       <c r="I114" s="8" t="n">
-        <v>0.4955841286118972</v>
+        <v>0.4935776183028208</v>
       </c>
       <c r="J114" s="8" t="n">
         <v>0.03525709383628232</v>
@@ -30408,7 +30408,7 @@
         <v>0.003394707232904506</v>
       </c>
       <c r="Q114" s="8" t="n">
-        <v>0.4631681845956252</v>
+        <v>0.3921687469394403</v>
       </c>
       <c r="R114" s="8" t="n">
         <v>0.7122597916666666</v>
@@ -30513,7 +30513,7 @@
         <v>0.5229503035773936</v>
       </c>
       <c r="I115" s="8" t="n">
-        <v>0.4956667419953364</v>
+        <v>0.4918460909060358</v>
       </c>
       <c r="J115" s="8" t="n">
         <v>0.02065735023466162</v>
@@ -30537,7 +30537,7 @@
         <v>0.0005271552599405427</v>
       </c>
       <c r="Q115" s="8" t="n">
-        <v>0.4849490598735675</v>
+        <v>0.4113191764725992</v>
       </c>
       <c r="R115" s="8" t="n">
         <v>0.7058491964285716</v>
@@ -30642,7 +30642,7 @@
         <v>0.6653365836374042</v>
       </c>
       <c r="I116" s="8" t="n">
-        <v>0.5397493255154182</v>
+        <v>0.5362202123419996</v>
       </c>
       <c r="J116" s="8" t="n">
         <v>0.03373129662156614</v>
@@ -30666,7 +30666,7 @@
         <v>0.01603154387530944</v>
       </c>
       <c r="Q116" s="8" t="n">
-        <v>0.5061311213293221</v>
+        <v>0.4300141499134637</v>
       </c>
       <c r="R116" s="8" t="n">
         <v>0.8266088392857142</v>
@@ -30771,7 +30771,7 @@
         <v>0.6658437771251146</v>
       </c>
       <c r="I117" s="8" t="n">
-        <v>0.423418165226334</v>
+        <v>0.4207750233154655</v>
       </c>
       <c r="J117" s="8" t="n">
         <v>0.01742580521381394</v>
@@ -30795,7 +30795,7 @@
         <v>0.07211563334234407</v>
       </c>
       <c r="Q117" s="8" t="n">
-        <v>0.3187338188237748</v>
+        <v>0.3009107129563851</v>
       </c>
       <c r="R117" s="8" t="n">
         <v>0.651818125</v>
@@ -30896,7 +30896,7 @@
         <v>0.8080168356062478</v>
       </c>
       <c r="I118" s="8" t="n">
-        <v>0.8793891228148867</v>
+        <v>0.8802074081081388</v>
       </c>
       <c r="J118" s="8" t="n">
         <v>0.7090859557747542</v>
@@ -30920,7 +30920,7 @@
         <v>0.415098076889466</v>
       </c>
       <c r="Q118" s="8" t="n">
-        <v>0.8756298748621116</v>
+        <v>0.8564423624558866</v>
       </c>
       <c r="R118" s="6" t="n"/>
       <c r="S118" s="8" t="n">
@@ -31019,7 +31019,7 @@
         <v>0.4459178538365407</v>
       </c>
       <c r="I119" s="8" t="n">
-        <v>0.3032167755822437</v>
+        <v>0.2979648438655986</v>
       </c>
       <c r="J119" s="8" t="n">
         <v>0.3878368322407665</v>
@@ -31043,7 +31043,7 @@
         <v>0.3134726693546021</v>
       </c>
       <c r="Q119" s="8" t="n">
-        <v>0.336069782832597</v>
+        <v>0.3446765896199573</v>
       </c>
       <c r="R119" s="6" t="n"/>
       <c r="S119" s="8" t="n">
@@ -31142,7 +31142,7 @@
         <v>0.3744844665358991</v>
       </c>
       <c r="I120" s="8" t="n">
-        <v>0.4232222906466782</v>
+        <v>0.4264624712664806</v>
       </c>
       <c r="J120" s="8" t="n">
         <v>0.4780274978301866</v>
@@ -31166,7 +31166,7 @@
         <v>0.275385979268835</v>
       </c>
       <c r="Q120" s="8" t="n">
-        <v>0.478616260868208</v>
+        <v>0.508117416747767</v>
       </c>
       <c r="R120" s="8" t="n">
         <v>0.603447373421729</v>
@@ -31225,7 +31225,7 @@
         <v>0.6834618958070257</v>
       </c>
       <c r="I121" s="8" t="n">
-        <v>0.5156953513591683</v>
+        <v>0.5112984064463347</v>
       </c>
       <c r="J121" s="8" t="n">
         <v>0.0226288083492714</v>
@@ -31249,7 +31249,7 @@
         <v>0.07101568626280524</v>
       </c>
       <c r="Q121" s="8" t="n">
-        <v>0.4361744324436219</v>
+        <v>0.3946953610388661</v>
       </c>
       <c r="R121" s="8" t="n">
         <v>0.7160723372166148</v>
@@ -31308,7 +31308,7 @@
         <v>0.3074975092103184</v>
       </c>
       <c r="I122" s="8" t="n">
-        <v>0.2578950820901456</v>
+        <v>0.2574391544539411</v>
       </c>
       <c r="J122" s="8" t="n">
         <v>0.02021812362832046</v>
@@ -31332,7 +31332,7 @@
         <v>0.03594300703015472</v>
       </c>
       <c r="Q122" s="8" t="n">
-        <v>0.3287917091126027</v>
+        <v>0.3328455532823235</v>
       </c>
       <c r="R122" s="8" t="n">
         <v>0.4753027554195719</v>
@@ -31515,7 +31515,7 @@
         </is>
       </c>
       <c r="G4" s="8" t="n">
-        <v>0.4860681114551084</v>
+        <v>0.4509803921568628</v>
       </c>
     </row>
     <row r="5">
@@ -31779,7 +31779,7 @@
         </is>
       </c>
       <c r="G12" s="8" t="n">
-        <v>0.3498452012383901</v>
+        <v>0.2796697626418989</v>
       </c>
     </row>
     <row r="13">
@@ -31845,7 +31845,7 @@
         </is>
       </c>
       <c r="G14" s="8" t="n">
-        <v>0.07120743034055728</v>
+        <v>0.05469556243550051</v>
       </c>
     </row>
     <row r="15">
@@ -32109,7 +32109,7 @@
         </is>
       </c>
       <c r="G22" s="8" t="n">
-        <v>-0.04024767801857585</v>
+        <v>-0.05882352941176471</v>
       </c>
     </row>
     <row r="23">
@@ -32142,7 +32142,7 @@
         </is>
       </c>
       <c r="G23" s="8" t="n">
-        <v>0.1393188854489164</v>
+        <v>0.09597523219814241</v>
       </c>
     </row>
     <row r="24">
@@ -32406,7 +32406,7 @@
         </is>
       </c>
       <c r="G31" s="8" t="n">
-        <v>0.03405572755417956</v>
+        <v>-0.01135190918472652</v>
       </c>
     </row>
     <row r="32">
@@ -32439,7 +32439,7 @@
         </is>
       </c>
       <c r="G32" s="8" t="n">
-        <v>-0.06914344685242518</v>
+        <v>-0.09184726522187822</v>
       </c>
     </row>
     <row r="33">
@@ -32472,7 +32472,7 @@
         </is>
       </c>
       <c r="G33" s="8" t="n">
-        <v>-0.09184726522187822</v>
+        <v>-0.1186790505675955</v>
       </c>
     </row>
     <row r="34">
@@ -32505,7 +32505,7 @@
         </is>
       </c>
       <c r="G34" s="8" t="n">
-        <v>-0.108359133126935</v>
+        <v>-0.1351909184726522</v>
       </c>
     </row>
     <row r="35">
@@ -32538,7 +32538,7 @@
         </is>
       </c>
       <c r="G35" s="8" t="n">
-        <v>-0.07739938080495357</v>
+        <v>-0.1104231166150671</v>
       </c>
     </row>
     <row r="36">
@@ -32571,7 +32571,7 @@
         </is>
       </c>
       <c r="G36" s="8" t="n">
-        <v>-0.0629514963880289</v>
+        <v>-0.08565531475748193</v>
       </c>
     </row>
     <row r="37">
@@ -32604,7 +32604,7 @@
         </is>
       </c>
       <c r="G37" s="8" t="n">
-        <v>0.08978328173374613</v>
+        <v>0.07739938080495357</v>
       </c>
     </row>
     <row r="38">
@@ -32637,7 +32637,7 @@
         </is>
       </c>
       <c r="G38" s="8" t="n">
-        <v>-0.5493356885321351</v>
+        <v>-0.5368743874690244</v>
       </c>
     </row>
     <row r="39">
@@ -32670,7 +32670,7 @@
         </is>
       </c>
       <c r="G39" s="8" t="n">
-        <v>0.9607843137254902</v>
+        <v>0.9484004127966976</v>
       </c>
     </row>
     <row r="40">
@@ -32901,7 +32901,7 @@
         </is>
       </c>
       <c r="G46" s="8" t="n">
-        <v>-0.1558307533539732</v>
+        <v>-0.1991744066047472</v>
       </c>
     </row>
     <row r="47">
@@ -33099,7 +33099,7 @@
         </is>
       </c>
       <c r="G52" s="8" t="n">
-        <v>-0.1847265221878225</v>
+        <v>-0.2260061919504644</v>
       </c>
     </row>
     <row r="53">
@@ -33264,7 +33264,7 @@
         </is>
       </c>
       <c r="G57" s="8" t="n">
-        <v>-0.2280701754385965</v>
+        <v>-0.2714138286893705</v>
       </c>
     </row>
     <row r="58">
@@ -33396,7 +33396,7 @@
         </is>
       </c>
       <c r="G61" s="8" t="n">
-        <v>-0.2156862745098039</v>
+        <v>-0.2714138286893705</v>
       </c>
     </row>
     <row r="62">
@@ -33495,7 +33495,7 @@
         </is>
       </c>
       <c r="G64" s="8" t="n">
-        <v>-0.1393188854489164</v>
+        <v>-0.1826625386996904</v>
       </c>
     </row>
     <row r="65">
@@ -33561,7 +33561,7 @@
         </is>
       </c>
       <c r="G66" s="8" t="n">
-        <v>0.04850361197110423</v>
+        <v>0.05675954592363261</v>
       </c>
     </row>
     <row r="67">
@@ -33594,7 +33594,7 @@
         </is>
       </c>
       <c r="G67" s="8" t="n">
-        <v>-0.5358359457137651</v>
+        <v>-0.5109133435875435</v>
       </c>
     </row>
     <row r="68">
@@ -33693,7 +33693,7 @@
         </is>
       </c>
       <c r="G70" s="8" t="n">
-        <v>0.4813186813186813</v>
+        <v>0.4505494505494506</v>
       </c>
     </row>
     <row r="71">
@@ -33957,7 +33957,7 @@
         </is>
       </c>
       <c r="G78" s="8" t="n">
-        <v>0.5560439560439561</v>
+        <v>0.4241758241758242</v>
       </c>
     </row>
     <row r="79">
@@ -34023,7 +34023,7 @@
         </is>
       </c>
       <c r="G80" s="8" t="n">
-        <v>0.3318681318681319</v>
+        <v>0.3406593406593407</v>
       </c>
     </row>
     <row r="81">
@@ -34287,7 +34287,7 @@
         </is>
       </c>
       <c r="G88" s="8" t="n">
-        <v>0.4197802197802198</v>
+        <v>0.4637362637362638</v>
       </c>
     </row>
     <row r="89">
@@ -34320,7 +34320,7 @@
         </is>
       </c>
       <c r="G89" s="8" t="n">
-        <v>0.03296703296703297</v>
+        <v>0.06373626373626373</v>
       </c>
     </row>
     <row r="90">
@@ -34584,7 +34584,7 @@
         </is>
       </c>
       <c r="G97" s="8" t="n">
-        <v>0.06373626373626373</v>
+        <v>-0.1384615384615385</v>
       </c>
     </row>
     <row r="98">
@@ -34617,7 +34617,7 @@
         </is>
       </c>
       <c r="G98" s="8" t="n">
-        <v>0.5428571428571428</v>
+        <v>0.5516483516483517</v>
       </c>
     </row>
     <row r="99">
@@ -34650,7 +34650,7 @@
         </is>
       </c>
       <c r="G99" s="8" t="n">
-        <v>0.4857142857142857</v>
+        <v>0.4813186813186813</v>
       </c>
     </row>
     <row r="100">
@@ -34683,7 +34683,7 @@
         </is>
       </c>
       <c r="G100" s="8" t="n">
-        <v>0.4813186813186813</v>
+        <v>0.4857142857142857</v>
       </c>
     </row>
     <row r="101">
@@ -34716,7 +34716,7 @@
         </is>
       </c>
       <c r="G101" s="8" t="n">
-        <v>0.3186813186813187</v>
+        <v>0.3362637362637363</v>
       </c>
     </row>
     <row r="102">
@@ -34749,7 +34749,7 @@
         </is>
       </c>
       <c r="G102" s="8" t="n">
-        <v>0.1340659340659341</v>
+        <v>0.1648351648351648</v>
       </c>
     </row>
     <row r="103">
@@ -34782,7 +34782,7 @@
         </is>
       </c>
       <c r="G103" s="8" t="n">
-        <v>0.2351648351648352</v>
+        <v>0.2659340659340659</v>
       </c>
     </row>
     <row r="104">
@@ -34815,7 +34815,7 @@
         </is>
       </c>
       <c r="G104" s="8" t="n">
-        <v>-0.3042434922296656</v>
+        <v>-0.3133936724470991</v>
       </c>
     </row>
     <row r="105">
@@ -34848,7 +34848,7 @@
         </is>
       </c>
       <c r="G105" s="8" t="n">
-        <v>0.9516483516483516</v>
+        <v>0.9032967032967033</v>
       </c>
     </row>
     <row r="106">
@@ -35079,7 +35079,7 @@
         </is>
       </c>
       <c r="G112" s="8" t="n">
-        <v>0.5648351648351648</v>
+        <v>0.7186813186813187</v>
       </c>
     </row>
     <row r="113">
@@ -35277,7 +35277,7 @@
         </is>
       </c>
       <c r="G118" s="8" t="n">
-        <v>0.4769230769230769</v>
+        <v>0.6615384615384615</v>
       </c>
     </row>
     <row r="119">
@@ -35442,7 +35442,7 @@
         </is>
       </c>
       <c r="G123" s="8" t="n">
-        <v>0.4901098901098901</v>
+        <v>0.621978021978022</v>
       </c>
     </row>
     <row r="124">
@@ -35574,7 +35574,7 @@
         </is>
       </c>
       <c r="G127" s="8" t="n">
-        <v>0.3362637362637363</v>
+        <v>0.5076923076923077</v>
       </c>
     </row>
     <row r="128">
@@ -35673,7 +35673,7 @@
         </is>
       </c>
       <c r="G130" s="8" t="n">
-        <v>0.1956043956043956</v>
+        <v>0.3142857142857143</v>
       </c>
     </row>
     <row r="131">
@@ -35739,7 +35739,7 @@
         </is>
       </c>
       <c r="G132" s="8" t="n">
-        <v>0.2615384615384616</v>
+        <v>0.4153846153846154</v>
       </c>
     </row>
     <row r="133">
@@ -35772,7 +35772,7 @@
         </is>
       </c>
       <c r="G133" s="8" t="n">
-        <v>-0.183003604348671</v>
+        <v>-0.1624156988594455</v>
       </c>
     </row>
     <row r="134">
@@ -36135,7 +36135,7 @@
         </is>
       </c>
       <c r="G144" s="8" t="n">
-        <v>0.08571428571428572</v>
+        <v>0.02857142857142857</v>
       </c>
     </row>
     <row r="145">
@@ -36465,7 +36465,7 @@
         </is>
       </c>
       <c r="G154" s="8" t="n">
-        <v>0.1824175824175824</v>
+        <v>0.0989010989010989</v>
       </c>
     </row>
     <row r="155">
@@ -36762,7 +36762,7 @@
         </is>
       </c>
       <c r="G163" s="8" t="n">
-        <v>0.01098901098901099</v>
+        <v>-0.1340659340659341</v>
       </c>
     </row>
     <row r="164">
@@ -37026,7 +37026,7 @@
         </is>
       </c>
       <c r="G171" s="8" t="n">
-        <v>0.8505494505494505</v>
+        <v>0.8725274725274725</v>
       </c>
     </row>
     <row r="172">
@@ -37257,7 +37257,7 @@
         </is>
       </c>
       <c r="G178" s="8" t="n">
-        <v>-0.2747252747252747</v>
+        <v>-0.2571428571428571</v>
       </c>
     </row>
     <row r="179">
@@ -37455,7 +37455,7 @@
         </is>
       </c>
       <c r="G184" s="8" t="n">
-        <v>-0.3758241758241758</v>
+        <v>-0.3142857142857143</v>
       </c>
     </row>
     <row r="185">
@@ -37620,7 +37620,7 @@
         </is>
       </c>
       <c r="G189" s="8" t="n">
-        <v>-0.4065934065934066</v>
+        <v>-0.4153846153846154</v>
       </c>
     </row>
     <row r="190">
@@ -37752,7 +37752,7 @@
         </is>
       </c>
       <c r="G193" s="8" t="n">
-        <v>-0.2791208791208791</v>
+        <v>-0.2835164835164835</v>
       </c>
     </row>
     <row r="194">
@@ -37851,7 +37851,7 @@
         </is>
       </c>
       <c r="G196" s="8" t="n">
-        <v>-0.2659340659340659</v>
+        <v>-0.2263736263736264</v>
       </c>
     </row>
     <row r="197">
@@ -37917,7 +37917,7 @@
         </is>
       </c>
       <c r="G198" s="8" t="n">
-        <v>0.3582417582417582</v>
+        <v>0.3538461538461539</v>
       </c>
     </row>
     <row r="199">
@@ -37950,7 +37950,7 @@
         </is>
       </c>
       <c r="G199" s="8" t="n">
-        <v>-0.4417582417582417</v>
+        <v>-0.4373626373626374</v>
       </c>
     </row>
     <row r="200">
@@ -38049,7 +38049,7 @@
         </is>
       </c>
       <c r="G202" s="8" t="n">
-        <v>0.1272727272727273</v>
+        <v>0.06363636363636363</v>
       </c>
     </row>
     <row r="203">
@@ -38313,7 +38313,7 @@
         </is>
       </c>
       <c r="G210" s="8" t="n">
-        <v>-0.1909090909090909</v>
+        <v>-0.1090909090909091</v>
       </c>
     </row>
     <row r="211">
@@ -38379,7 +38379,7 @@
         </is>
       </c>
       <c r="G212" s="8" t="n">
-        <v>0.1454545454545454</v>
+        <v>0.1272727272727273</v>
       </c>
     </row>
     <row r="213">
@@ -38643,7 +38643,7 @@
         </is>
       </c>
       <c r="G220" s="8" t="n">
-        <v>-0.1</v>
+        <v>0.1363636363636364</v>
       </c>
     </row>
     <row r="221">
@@ -38676,7 +38676,7 @@
         </is>
       </c>
       <c r="G221" s="8" t="n">
-        <v>0.1727272727272727</v>
+        <v>0.1272727272727273</v>
       </c>
     </row>
     <row r="222">
@@ -38940,7 +38940,7 @@
         </is>
       </c>
       <c r="G229" s="8" t="n">
-        <v>0.01818181818181818</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="230">
@@ -38973,7 +38973,7 @@
         </is>
       </c>
       <c r="G230" s="8" t="n">
-        <v>-0.3363636363636364</v>
+        <v>-0.4272727272727272</v>
       </c>
     </row>
     <row r="231">
@@ -39006,7 +39006,7 @@
         </is>
       </c>
       <c r="G231" s="8" t="n">
-        <v>-0.03636363636363636</v>
+        <v>-0.1181818181818182</v>
       </c>
     </row>
     <row r="232">
@@ -39039,7 +39039,7 @@
         </is>
       </c>
       <c r="G232" s="8" t="n">
-        <v>-0.3363636363636364</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="233">
@@ -39072,7 +39072,7 @@
         </is>
       </c>
       <c r="G233" s="8" t="n">
-        <v>-0.00909090909090909</v>
+        <v>-0.08181818181818182</v>
       </c>
     </row>
     <row r="234">
@@ -39105,7 +39105,7 @@
         </is>
       </c>
       <c r="G234" s="8" t="n">
-        <v>0.06363636363636363</v>
+        <v>-0.02727272727272727</v>
       </c>
     </row>
     <row r="235">
@@ -39138,7 +39138,7 @@
         </is>
       </c>
       <c r="G235" s="8" t="n">
-        <v>0.02727272727272727</v>
+        <v>-0.01818181818181818</v>
       </c>
     </row>
     <row r="236">
@@ -39171,7 +39171,7 @@
         </is>
       </c>
       <c r="G236" s="8" t="n">
-        <v>0.2110180549825524</v>
+        <v>0.1834939608543934</v>
       </c>
     </row>
     <row r="237">
@@ -39204,7 +39204,7 @@
         </is>
       </c>
       <c r="G237" s="8" t="n">
-        <v>0.6909090909090909</v>
+        <v>0.8090909090909091</v>
       </c>
     </row>
     <row r="238">
@@ -39435,7 +39435,7 @@
         </is>
       </c>
       <c r="G244" s="8" t="n">
-        <v>-0.1181818181818182</v>
+        <v>-0.3363636363636364</v>
       </c>
     </row>
     <row r="245">
@@ -39633,7 +39633,7 @@
         </is>
       </c>
       <c r="G250" s="8" t="n">
-        <v>0.09090909090909091</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="251">
@@ -39798,7 +39798,7 @@
         </is>
       </c>
       <c r="G255" s="8" t="n">
-        <v>0.04545454545454546</v>
+        <v>-0.2272727272727273</v>
       </c>
     </row>
     <row r="256">
@@ -39930,7 +39930,7 @@
         </is>
       </c>
       <c r="G259" s="8" t="n">
-        <v>0.2363636363636364</v>
+        <v>0.02727272727272727</v>
       </c>
     </row>
     <row r="260">
@@ -40029,7 +40029,7 @@
         </is>
       </c>
       <c r="G262" s="8" t="n">
-        <v>0.2</v>
+        <v>-0.05454545454545454</v>
       </c>
     </row>
     <row r="263">
@@ -40095,7 +40095,7 @@
         </is>
       </c>
       <c r="G264" s="8" t="n">
-        <v>-0.04545454545454546</v>
+        <v>0.05454545454545454</v>
       </c>
     </row>
     <row r="265">
@@ -40128,7 +40128,7 @@
         </is>
       </c>
       <c r="G265" s="8" t="n">
-        <v>0.1926686588971131</v>
+        <v>0.4128614119223852</v>
       </c>
     </row>
     <row r="266">
@@ -40491,7 +40491,7 @@
         </is>
       </c>
       <c r="G276" s="8" t="n">
-        <v>0.1636363636363636</v>
+        <v>0.2636363636363636</v>
       </c>
     </row>
     <row r="277">
@@ -40821,7 +40821,7 @@
         </is>
       </c>
       <c r="G286" s="8" t="n">
-        <v>0.07272727272727272</v>
+        <v>0.2272727272727273</v>
       </c>
     </row>
     <row r="287">
@@ -41118,7 +41118,7 @@
         </is>
       </c>
       <c r="G295" s="8" t="n">
-        <v>0.2272727272727273</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="296">
@@ -41382,7 +41382,7 @@
         </is>
       </c>
       <c r="G303" s="8" t="n">
-        <v>0.8636363636363636</v>
+        <v>0.8818181818181818</v>
       </c>
     </row>
     <row r="304">
@@ -41613,7 +41613,7 @@
         </is>
       </c>
       <c r="G310" s="8" t="n">
-        <v>-0.3909090909090909</v>
+        <v>-0.4909090909090909</v>
       </c>
     </row>
     <row r="311">
@@ -41811,7 +41811,7 @@
         </is>
       </c>
       <c r="G316" s="8" t="n">
-        <v>-0.2363636363636364</v>
+        <v>-0.3636363636363636</v>
       </c>
     </row>
     <row r="317">
@@ -41976,7 +41976,7 @@
         </is>
       </c>
       <c r="G321" s="8" t="n">
-        <v>-0.4090909090909091</v>
+        <v>-0.5454545454545454</v>
       </c>
     </row>
     <row r="322">
@@ -42108,7 +42108,7 @@
         </is>
       </c>
       <c r="G325" s="8" t="n">
-        <v>0.2181818181818182</v>
+        <v>0.08181818181818182</v>
       </c>
     </row>
     <row r="326">
@@ -42207,7 +42207,7 @@
         </is>
       </c>
       <c r="G328" s="8" t="n">
-        <v>0.1909090909090909</v>
+        <v>0.1727272727272727</v>
       </c>
     </row>
     <row r="329">
@@ -42273,7 +42273,7 @@
         </is>
       </c>
       <c r="G330" s="8" t="n">
-        <v>-0.1727272727272727</v>
+        <v>-0.06363636363636363</v>
       </c>
     </row>
     <row r="331">
@@ -42306,7 +42306,7 @@
         </is>
       </c>
       <c r="G331" s="8" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="332">
@@ -42405,7 +42405,7 @@
         </is>
       </c>
       <c r="G334" s="8" t="n">
-        <v>0.2824561403508772</v>
+        <v>0.2684210526315789</v>
       </c>
     </row>
     <row r="335">
@@ -42669,7 +42669,7 @@
         </is>
       </c>
       <c r="G342" s="8" t="n">
-        <v>0.1192982456140351</v>
+        <v>0.2070175438596491</v>
       </c>
     </row>
     <row r="343">
@@ -42735,7 +42735,7 @@
         </is>
       </c>
       <c r="G344" s="8" t="n">
-        <v>0.2842105263157895</v>
+        <v>0.2719298245614035</v>
       </c>
     </row>
     <row r="345">
@@ -42999,7 +42999,7 @@
         </is>
       </c>
       <c r="G352" s="8" t="n">
-        <v>0.07894736842105263</v>
+        <v>0.1982456140350877</v>
       </c>
     </row>
     <row r="353">
@@ -43032,7 +43032,7 @@
         </is>
       </c>
       <c r="G353" s="8" t="n">
-        <v>0.2175438596491228</v>
+        <v>0.2105263157894737</v>
       </c>
     </row>
     <row r="354">
@@ -43296,7 +43296,7 @@
         </is>
       </c>
       <c r="G361" s="8" t="n">
-        <v>0.2298245614035088</v>
+        <v>0.1421052631578947</v>
       </c>
     </row>
     <row r="362">
@@ -43329,7 +43329,7 @@
         </is>
       </c>
       <c r="G362" s="8" t="n">
-        <v>-0.4526315789473684</v>
+        <v>-0.4631578947368421</v>
       </c>
     </row>
     <row r="363">
@@ -43362,7 +43362,7 @@
         </is>
       </c>
       <c r="G363" s="8" t="n">
-        <v>-0.4894736842105263</v>
+        <v>-0.5087719298245614</v>
       </c>
     </row>
     <row r="364">
@@ -43395,7 +43395,7 @@
         </is>
       </c>
       <c r="G364" s="8" t="n">
-        <v>0.1473684210526316</v>
+        <v>0.1596491228070175</v>
       </c>
     </row>
     <row r="365">
@@ -43428,7 +43428,7 @@
         </is>
       </c>
       <c r="G365" s="8" t="n">
-        <v>0.07719298245614035</v>
+        <v>0.06491228070175438</v>
       </c>
     </row>
     <row r="366">
@@ -43461,7 +43461,7 @@
         </is>
       </c>
       <c r="G366" s="8" t="n">
-        <v>0.4596491228070175</v>
+        <v>0.456140350877193</v>
       </c>
     </row>
     <row r="367">
@@ -43494,7 +43494,7 @@
         </is>
       </c>
       <c r="G367" s="8" t="n">
-        <v>-0.1245614035087719</v>
+        <v>-0.1280701754385965</v>
       </c>
     </row>
     <row r="368">
@@ -43527,7 +43527,7 @@
         </is>
       </c>
       <c r="G368" s="8" t="n">
-        <v>0.512280701754386</v>
+        <v>0.4929824561403509</v>
       </c>
     </row>
     <row r="369">
@@ -43560,7 +43560,7 @@
         </is>
       </c>
       <c r="G369" s="8" t="n">
-        <v>0.9105263157894737</v>
+        <v>0.9157894736842105</v>
       </c>
     </row>
     <row r="370">
@@ -43791,7 +43791,7 @@
         </is>
       </c>
       <c r="G376" s="8" t="n">
-        <v>-0.4789473684210526</v>
+        <v>-0.5666666666666667</v>
       </c>
     </row>
     <row r="377">
@@ -43989,7 +43989,7 @@
         </is>
       </c>
       <c r="G382" s="8" t="n">
-        <v>-0.4578947368421052</v>
+        <v>-0.5298245614035088</v>
       </c>
     </row>
     <row r="383">
@@ -44154,7 +44154,7 @@
         </is>
       </c>
       <c r="G387" s="8" t="n">
-        <v>0.1543859649122807</v>
+        <v>0.0456140350877193</v>
       </c>
     </row>
     <row r="388">
@@ -44286,7 +44286,7 @@
         </is>
       </c>
       <c r="G391" s="8" t="n">
-        <v>0.3035087719298246</v>
+        <v>0.2192982456140351</v>
       </c>
     </row>
     <row r="392">
@@ -44385,7 +44385,7 @@
         </is>
       </c>
       <c r="G394" s="8" t="n">
-        <v>0.4894736842105263</v>
+        <v>0.456140350877193</v>
       </c>
     </row>
     <row r="395">
@@ -44451,7 +44451,7 @@
         </is>
       </c>
       <c r="G396" s="8" t="n">
-        <v>-0.243859649122807</v>
+        <v>-0.1894736842105263</v>
       </c>
     </row>
     <row r="397">
@@ -44484,7 +44484,7 @@
         </is>
       </c>
       <c r="G397" s="8" t="n">
-        <v>0.4368421052631579</v>
+        <v>0.5245614035087719</v>
       </c>
     </row>
     <row r="398">
@@ -46761,7 +46761,7 @@
         </is>
       </c>
       <c r="G466" s="8" t="n">
-        <v>0.5678152492668622</v>
+        <v>0.5487536656891495</v>
       </c>
     </row>
     <row r="467">
@@ -47025,7 +47025,7 @@
         </is>
       </c>
       <c r="G474" s="8" t="n">
-        <v>0.5359237536656891</v>
+        <v>0.3478739002932552</v>
       </c>
     </row>
     <row r="475">
@@ -47091,7 +47091,7 @@
         </is>
       </c>
       <c r="G476" s="8" t="n">
-        <v>0.4593108504398827</v>
+        <v>0.4541788856304985</v>
       </c>
     </row>
     <row r="477">
@@ -47355,7 +47355,7 @@
         </is>
       </c>
       <c r="G484" s="8" t="n">
-        <v>0.3460410557184751</v>
+        <v>0.07954545454545454</v>
       </c>
     </row>
     <row r="485">
@@ -47388,7 +47388,7 @@
         </is>
       </c>
       <c r="G485" s="8" t="n">
-        <v>0.6554252199413489</v>
+        <v>0.6502932551319648</v>
       </c>
     </row>
     <row r="486">
@@ -47652,7 +47652,7 @@
         </is>
       </c>
       <c r="G493" s="8" t="n">
-        <v>0.4024926686217009</v>
+        <v>0.02529325513196481</v>
       </c>
     </row>
     <row r="494">
@@ -47685,7 +47685,7 @@
         </is>
       </c>
       <c r="G494" s="8" t="n">
-        <v>-0.2030791788856305</v>
+        <v>-0.2093108504398827</v>
       </c>
     </row>
     <row r="495">
@@ -47718,7 +47718,7 @@
         </is>
       </c>
       <c r="G495" s="8" t="n">
-        <v>-0.2767595307917888</v>
+        <v>-0.2829912023460411</v>
       </c>
     </row>
     <row r="496">
@@ -47751,7 +47751,7 @@
         </is>
       </c>
       <c r="G496" s="8" t="n">
-        <v>-0.2313049853372434</v>
+        <v>-0.2375366568914956</v>
       </c>
     </row>
     <row r="497">
@@ -47784,7 +47784,7 @@
         </is>
       </c>
       <c r="G497" s="8" t="n">
-        <v>-0.3295454545454545</v>
+        <v>-0.3376099706744868</v>
       </c>
     </row>
     <row r="498">
@@ -47817,7 +47817,7 @@
         </is>
       </c>
       <c r="G498" s="8" t="n">
-        <v>-0.5087976539589443</v>
+        <v>-0.5117302052785924</v>
       </c>
     </row>
     <row r="499">
@@ -47883,7 +47883,7 @@
         </is>
       </c>
       <c r="G500" s="8" t="n">
-        <v>-0.5391065310934595</v>
+        <v>-0.53724497539217</v>
       </c>
     </row>
     <row r="501">
@@ -47916,7 +47916,7 @@
         </is>
       </c>
       <c r="G501" s="8" t="n">
-        <v>0.8867302052785924</v>
+        <v>0.6730205278592375</v>
       </c>
     </row>
     <row r="502">
@@ -48147,7 +48147,7 @@
         </is>
       </c>
       <c r="G508" s="8" t="n">
-        <v>-0.06964809384164222</v>
+        <v>0.1429618768328446</v>
       </c>
     </row>
     <row r="509">
@@ -48345,7 +48345,7 @@
         </is>
       </c>
       <c r="G514" s="8" t="n">
-        <v>-0.156524926686217</v>
+        <v>0.07441348973607038</v>
       </c>
     </row>
     <row r="515">
@@ -48510,7 +48510,7 @@
         </is>
       </c>
       <c r="G519" s="8" t="n">
-        <v>-0.1319648093841642</v>
+        <v>0.06708211143695014</v>
       </c>
     </row>
     <row r="520">
@@ -48642,7 +48642,7 @@
         </is>
       </c>
       <c r="G523" s="8" t="n">
-        <v>-0.2265395894428152</v>
+        <v>-0.003665689149560118</v>
       </c>
     </row>
     <row r="524">
@@ -48741,7 +48741,7 @@
         </is>
       </c>
       <c r="G526" s="8" t="n">
-        <v>-0.2932551319648094</v>
+        <v>-0.01209677419354839</v>
       </c>
     </row>
     <row r="527">
@@ -48807,7 +48807,7 @@
         </is>
       </c>
       <c r="G528" s="8" t="n">
-        <v>-0.3189149560117302</v>
+        <v>-0.02016129032258064</v>
       </c>
     </row>
     <row r="529">
@@ -48840,7 +48840,7 @@
         </is>
       </c>
       <c r="G529" s="8" t="n">
-        <v>-0.4359763452420173</v>
+        <v>-0.2438637968689337</v>
       </c>
     </row>
     <row r="530">
@@ -48939,7 +48939,7 @@
         </is>
       </c>
       <c r="G532" s="8" t="n">
-        <v>0.3299120234604105</v>
+        <v>0.3152492668621701</v>
       </c>
     </row>
     <row r="533">
@@ -49203,7 +49203,7 @@
         </is>
       </c>
       <c r="G540" s="8" t="n">
-        <v>0.2342375366568915</v>
+        <v>0.1627565982404692</v>
       </c>
     </row>
     <row r="541">
@@ -49269,7 +49269,7 @@
         </is>
       </c>
       <c r="G542" s="8" t="n">
-        <v>-0.2459677419354839</v>
+        <v>-0.251099706744868</v>
       </c>
     </row>
     <row r="543">
@@ -49533,7 +49533,7 @@
         </is>
       </c>
       <c r="G550" s="8" t="n">
-        <v>-0.3328445747800586</v>
+        <v>-0.374633431085044</v>
       </c>
     </row>
     <row r="551">
@@ -49566,7 +49566,7 @@
         </is>
       </c>
       <c r="G551" s="8" t="n">
-        <v>-0.1737536656891496</v>
+        <v>-0.18658357771261</v>
       </c>
     </row>
     <row r="552">
@@ -49830,7 +49830,7 @@
         </is>
       </c>
       <c r="G559" s="8" t="n">
-        <v>-0.2445014662756598</v>
+        <v>-0.3049853372434018</v>
       </c>
     </row>
     <row r="560">
@@ -49863,7 +49863,7 @@
         </is>
       </c>
       <c r="G560" s="8" t="n">
-        <v>-0.5769794721407625</v>
+        <v>-0.5810117302052786</v>
       </c>
     </row>
     <row r="561">
@@ -49896,7 +49896,7 @@
         </is>
       </c>
       <c r="G561" s="8" t="n">
-        <v>-0.5795454545454546</v>
+        <v>-0.5843108504398827</v>
       </c>
     </row>
     <row r="562">
@@ -49929,7 +49929,7 @@
         </is>
       </c>
       <c r="G562" s="8" t="n">
-        <v>-0.5395894428152492</v>
+        <v>-0.5447214076246334</v>
       </c>
     </row>
     <row r="563">
@@ -49962,7 +49962,7 @@
         </is>
       </c>
       <c r="G563" s="8" t="n">
-        <v>-0.4717741935483871</v>
+        <v>-0.4783724340175953</v>
       </c>
     </row>
     <row r="564">
@@ -49995,7 +49995,7 @@
         </is>
       </c>
       <c r="G564" s="8" t="n">
-        <v>-0.5494868035190615</v>
+        <v>-0.5531524926686217</v>
       </c>
     </row>
     <row r="565">
@@ -50028,7 +50028,7 @@
         </is>
       </c>
       <c r="G565" s="8" t="n">
-        <v>0.5021994134897361</v>
+        <v>0.499633431085044</v>
       </c>
     </row>
     <row r="566">
@@ -50061,7 +50061,7 @@
         </is>
       </c>
       <c r="G566" s="8" t="n">
-        <v>-0.3535360749646683</v>
+        <v>-0.3498629728871133</v>
       </c>
     </row>
     <row r="567">
@@ -50094,7 +50094,7 @@
         </is>
       </c>
       <c r="G567" s="8" t="n">
-        <v>0.9659090909090909</v>
+        <v>0.9457478005865103</v>
       </c>
     </row>
     <row r="568">
@@ -50325,7 +50325,7 @@
         </is>
       </c>
       <c r="G574" s="8" t="n">
-        <v>-0.6136363636363636</v>
+        <v>-0.5945747800586511</v>
       </c>
     </row>
     <row r="575">
@@ -50523,7 +50523,7 @@
         </is>
       </c>
       <c r="G580" s="8" t="n">
-        <v>-0.6385630498533724</v>
+        <v>-0.6271994134897361</v>
       </c>
     </row>
     <row r="581">
@@ -50688,7 +50688,7 @@
         </is>
       </c>
       <c r="G585" s="8" t="n">
-        <v>-0.6074046920821115</v>
+        <v>-0.6162023460410557</v>
       </c>
     </row>
     <row r="586">
@@ -50820,7 +50820,7 @@
         </is>
       </c>
       <c r="G589" s="8" t="n">
-        <v>-0.5373900293255132</v>
+        <v>-0.5428885630498533</v>
       </c>
     </row>
     <row r="590">
@@ -50919,7 +50919,7 @@
         </is>
       </c>
       <c r="G592" s="8" t="n">
-        <v>-0.5883431085043989</v>
+        <v>-0.5692815249266863</v>
       </c>
     </row>
     <row r="593">
@@ -50985,7 +50985,7 @@
         </is>
       </c>
       <c r="G594" s="8" t="n">
-        <v>0.500366568914956</v>
+        <v>0.4629765395894428</v>
       </c>
     </row>
     <row r="595">
@@ -51018,7 +51018,7 @@
         </is>
       </c>
       <c r="G595" s="8" t="n">
-        <v>-0.3285589808372943</v>
+        <v>-0.332415738018727</v>
       </c>
     </row>
     <row r="596">
@@ -51117,7 +51117,7 @@
         </is>
       </c>
       <c r="G598" s="8" t="n">
-        <v>0.8300492610837439</v>
+        <v>0.8182266009852217</v>
       </c>
     </row>
     <row r="599">
@@ -51381,7 +51381,7 @@
         </is>
       </c>
       <c r="G606" s="8" t="n">
-        <v>0.780295566502463</v>
+        <v>0.7536945812807881</v>
       </c>
     </row>
     <row r="607">
@@ -51447,7 +51447,7 @@
         </is>
       </c>
       <c r="G608" s="8" t="n">
-        <v>0.7320197044334975</v>
+        <v>0.7270935960591133</v>
       </c>
     </row>
     <row r="609">
@@ -51711,7 +51711,7 @@
         </is>
       </c>
       <c r="G616" s="8" t="n">
-        <v>0.6921182266009852</v>
+        <v>0.6655172413793103</v>
       </c>
     </row>
     <row r="617">
@@ -51744,7 +51744,7 @@
         </is>
       </c>
       <c r="G617" s="8" t="n">
-        <v>0.7497536945812808</v>
+        <v>0.7369458128078817</v>
       </c>
     </row>
     <row r="618">
@@ -52008,7 +52008,7 @@
         </is>
       </c>
       <c r="G625" s="8" t="n">
-        <v>0.716256157635468</v>
+        <v>0.6832512315270935</v>
       </c>
     </row>
     <row r="626">
@@ -52041,7 +52041,7 @@
         </is>
       </c>
       <c r="G626" s="8" t="n">
-        <v>-0.5926108374384237</v>
+        <v>-0.6088669950738916</v>
       </c>
     </row>
     <row r="627">
@@ -52074,7 +52074,7 @@
         </is>
       </c>
       <c r="G627" s="8" t="n">
-        <v>-0.5192118226600986</v>
+        <v>-0.5369458128078818</v>
       </c>
     </row>
     <row r="628">
@@ -52107,7 +52107,7 @@
         </is>
       </c>
       <c r="G628" s="8" t="n">
-        <v>-0.4605911330049261</v>
+        <v>-0.4768472906403941</v>
       </c>
     </row>
     <row r="629">
@@ -52140,7 +52140,7 @@
         </is>
       </c>
       <c r="G629" s="8" t="n">
-        <v>-0.6655172413793103</v>
+        <v>-0.6812807881773399</v>
       </c>
     </row>
     <row r="630">
@@ -52173,7 +52173,7 @@
         </is>
       </c>
       <c r="G630" s="8" t="n">
-        <v>-0.6113300492610837</v>
+        <v>-0.6280788177339901</v>
       </c>
     </row>
     <row r="631">
@@ -52206,7 +52206,7 @@
         </is>
       </c>
       <c r="G631" s="8" t="n">
-        <v>-0.5940886699507389</v>
+        <v>-0.6004926108374384</v>
       </c>
     </row>
     <row r="632">
@@ -52239,7 +52239,7 @@
         </is>
       </c>
       <c r="G632" s="8" t="n">
-        <v>-0.5351168003619543</v>
+        <v>-0.534124465080801</v>
       </c>
     </row>
     <row r="633">
@@ -52272,7 +52272,7 @@
         </is>
       </c>
       <c r="G633" s="8" t="n">
-        <v>0.9738916256157636</v>
+        <v>0.9729064039408867</v>
       </c>
     </row>
     <row r="634">
@@ -52503,7 +52503,7 @@
         </is>
       </c>
       <c r="G640" s="8" t="n">
-        <v>-0.6098522167487684</v>
+        <v>-0.6438423645320197</v>
       </c>
     </row>
     <row r="641">
@@ -52701,7 +52701,7 @@
         </is>
       </c>
       <c r="G646" s="8" t="n">
-        <v>-0.5472906403940887</v>
+        <v>-0.5842364532019705</v>
       </c>
     </row>
     <row r="647">
@@ -52866,7 +52866,7 @@
         </is>
       </c>
       <c r="G651" s="8" t="n">
-        <v>-0.4852216748768473</v>
+        <v>-0.5216748768472906</v>
       </c>
     </row>
     <row r="652">
@@ -52998,7 +52998,7 @@
         </is>
       </c>
       <c r="G655" s="8" t="n">
-        <v>-0.6886699507389162</v>
+        <v>-0.7088669950738916</v>
       </c>
     </row>
     <row r="656">
@@ -53097,7 +53097,7 @@
         </is>
       </c>
       <c r="G658" s="8" t="n">
-        <v>-0.632512315270936</v>
+        <v>-0.6719211822660098</v>
       </c>
     </row>
     <row r="659">
@@ -53163,7 +53163,7 @@
         </is>
       </c>
       <c r="G660" s="8" t="n">
-        <v>-0.6251231527093596</v>
+        <v>-0.6118226600985222</v>
       </c>
     </row>
     <row r="661">
@@ -53196,7 +53196,7 @@
         </is>
       </c>
       <c r="G661" s="8" t="n">
-        <v>-0.5430554826111813</v>
+        <v>-0.4874847068665926</v>
       </c>
     </row>
     <row r="662">
@@ -53295,7 +53295,7 @@
         </is>
       </c>
       <c r="G664" s="8" t="n">
-        <v>0.8440018966334756</v>
+        <v>0.8380749170222854</v>
       </c>
     </row>
     <row r="665">
@@ -53559,7 +53559,7 @@
         </is>
       </c>
       <c r="G672" s="8" t="n">
-        <v>0.8063063063063063</v>
+        <v>0.7923186344238976</v>
       </c>
     </row>
     <row r="673">
@@ -53625,7 +53625,7 @@
         </is>
       </c>
       <c r="G674" s="8" t="n">
-        <v>0.7965860597439545</v>
+        <v>0.7930298719772404</v>
       </c>
     </row>
     <row r="675">
@@ -53889,7 +53889,7 @@
         </is>
       </c>
       <c r="G682" s="8" t="n">
-        <v>0.7560455192034139</v>
+        <v>0.7332859174964438</v>
       </c>
     </row>
     <row r="683">
@@ -53922,7 +53922,7 @@
         </is>
       </c>
       <c r="G683" s="8" t="n">
-        <v>0.7954006638217165</v>
+        <v>0.7894736842105263</v>
       </c>
     </row>
     <row r="684">
@@ -54186,7 +54186,7 @@
         </is>
       </c>
       <c r="G691" s="8" t="n">
-        <v>0.7849691797060218</v>
+        <v>0.7548601232811759</v>
       </c>
     </row>
     <row r="692">
@@ -54219,7 +54219,7 @@
         </is>
       </c>
       <c r="G692" s="8" t="n">
-        <v>-0.7631578947368421</v>
+        <v>-0.768610715979137</v>
       </c>
     </row>
     <row r="693">
@@ -54252,7 +54252,7 @@
         </is>
       </c>
       <c r="G693" s="8" t="n">
-        <v>-0.7724039829302988</v>
+        <v>-0.7790422000948317</v>
       </c>
     </row>
     <row r="694">
@@ -54285,7 +54285,7 @@
         </is>
       </c>
       <c r="G694" s="8" t="n">
-        <v>-0.4506875296348981</v>
+        <v>-0.4566145092460882</v>
       </c>
     </row>
     <row r="695">
@@ -54318,7 +54318,7 @@
         </is>
       </c>
       <c r="G695" s="8" t="n">
-        <v>-0.6797060218112849</v>
+        <v>-0.6889521100047415</v>
       </c>
     </row>
     <row r="696">
@@ -54351,7 +54351,7 @@
         </is>
       </c>
       <c r="G696" s="8" t="n">
-        <v>-0.5739687055476529</v>
+        <v>-0.5815552394499763</v>
       </c>
     </row>
     <row r="697">
@@ -54384,7 +54384,7 @@
         </is>
       </c>
       <c r="G697" s="8" t="n">
-        <v>-0.6889521100047415</v>
+        <v>-0.69108582266477</v>
       </c>
     </row>
     <row r="698">
@@ -54417,7 +54417,7 @@
         </is>
       </c>
       <c r="G698" s="8" t="n">
-        <v>-0.394896479021524</v>
+        <v>-0.3965582015061352</v>
       </c>
     </row>
     <row r="699">
@@ -54450,7 +54450,7 @@
         </is>
       </c>
       <c r="G699" s="8" t="n">
-        <v>0.9834044570886676</v>
+        <v>0.9772403982930299</v>
       </c>
     </row>
     <row r="700">
@@ -54681,7 +54681,7 @@
         </is>
       </c>
       <c r="G706" s="8" t="n">
-        <v>-0.7844950213371266</v>
+        <v>-0.7961119013750593</v>
       </c>
     </row>
     <row r="707">
@@ -54879,7 +54879,7 @@
         </is>
       </c>
       <c r="G712" s="8" t="n">
-        <v>-0.7835467045993362</v>
+        <v>-0.787814129919393</v>
       </c>
     </row>
     <row r="713">
@@ -55044,7 +55044,7 @@
         </is>
       </c>
       <c r="G717" s="8" t="n">
-        <v>-0.4779516358463727</v>
+        <v>-0.4964438122332859</v>
       </c>
     </row>
     <row r="718">
@@ -55176,7 +55176,7 @@
         </is>
       </c>
       <c r="G721" s="8" t="n">
-        <v>-0.670697012802276</v>
+        <v>-0.6752015173067805</v>
       </c>
     </row>
     <row r="722">
@@ -55275,7 +55275,7 @@
         </is>
       </c>
       <c r="G724" s="8" t="n">
-        <v>-0.5874822190611664</v>
+        <v>-0.5988620199146515</v>
       </c>
     </row>
     <row r="725">
@@ -55341,7 +55341,7 @@
         </is>
       </c>
       <c r="G726" s="8" t="n">
-        <v>-0.7195353247984827</v>
+        <v>-0.7010431484115695</v>
       </c>
     </row>
     <row r="727">
@@ -55374,7 +55374,7 @@
         </is>
       </c>
       <c r="G727" s="8" t="n">
-        <v>-0.4100893703093975</v>
+        <v>-0.3609498625501817</v>
       </c>
     </row>
     <row r="728">
@@ -55473,7 +55473,7 @@
         </is>
       </c>
       <c r="G730" s="8" t="n">
-        <v>0.7889423076923077</v>
+        <v>0.7830856643356643</v>
       </c>
     </row>
     <row r="731">
@@ -55737,7 +55737,7 @@
         </is>
       </c>
       <c r="G738" s="8" t="n">
-        <v>0.7716783216783217</v>
+        <v>0.7098339160839161</v>
       </c>
     </row>
     <row r="739">
@@ -55803,7 +55803,7 @@
         </is>
       </c>
       <c r="G740" s="8" t="n">
-        <v>0.65625</v>
+        <v>0.6541520979020979</v>
       </c>
     </row>
     <row r="741">
@@ -56067,7 +56067,7 @@
         </is>
       </c>
       <c r="G748" s="8" t="n">
-        <v>0.6289772727272728</v>
+        <v>0.5636800699300699</v>
       </c>
     </row>
     <row r="749">
@@ -56100,7 +56100,7 @@
         </is>
       </c>
       <c r="G749" s="8" t="n">
-        <v>0.8042832167832168</v>
+        <v>0.801048951048951</v>
       </c>
     </row>
     <row r="750">
@@ -56364,7 +56364,7 @@
         </is>
       </c>
       <c r="G757" s="8" t="n">
-        <v>0.7421765734265734</v>
+        <v>0.6301573426573427</v>
       </c>
     </row>
     <row r="758">
@@ -56397,7 +56397,7 @@
         </is>
       </c>
       <c r="G758" s="8" t="n">
-        <v>-0.7342657342657343</v>
+        <v>-0.7333479020979021</v>
       </c>
     </row>
     <row r="759">
@@ -56430,7 +56430,7 @@
         </is>
       </c>
       <c r="G759" s="8" t="n">
-        <v>-0.7420454545454546</v>
+        <v>-0.7417832167832168</v>
       </c>
     </row>
     <row r="760">
@@ -56463,7 +56463,7 @@
         </is>
       </c>
       <c r="G760" s="8" t="n">
-        <v>-0.5883304195804195</v>
+        <v>-0.5871940559440559</v>
       </c>
     </row>
     <row r="761">
@@ -56496,7 +56496,7 @@
         </is>
       </c>
       <c r="G761" s="8" t="n">
-        <v>-0.7261363636363637</v>
+        <v>-0.7250874125874126</v>
       </c>
     </row>
     <row r="762">
@@ -56529,7 +56529,7 @@
         </is>
       </c>
       <c r="G762" s="8" t="n">
-        <v>-0.6424825174825175</v>
+        <v>-0.6419143356643356</v>
       </c>
     </row>
     <row r="763">
@@ -56562,7 +56562,7 @@
         </is>
       </c>
       <c r="G763" s="8" t="n">
-        <v>-0.4571678321678322</v>
+        <v>-0.4555944055944056</v>
       </c>
     </row>
     <row r="764">
@@ -56595,7 +56595,7 @@
         </is>
       </c>
       <c r="G764" s="8" t="n">
-        <v>-0.3690390187345877</v>
+        <v>-0.3712531651580279</v>
       </c>
     </row>
     <row r="765">
@@ -56628,7 +56628,7 @@
         </is>
       </c>
       <c r="G765" s="8" t="n">
-        <v>0.9764423076923077</v>
+        <v>0.9329108391608392</v>
       </c>
     </row>
     <row r="766">
@@ -56859,7 +56859,7 @@
         </is>
       </c>
       <c r="G772" s="8" t="n">
-        <v>-0.6940996503496504</v>
+        <v>-0.6060314685314685</v>
       </c>
     </row>
     <row r="773">
@@ -57057,7 +57057,7 @@
         </is>
       </c>
       <c r="G778" s="8" t="n">
-        <v>-0.7041958041958042</v>
+        <v>-0.6152097902097902</v>
       </c>
     </row>
     <row r="779">
@@ -57222,7 +57222,7 @@
         </is>
       </c>
       <c r="G783" s="8" t="n">
-        <v>-0.5604895104895105</v>
+        <v>-0.4708916083916084</v>
       </c>
     </row>
     <row r="784">
@@ -57354,7 +57354,7 @@
         </is>
       </c>
       <c r="G787" s="8" t="n">
-        <v>-0.6868444055944056</v>
+        <v>-0.6054195804195804</v>
       </c>
     </row>
     <row r="788">
@@ -57453,7 +57453,7 @@
         </is>
       </c>
       <c r="G790" s="8" t="n">
-        <v>-0.5844842657342657</v>
+        <v>-0.4672202797202797</v>
       </c>
     </row>
     <row r="791">
@@ -57519,7 +57519,7 @@
         </is>
       </c>
       <c r="G792" s="8" t="n">
-        <v>-0.395236013986014</v>
+        <v>-0.2678758741258741</v>
       </c>
     </row>
     <row r="793">
@@ -57552,7 +57552,7 @@
         </is>
       </c>
       <c r="G793" s="8" t="n">
-        <v>-0.333744209410441</v>
+        <v>-0.2734799666575966</v>
       </c>
     </row>
     <row r="794">
@@ -57651,7 +57651,7 @@
         </is>
       </c>
       <c r="G796" s="8" t="n">
-        <v>0.7936016511867905</v>
+        <v>0.8059855521155831</v>
       </c>
     </row>
     <row r="797">
@@ -57915,7 +57915,7 @@
         </is>
       </c>
       <c r="G804" s="8" t="n">
-        <v>0.8328173374613003</v>
+        <v>0.7853457172342622</v>
       </c>
     </row>
     <row r="805">
@@ -57981,7 +57981,7 @@
         </is>
       </c>
       <c r="G806" s="8" t="n">
-        <v>0.4901960784313725</v>
+        <v>0.500515995872033</v>
       </c>
     </row>
     <row r="807">
@@ -58245,7 +58245,7 @@
         </is>
       </c>
       <c r="G814" s="8" t="n">
-        <v>0.4365325077399381</v>
+        <v>0.3560371517027864</v>
       </c>
     </row>
     <row r="815">
@@ -58278,7 +58278,7 @@
         </is>
       </c>
       <c r="G815" s="8" t="n">
-        <v>0.7213622291021672</v>
+        <v>0.7254901960784313</v>
       </c>
     </row>
     <row r="816">
@@ -58542,7 +58542,7 @@
         </is>
       </c>
       <c r="G823" s="8" t="n">
-        <v>0.7564499484004128</v>
+        <v>0.7151702786377709</v>
       </c>
     </row>
     <row r="824">
@@ -58575,7 +58575,7 @@
         </is>
       </c>
       <c r="G824" s="8" t="n">
-        <v>0.5479876160990712</v>
+        <v>0.5603715170278638</v>
       </c>
     </row>
     <row r="825">
@@ -58608,7 +58608,7 @@
         </is>
       </c>
       <c r="G825" s="8" t="n">
-        <v>0.651186790505676</v>
+        <v>0.6553147574819401</v>
       </c>
     </row>
     <row r="826">
@@ -58641,7 +58641,7 @@
         </is>
       </c>
       <c r="G826" s="8" t="n">
-        <v>0.4860681114551084</v>
+        <v>0.4943240454076367</v>
       </c>
     </row>
     <row r="827">
@@ -58674,7 +58674,7 @@
         </is>
       </c>
       <c r="G827" s="8" t="n">
-        <v>0.347781217750258</v>
+        <v>0.3601651186790505</v>
       </c>
     </row>
     <row r="828">
@@ -58707,7 +58707,7 @@
         </is>
       </c>
       <c r="G828" s="8" t="n">
-        <v>0.5830753353973168</v>
+        <v>0.5954592363261094</v>
       </c>
     </row>
     <row r="829">
@@ -58740,7 +58740,7 @@
         </is>
       </c>
       <c r="G829" s="8" t="n">
-        <v>0.06914344685242518</v>
+        <v>0.07739938080495357</v>
       </c>
     </row>
     <row r="830">
@@ -58773,7 +58773,7 @@
         </is>
       </c>
       <c r="G830" s="8" t="n">
-        <v>-0.1463438477643422</v>
+        <v>-0.1235100559145867</v>
       </c>
     </row>
     <row r="831">
@@ -58806,7 +58806,7 @@
         </is>
       </c>
       <c r="G831" s="8" t="n">
-        <v>0.9793601651186791</v>
+        <v>0.9566563467492261</v>
       </c>
     </row>
     <row r="832">
@@ -59037,7 +59037,7 @@
         </is>
       </c>
       <c r="G838" s="8" t="n">
-        <v>0.6346749226006192</v>
+        <v>0.6491228070175439</v>
       </c>
     </row>
     <row r="839">
@@ -59235,7 +59235,7 @@
         </is>
       </c>
       <c r="G844" s="8" t="n">
-        <v>0.7192982456140351</v>
+        <v>0.6759545923632611</v>
       </c>
     </row>
     <row r="845">
@@ -59400,7 +59400,7 @@
         </is>
       </c>
       <c r="G849" s="8" t="n">
-        <v>0.5603715170278638</v>
+        <v>0.5356037151702786</v>
       </c>
     </row>
     <row r="850">
@@ -59532,7 +59532,7 @@
         </is>
       </c>
       <c r="G853" s="8" t="n">
-        <v>0.4324045407636739</v>
+        <v>0.4158926728586171</v>
       </c>
     </row>
     <row r="854">
@@ -59631,7 +59631,7 @@
         </is>
       </c>
       <c r="G856" s="8" t="n">
-        <v>0.6016511867905057</v>
+        <v>0.5830753353973168</v>
       </c>
     </row>
     <row r="857">
@@ -59697,7 +59697,7 @@
         </is>
       </c>
       <c r="G858" s="8" t="n">
-        <v>-0.003095975232198143</v>
+        <v>-0.02373581011351909</v>
       </c>
     </row>
     <row r="859">
@@ -59730,7 +59730,7 @@
         </is>
       </c>
       <c r="G859" s="8" t="n">
-        <v>-0.05604657999485445</v>
+        <v>-0.02594749073835854</v>
       </c>
     </row>
     <row r="860">
@@ -60093,7 +60093,7 @@
         </is>
       </c>
       <c r="G870" s="8" t="n">
-        <v>0.389010989010989</v>
+        <v>0.5560439560439561</v>
       </c>
     </row>
     <row r="871">
@@ -60720,7 +60720,7 @@
         </is>
       </c>
       <c r="G889" s="8" t="n">
-        <v>0.8065934065934066</v>
+        <v>0.6571428571428571</v>
       </c>
     </row>
     <row r="890">
@@ -60984,7 +60984,7 @@
         </is>
       </c>
       <c r="G897" s="8" t="n">
-        <v>0.9208791208791208</v>
+        <v>0.7978021978021979</v>
       </c>
     </row>
     <row r="898">
@@ -61215,7 +61215,7 @@
         </is>
       </c>
       <c r="G904" s="8" t="n">
-        <v>0.2439560439560439</v>
+        <v>0.3582417582417582</v>
       </c>
     </row>
     <row r="905">
@@ -61413,7 +61413,7 @@
         </is>
       </c>
       <c r="G910" s="8" t="n">
-        <v>0.2395604395604396</v>
+        <v>0.3450549450549451</v>
       </c>
     </row>
     <row r="911">
@@ -61578,7 +61578,7 @@
         </is>
       </c>
       <c r="G915" s="8" t="n">
-        <v>-0.03736263736263736</v>
+        <v>0.09010989010989011</v>
       </c>
     </row>
     <row r="916">
@@ -61710,7 +61710,7 @@
         </is>
       </c>
       <c r="G919" s="8" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.1868131868131868</v>
       </c>
     </row>
     <row r="920">
@@ -61809,7 +61809,7 @@
         </is>
       </c>
       <c r="G922" s="8" t="n">
-        <v>0.09010989010989011</v>
+        <v>0.2483516483516484</v>
       </c>
     </row>
     <row r="923">
@@ -61875,7 +61875,7 @@
         </is>
       </c>
       <c r="G924" s="8" t="n">
-        <v>-0.1523193653310294</v>
+        <v>-0.03311290550674552</v>
       </c>
     </row>
     <row r="925">
@@ -61908,7 +61908,7 @@
         </is>
       </c>
       <c r="G925" s="8" t="n">
-        <v>-0.01601281538050871</v>
+        <v>-0.100651982391769</v>
       </c>
     </row>
     <row r="926">
@@ -62007,7 +62007,7 @@
         </is>
       </c>
       <c r="G928" s="8" t="n">
-        <v>0.2351648351648352</v>
+        <v>0.1912087912087912</v>
       </c>
     </row>
     <row r="929">
@@ -62271,7 +62271,7 @@
         </is>
       </c>
       <c r="G936" s="8" t="n">
-        <v>0.1516483516483516</v>
+        <v>0.1428571428571428</v>
       </c>
     </row>
     <row r="937">
@@ -62337,7 +62337,7 @@
         </is>
       </c>
       <c r="G938" s="8" t="n">
-        <v>0.2087912087912088</v>
+        <v>0.1824175824175824</v>
       </c>
     </row>
     <row r="939">
@@ -62601,7 +62601,7 @@
         </is>
       </c>
       <c r="G946" s="8" t="n">
-        <v>0.01978021978021978</v>
+        <v>0.04175824175824176</v>
       </c>
     </row>
     <row r="947">
@@ -62634,7 +62634,7 @@
         </is>
       </c>
       <c r="G947" s="8" t="n">
-        <v>0.2791208791208791</v>
+        <v>0.2483516483516484</v>
       </c>
     </row>
     <row r="948">
@@ -62898,7 +62898,7 @@
         </is>
       </c>
       <c r="G955" s="8" t="n">
-        <v>0.3934065934065934</v>
+        <v>0.4021978021978022</v>
       </c>
     </row>
     <row r="956">
@@ -62931,7 +62931,7 @@
         </is>
       </c>
       <c r="G956" s="8" t="n">
-        <v>0.2615384615384616</v>
+        <v>0.2659340659340659</v>
       </c>
     </row>
     <row r="957">
@@ -62964,7 +62964,7 @@
         </is>
       </c>
       <c r="G957" s="8" t="n">
-        <v>0.002197802197802198</v>
+        <v>0.04175824175824176</v>
       </c>
     </row>
     <row r="958">
@@ -62997,7 +62997,7 @@
         </is>
       </c>
       <c r="G958" s="8" t="n">
-        <v>0.04615384615384616</v>
+        <v>0.07692307692307693</v>
       </c>
     </row>
     <row r="959">
@@ -63030,7 +63030,7 @@
         </is>
       </c>
       <c r="G959" s="8" t="n">
-        <v>-0.08571428571428572</v>
+        <v>-0.06373626373626373</v>
       </c>
     </row>
     <row r="960">
@@ -63063,7 +63063,7 @@
         </is>
       </c>
       <c r="G960" s="8" t="n">
-        <v>0.03296703296703297</v>
+        <v>0.06813186813186813</v>
       </c>
     </row>
     <row r="961">
@@ -63096,7 +63096,7 @@
         </is>
       </c>
       <c r="G961" s="8" t="n">
-        <v>0.3450549450549451</v>
+        <v>0.3054945054945055</v>
       </c>
     </row>
     <row r="962">
@@ -63162,7 +63162,7 @@
         </is>
       </c>
       <c r="G963" s="8" t="n">
-        <v>0.5208791208791209</v>
+        <v>0.4549450549450549</v>
       </c>
     </row>
     <row r="964">
@@ -63393,7 +63393,7 @@
         </is>
       </c>
       <c r="G970" s="8" t="n">
-        <v>-0.02417582417582418</v>
+        <v>-0.1120879120879121</v>
       </c>
     </row>
     <row r="971">
@@ -63591,7 +63591,7 @@
         </is>
       </c>
       <c r="G976" s="8" t="n">
-        <v>-0.2263736263736264</v>
+        <v>-0.2791208791208791</v>
       </c>
     </row>
     <row r="977">
@@ -63756,7 +63756,7 @@
         </is>
       </c>
       <c r="G981" s="8" t="n">
-        <v>-0.01978021978021978</v>
+        <v>-0.02857142857142857</v>
       </c>
     </row>
     <row r="982">
@@ -63888,7 +63888,7 @@
         </is>
       </c>
       <c r="G985" s="8" t="n">
-        <v>-0.1824175824175824</v>
+        <v>-0.2263736263736264</v>
       </c>
     </row>
     <row r="986">
@@ -63987,7 +63987,7 @@
         </is>
       </c>
       <c r="G988" s="8" t="n">
-        <v>-0.2175824175824176</v>
+        <v>-0.2439560439560439</v>
       </c>
     </row>
     <row r="989">
@@ -64053,7 +64053,7 @@
         </is>
       </c>
       <c r="G990" s="8" t="n">
-        <v>0.3142857142857143</v>
+        <v>0.4021978021978022</v>
       </c>
     </row>
     <row r="991">
@@ -64086,7 +64086,7 @@
         </is>
       </c>
       <c r="G991" s="8" t="n">
-        <v>-0.4285714285714285</v>
+        <v>-0.4681318681318681</v>
       </c>
     </row>
     <row r="992">
@@ -64449,7 +64449,7 @@
         </is>
       </c>
       <c r="G1002" s="8" t="n">
-        <v>0.1454545454545454</v>
+        <v>0.07272727272727272</v>
       </c>
     </row>
     <row r="1003">
@@ -64779,7 +64779,7 @@
         </is>
       </c>
       <c r="G1012" s="8" t="n">
-        <v>0.02727272727272727</v>
+        <v>0.09090909090909091</v>
       </c>
     </row>
     <row r="1013">
@@ -65076,7 +65076,7 @@
         </is>
       </c>
       <c r="G1021" s="8" t="n">
-        <v>0.2454545454545455</v>
+        <v>0.2090909090909091</v>
       </c>
     </row>
     <row r="1022">
@@ -65340,7 +65340,7 @@
         </is>
       </c>
       <c r="G1029" s="8" t="n">
-        <v>0.9090909090909091</v>
+        <v>0.8454545454545455</v>
       </c>
     </row>
     <row r="1030">
@@ -65571,7 +65571,7 @@
         </is>
       </c>
       <c r="G1036" s="8" t="n">
-        <v>0.3363636363636364</v>
+        <v>0.2545454545454545</v>
       </c>
     </row>
     <row r="1037">
@@ -65769,7 +65769,7 @@
         </is>
       </c>
       <c r="G1042" s="8" t="n">
-        <v>0.3545454545454546</v>
+        <v>0.2545454545454545</v>
       </c>
     </row>
     <row r="1043">
@@ -65934,7 +65934,7 @@
         </is>
       </c>
       <c r="G1047" s="8" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="1048">
@@ -66066,7 +66066,7 @@
         </is>
       </c>
       <c r="G1051" s="8" t="n">
-        <v>0.3727272727272727</v>
+        <v>0.3090909090909091</v>
       </c>
     </row>
     <row r="1052">
@@ -66165,7 +66165,7 @@
         </is>
       </c>
       <c r="G1054" s="8" t="n">
-        <v>0.5545454545454546</v>
+        <v>0.4181818181818182</v>
       </c>
     </row>
     <row r="1055">
@@ -66231,7 +66231,7 @@
         </is>
       </c>
       <c r="G1056" s="8" t="n">
-        <v>-0.06363636363636363</v>
+        <v>-0.09090909090909091</v>
       </c>
     </row>
     <row r="1057">
@@ -66264,7 +66264,7 @@
         </is>
       </c>
       <c r="G1057" s="8" t="n">
-        <v>-0.2180999027225083</v>
+        <v>-0.1437476631580168</v>
       </c>
     </row>
     <row r="1058">
@@ -66627,7 +66627,7 @@
         </is>
       </c>
       <c r="G1068" s="8" t="n">
-        <v>0.2272727272727273</v>
+        <v>0.2090909090909091</v>
       </c>
     </row>
     <row r="1069">
@@ -66957,7 +66957,7 @@
         </is>
       </c>
       <c r="G1078" s="8" t="n">
-        <v>0.1727272727272727</v>
+        <v>0.2090909090909091</v>
       </c>
     </row>
     <row r="1079">
@@ -67254,7 +67254,7 @@
         </is>
       </c>
       <c r="G1087" s="8" t="n">
-        <v>-0.02727272727272727</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="1088">
@@ -67518,7 +67518,7 @@
         </is>
       </c>
       <c r="G1095" s="8" t="n">
-        <v>0.8363636363636363</v>
+        <v>0.8545454545454545</v>
       </c>
     </row>
     <row r="1096">
@@ -67749,7 +67749,7 @@
         </is>
       </c>
       <c r="G1102" s="8" t="n">
-        <v>0.2454545454545455</v>
+        <v>0.1363636363636364</v>
       </c>
     </row>
     <row r="1103">
@@ -67947,7 +67947,7 @@
         </is>
       </c>
       <c r="G1108" s="8" t="n">
-        <v>0.02727272727272727</v>
+        <v>-0.06363636363636363</v>
       </c>
     </row>
     <row r="1109">
@@ -68112,7 +68112,7 @@
         </is>
       </c>
       <c r="G1113" s="8" t="n">
-        <v>0.05454545454545454</v>
+        <v>-0.03636363636363636</v>
       </c>
     </row>
     <row r="1114">
@@ -68244,7 +68244,7 @@
         </is>
       </c>
       <c r="G1117" s="8" t="n">
-        <v>0.3727272727272727</v>
+        <v>0.2454545454545455</v>
       </c>
     </row>
     <row r="1118">
@@ -68343,7 +68343,7 @@
         </is>
       </c>
       <c r="G1120" s="8" t="n">
-        <v>0.4909090909090909</v>
+        <v>0.3636363636363636</v>
       </c>
     </row>
     <row r="1121">
@@ -68409,7 +68409,7 @@
         </is>
       </c>
       <c r="G1122" s="8" t="n">
-        <v>-0.2</v>
+        <v>-0.1272727272727273</v>
       </c>
     </row>
     <row r="1123">
@@ -68442,7 +68442,7 @@
         </is>
       </c>
       <c r="G1123" s="8" t="n">
-        <v>-0.01818181818181818</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1124">
@@ -68541,7 +68541,7 @@
         </is>
       </c>
       <c r="G1126" s="8" t="n">
-        <v>0.356140350877193</v>
+        <v>0.3684210526315789</v>
       </c>
     </row>
     <row r="1127">
@@ -68871,7 +68871,7 @@
         </is>
       </c>
       <c r="G1136" s="8" t="n">
-        <v>0.5140350877192983</v>
+        <v>0.5280701754385965</v>
       </c>
     </row>
     <row r="1137">
@@ -69135,7 +69135,7 @@
         </is>
       </c>
       <c r="G1144" s="8" t="n">
-        <v>0.2456140350877193</v>
+        <v>0.2614035087719298</v>
       </c>
     </row>
     <row r="1145">
@@ -69168,7 +69168,7 @@
         </is>
       </c>
       <c r="G1145" s="8" t="n">
-        <v>0.3894736842105263</v>
+        <v>0.3964912280701754</v>
       </c>
     </row>
     <row r="1146">
@@ -69432,7 +69432,7 @@
         </is>
       </c>
       <c r="G1153" s="8" t="n">
-        <v>0.1403508771929824</v>
+        <v>0.1982456140350877</v>
       </c>
     </row>
     <row r="1154">
@@ -69465,7 +69465,7 @@
         </is>
       </c>
       <c r="G1154" s="8" t="n">
-        <v>0.04035087719298246</v>
+        <v>0.05087719298245614</v>
       </c>
     </row>
     <row r="1155">
@@ -69498,7 +69498,7 @@
         </is>
       </c>
       <c r="G1155" s="8" t="n">
-        <v>-0.1456140350877193</v>
+        <v>-0.1333333333333333</v>
       </c>
     </row>
     <row r="1156">
@@ -69531,7 +69531,7 @@
         </is>
       </c>
       <c r="G1156" s="8" t="n">
-        <v>0.2210526315789474</v>
+        <v>0.212280701754386</v>
       </c>
     </row>
     <row r="1157">
@@ -69564,7 +69564,7 @@
         </is>
       </c>
       <c r="G1157" s="8" t="n">
-        <v>0.07017543859649122</v>
+        <v>0.06140350877192982</v>
       </c>
     </row>
     <row r="1158">
@@ -69597,7 +69597,7 @@
         </is>
       </c>
       <c r="G1158" s="8" t="n">
-        <v>0.4807017543859649</v>
+        <v>0.4824561403508772</v>
       </c>
     </row>
     <row r="1159">
@@ -69630,7 +69630,7 @@
         </is>
       </c>
       <c r="G1159" s="8" t="n">
-        <v>-0.03508771929824561</v>
+        <v>-0.04210526315789474</v>
       </c>
     </row>
     <row r="1160">
@@ -69663,7 +69663,7 @@
         </is>
       </c>
       <c r="G1160" s="8" t="n">
-        <v>0.2754385964912281</v>
+        <v>0.2859649122807018</v>
       </c>
     </row>
     <row r="1161">
@@ -69696,7 +69696,7 @@
         </is>
       </c>
       <c r="G1161" s="8" t="n">
-        <v>0.8719298245614036</v>
+        <v>0.8649122807017544</v>
       </c>
     </row>
     <row r="1162">
@@ -69927,7 +69927,7 @@
         </is>
       </c>
       <c r="G1168" s="8" t="n">
-        <v>-0.1421052631578947</v>
+        <v>-0.1789473684210526</v>
       </c>
     </row>
     <row r="1169">
@@ -70125,7 +70125,7 @@
         </is>
       </c>
       <c r="G1174" s="8" t="n">
-        <v>-0.3192982456140351</v>
+        <v>-0.3456140350877193</v>
       </c>
     </row>
     <row r="1175">
@@ -70290,7 +70290,7 @@
         </is>
       </c>
       <c r="G1179" s="8" t="n">
-        <v>0.06842105263157895</v>
+        <v>0.04210526315789474</v>
       </c>
     </row>
     <row r="1180">
@@ -70422,7 +70422,7 @@
         </is>
       </c>
       <c r="G1183" s="8" t="n">
-        <v>0.1701754385964912</v>
+        <v>0.1368421052631579</v>
       </c>
     </row>
     <row r="1184">
@@ -70521,7 +70521,7 @@
         </is>
       </c>
       <c r="G1186" s="8" t="n">
-        <v>0.3842105263157894</v>
+        <v>0.3508771929824561</v>
       </c>
     </row>
     <row r="1187">
@@ -70587,7 +70587,7 @@
         </is>
       </c>
       <c r="G1188" s="8" t="n">
-        <v>-0.356140350877193</v>
+        <v>-0.3491228070175438</v>
       </c>
     </row>
     <row r="1189">
@@ -70620,7 +70620,7 @@
         </is>
       </c>
       <c r="G1189" s="8" t="n">
-        <v>0.2175438596491228</v>
+        <v>0.2368421052631579</v>
       </c>
     </row>
     <row r="1190">
@@ -70719,7 +70719,7 @@
         </is>
       </c>
       <c r="G1192" s="8" t="n">
-        <v>0.1904761904761905</v>
+        <v>0.2857142857142857</v>
       </c>
     </row>
     <row r="1193">
@@ -71049,7 +71049,7 @@
         </is>
       </c>
       <c r="G1202" s="8" t="n">
-        <v>0.3809523809523809</v>
+        <v>0.4523809523809524</v>
       </c>
     </row>
     <row r="1203">
@@ -71346,7 +71346,7 @@
         </is>
       </c>
       <c r="G1211" s="8" t="n">
-        <v>0.6904761904761905</v>
+        <v>0.7142857142857143</v>
       </c>
     </row>
     <row r="1212">
@@ -71643,7 +71643,7 @@
         </is>
       </c>
       <c r="G1220" s="8" t="n">
-        <v>-0.4047619047619048</v>
+        <v>-0.3095238095238095</v>
       </c>
     </row>
     <row r="1221">
@@ -71676,7 +71676,7 @@
         </is>
       </c>
       <c r="G1221" s="8" t="n">
-        <v>-0.6666666666666666</v>
+        <v>-0.5952380952380952</v>
       </c>
     </row>
     <row r="1222">
@@ -71709,7 +71709,7 @@
         </is>
       </c>
       <c r="G1222" s="8" t="n">
-        <v>0.6428571428571429</v>
+        <v>0.5714285714285714</v>
       </c>
     </row>
     <row r="1223">
@@ -71742,7 +71742,7 @@
         </is>
       </c>
       <c r="G1223" s="8" t="n">
-        <v>0.5952380952380952</v>
+        <v>0.4761904761904762</v>
       </c>
     </row>
     <row r="1224">
@@ -71775,7 +71775,7 @@
         </is>
       </c>
       <c r="G1224" s="8" t="n">
-        <v>0.4523809523809524</v>
+        <v>0.4761904761904762</v>
       </c>
     </row>
     <row r="1225">
@@ -71808,7 +71808,7 @@
         </is>
       </c>
       <c r="G1225" s="8" t="n">
-        <v>-0.2380952380952381</v>
+        <v>-0.2857142857142857</v>
       </c>
     </row>
     <row r="1226">
@@ -71841,7 +71841,7 @@
         </is>
       </c>
       <c r="G1226" s="8" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.5476190476190477</v>
       </c>
     </row>
     <row r="1227">
@@ -71874,7 +71874,7 @@
         </is>
       </c>
       <c r="G1227" s="8" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.7857142857142857</v>
       </c>
     </row>
     <row r="1228">
@@ -72897,7 +72897,7 @@
         </is>
       </c>
       <c r="G1258" s="8" t="n">
-        <v>0.5799120234604106</v>
+        <v>0.5824780058651027</v>
       </c>
     </row>
     <row r="1259">
@@ -73161,7 +73161,7 @@
         </is>
       </c>
       <c r="G1266" s="8" t="n">
-        <v>0.624633431085044</v>
+        <v>0.6374633431085044</v>
       </c>
     </row>
     <row r="1267">
@@ -73227,7 +73227,7 @@
         </is>
       </c>
       <c r="G1268" s="8" t="n">
-        <v>0.5018328445747801</v>
+        <v>0.5040322580645161</v>
       </c>
     </row>
     <row r="1269">
@@ -73491,7 +73491,7 @@
         </is>
       </c>
       <c r="G1276" s="8" t="n">
-        <v>0.4952346041055719</v>
+        <v>0.4186217008797654</v>
       </c>
     </row>
     <row r="1277">
@@ -73524,7 +73524,7 @@
         </is>
       </c>
       <c r="G1277" s="8" t="n">
-        <v>0.782258064516129</v>
+        <v>0.782991202346041</v>
       </c>
     </row>
     <row r="1278">
@@ -73788,7 +73788,7 @@
         </is>
       </c>
       <c r="G1285" s="8" t="n">
-        <v>0.7382697947214076</v>
+        <v>0.625366568914956</v>
       </c>
     </row>
     <row r="1286">
@@ -73821,7 +73821,7 @@
         </is>
       </c>
       <c r="G1286" s="8" t="n">
-        <v>-0.02932551319648094</v>
+        <v>-0.02675953079178886</v>
       </c>
     </row>
     <row r="1287">
@@ -73854,7 +73854,7 @@
         </is>
       </c>
       <c r="G1287" s="8" t="n">
-        <v>0.08431085043988269</v>
+        <v>0.08541055718475073</v>
       </c>
     </row>
     <row r="1288">
@@ -73887,7 +73887,7 @@
         </is>
       </c>
       <c r="G1288" s="8" t="n">
-        <v>-0.2481671554252199</v>
+        <v>-0.2459677419354839</v>
       </c>
     </row>
     <row r="1289">
@@ -73920,7 +73920,7 @@
         </is>
       </c>
       <c r="G1289" s="8" t="n">
-        <v>-0.2404692082111437</v>
+        <v>-0.2375366568914956</v>
       </c>
     </row>
     <row r="1290">
@@ -73953,7 +73953,7 @@
         </is>
       </c>
       <c r="G1290" s="8" t="n">
-        <v>-0.05498533724340176</v>
+        <v>-0.05205278592375367</v>
       </c>
     </row>
     <row r="1291">
@@ -73986,7 +73986,7 @@
         </is>
       </c>
       <c r="G1291" s="8" t="n">
-        <v>-0.4708471163661926</v>
+        <v>-0.4686468961962572</v>
       </c>
     </row>
     <row r="1292">
@@ -74019,7 +74019,7 @@
         </is>
       </c>
       <c r="G1292" s="8" t="n">
-        <v>-0.3028464841094991</v>
+        <v>-0.2983791727274291</v>
       </c>
     </row>
     <row r="1293">
@@ -74052,7 +74052,7 @@
         </is>
       </c>
       <c r="G1293" s="8" t="n">
-        <v>0.9699413489736071</v>
+        <v>0.9138563049853372</v>
       </c>
     </row>
     <row r="1294">
@@ -74283,7 +74283,7 @@
         </is>
       </c>
       <c r="G1300" s="8" t="n">
-        <v>0.1066715542521994</v>
+        <v>0.218475073313783</v>
       </c>
     </row>
     <row r="1301">
@@ -74481,7 +74481,7 @@
         </is>
       </c>
       <c r="G1306" s="8" t="n">
-        <v>0.2049120234604106</v>
+        <v>0.3005865102639296</v>
       </c>
     </row>
     <row r="1307">
@@ -74646,7 +74646,7 @@
         </is>
       </c>
       <c r="G1311" s="8" t="n">
-        <v>-0.1370967741935484</v>
+        <v>-0.005131964809384164</v>
       </c>
     </row>
     <row r="1312">
@@ -74778,7 +74778,7 @@
         </is>
       </c>
       <c r="G1315" s="8" t="n">
-        <v>-0.1352639296187683</v>
+        <v>-0.01502932551319648</v>
       </c>
     </row>
     <row r="1316">
@@ -74877,7 +74877,7 @@
         </is>
       </c>
       <c r="G1318" s="8" t="n">
-        <v>0.05058651026392962</v>
+        <v>0.1733870967741936</v>
       </c>
     </row>
     <row r="1319">
@@ -74943,7 +74943,7 @@
         </is>
       </c>
       <c r="G1320" s="8" t="n">
-        <v>-0.4242757894358917</v>
+        <v>-0.3039970868127521</v>
       </c>
     </row>
     <row r="1321">
@@ -74976,7 +74976,7 @@
         </is>
       </c>
       <c r="G1321" s="8" t="n">
-        <v>-0.2611515778768453</v>
+        <v>-0.2280190184598257</v>
       </c>
     </row>
     <row r="1322">
@@ -75075,7 +75075,7 @@
         </is>
       </c>
       <c r="G1324" s="8" t="n">
-        <v>0.7096774193548387</v>
+        <v>0.7093108504398827</v>
       </c>
     </row>
     <row r="1325">
@@ -75339,7 +75339,7 @@
         </is>
       </c>
       <c r="G1332" s="8" t="n">
-        <v>0.656158357771261</v>
+        <v>0.5678152492668622</v>
       </c>
     </row>
     <row r="1333">
@@ -75405,7 +75405,7 @@
         </is>
       </c>
       <c r="G1334" s="8" t="n">
-        <v>0.4226539589442815</v>
+        <v>0.4241202346041056</v>
       </c>
     </row>
     <row r="1335">
@@ -75669,7 +75669,7 @@
         </is>
       </c>
       <c r="G1342" s="8" t="n">
-        <v>0.3328445747800586</v>
+        <v>0.248533724340176</v>
       </c>
     </row>
     <row r="1343">
@@ -75702,7 +75702,7 @@
         </is>
       </c>
       <c r="G1343" s="8" t="n">
-        <v>0.6455278592375366</v>
+        <v>0.6466275659824047</v>
       </c>
     </row>
     <row r="1344">
@@ -75966,7 +75966,7 @@
         </is>
       </c>
       <c r="G1351" s="8" t="n">
-        <v>0.6532258064516129</v>
+        <v>0.5612170087976539</v>
       </c>
     </row>
     <row r="1352">
@@ -75999,7 +75999,7 @@
         </is>
       </c>
       <c r="G1352" s="8" t="n">
-        <v>0.2423020527859238</v>
+        <v>0.2371700879765396</v>
       </c>
     </row>
     <row r="1353">
@@ -76032,7 +76032,7 @@
         </is>
       </c>
       <c r="G1353" s="8" t="n">
-        <v>0.2639296187683284</v>
+        <v>0.2624633431085044</v>
       </c>
     </row>
     <row r="1354">
@@ -76065,7 +76065,7 @@
         </is>
       </c>
       <c r="G1354" s="8" t="n">
-        <v>0.2628299120234604</v>
+        <v>0.2664956011730205</v>
       </c>
     </row>
     <row r="1355">
@@ -76098,7 +76098,7 @@
         </is>
       </c>
       <c r="G1355" s="8" t="n">
-        <v>0.1612903225806452</v>
+        <v>0.1609237536656891</v>
       </c>
     </row>
     <row r="1356">
@@ -76131,7 +76131,7 @@
         </is>
       </c>
       <c r="G1356" s="8" t="n">
-        <v>0.2580645161290323</v>
+        <v>0.2587976539589443</v>
       </c>
     </row>
     <row r="1357">
@@ -76164,7 +76164,7 @@
         </is>
       </c>
       <c r="G1357" s="8" t="n">
-        <v>0.2104105571847507</v>
+        <v>0.2159090909090909</v>
       </c>
     </row>
     <row r="1358">
@@ -76197,7 +76197,7 @@
         </is>
       </c>
       <c r="G1358" s="8" t="n">
-        <v>-0.1818018254317112</v>
+        <v>-0.1784963376965892</v>
       </c>
     </row>
     <row r="1359">
@@ -76230,7 +76230,7 @@
         </is>
       </c>
       <c r="G1359" s="8" t="n">
-        <v>0.8925953079178885</v>
+        <v>0.8255131964809385</v>
       </c>
     </row>
     <row r="1360">
@@ -76461,7 +76461,7 @@
         </is>
       </c>
       <c r="G1366" s="8" t="n">
-        <v>0.2950879765395895</v>
+        <v>0.3405425219941349</v>
       </c>
     </row>
     <row r="1367">
@@ -76659,7 +76659,7 @@
         </is>
       </c>
       <c r="G1372" s="8" t="n">
-        <v>0.3174486803519062</v>
+        <v>0.3060850439882698</v>
       </c>
     </row>
     <row r="1373">
@@ -76824,7 +76824,7 @@
         </is>
       </c>
       <c r="G1377" s="8" t="n">
-        <v>0.3024193548387097</v>
+        <v>0.2888563049853373</v>
       </c>
     </row>
     <row r="1378">
@@ -76956,7 +76956,7 @@
         </is>
       </c>
       <c r="G1381" s="8" t="n">
-        <v>0.2034457478005865</v>
+        <v>0.1953812316715542</v>
       </c>
     </row>
     <row r="1382">
@@ -77055,7 +77055,7 @@
         </is>
       </c>
       <c r="G1384" s="8" t="n">
-        <v>0.2591642228739003</v>
+        <v>0.3031524926686217</v>
       </c>
     </row>
     <row r="1385">
@@ -77121,7 +77121,7 @@
         </is>
       </c>
       <c r="G1386" s="8" t="n">
-        <v>0.07441348973607038</v>
+        <v>0.02016129032258064</v>
       </c>
     </row>
     <row r="1387">
@@ -77154,7 +77154,7 @@
         </is>
       </c>
       <c r="G1387" s="8" t="n">
-        <v>-0.1592143259083774</v>
+        <v>-0.1590306877008706</v>
       </c>
     </row>
     <row r="1388">
@@ -77253,7 +77253,7 @@
         </is>
       </c>
       <c r="G1390" s="8" t="n">
-        <v>0.9054187192118227</v>
+        <v>0.903448275862069</v>
       </c>
     </row>
     <row r="1391">
@@ -77517,7 +77517,7 @@
         </is>
       </c>
       <c r="G1398" s="8" t="n">
-        <v>0.90935960591133</v>
+        <v>0.8729064039408867</v>
       </c>
     </row>
     <row r="1399">
@@ -77583,7 +77583,7 @@
         </is>
       </c>
       <c r="G1400" s="8" t="n">
-        <v>0.8177339901477833</v>
+        <v>0.8123152709359606</v>
       </c>
     </row>
     <row r="1401">
@@ -77847,7 +77847,7 @@
         </is>
       </c>
       <c r="G1408" s="8" t="n">
-        <v>0.8078817733990148</v>
+        <v>0.7541871921182266</v>
       </c>
     </row>
     <row r="1409">
@@ -77880,7 +77880,7 @@
         </is>
       </c>
       <c r="G1409" s="8" t="n">
-        <v>0.9024630541871921</v>
+        <v>0.9014778325123153</v>
       </c>
     </row>
     <row r="1410">
@@ -78144,7 +78144,7 @@
         </is>
       </c>
       <c r="G1417" s="8" t="n">
-        <v>0.8945812807881773</v>
+        <v>0.8660098522167488</v>
       </c>
     </row>
     <row r="1418">
@@ -78177,7 +78177,7 @@
         </is>
       </c>
       <c r="G1418" s="8" t="n">
-        <v>-0.1305418719211823</v>
+        <v>-0.1241379310344828</v>
       </c>
     </row>
     <row r="1419">
@@ -78210,7 +78210,7 @@
         </is>
       </c>
       <c r="G1419" s="8" t="n">
-        <v>0.02019704433497537</v>
+        <v>0.02413793103448276</v>
       </c>
     </row>
     <row r="1420">
@@ -78243,7 +78243,7 @@
         </is>
       </c>
       <c r="G1420" s="8" t="n">
-        <v>-0.2605911330049261</v>
+        <v>-0.2556650246305419</v>
       </c>
     </row>
     <row r="1421">
@@ -78276,7 +78276,7 @@
         </is>
       </c>
       <c r="G1421" s="8" t="n">
-        <v>-0.5300492610837438</v>
+        <v>-0.5226600985221674</v>
       </c>
     </row>
     <row r="1422">
@@ -78309,7 +78309,7 @@
         </is>
       </c>
       <c r="G1422" s="8" t="n">
-        <v>0.0561576354679803</v>
+        <v>0.05862068965517241</v>
       </c>
     </row>
     <row r="1423">
@@ -78342,7 +78342,7 @@
         </is>
       </c>
       <c r="G1423" s="8" t="n">
-        <v>-0.6137931034482759</v>
+        <v>-0.6093596059113301</v>
       </c>
     </row>
     <row r="1424">
@@ -78375,7 +78375,7 @@
         </is>
       </c>
       <c r="G1424" s="8" t="n">
-        <v>-0.4831326349547782</v>
+        <v>-0.4710606065956791</v>
       </c>
     </row>
     <row r="1425">
@@ -78408,7 +78408,7 @@
         </is>
       </c>
       <c r="G1425" s="8" t="n">
-        <v>0.9852216748768473</v>
+        <v>0.9768472906403941</v>
       </c>
     </row>
     <row r="1426">
@@ -78639,7 +78639,7 @@
         </is>
       </c>
       <c r="G1432" s="8" t="n">
-        <v>-0.1068965517241379</v>
+        <v>-0.06650246305418719</v>
       </c>
     </row>
     <row r="1433">
@@ -78837,7 +78837,7 @@
         </is>
       </c>
       <c r="G1438" s="8" t="n">
-        <v>0.02758620689655172</v>
+        <v>0.04384236453201971</v>
       </c>
     </row>
     <row r="1439">
@@ -79002,7 +79002,7 @@
         </is>
       </c>
       <c r="G1443" s="8" t="n">
-        <v>-0.2532019704433497</v>
+        <v>-0.225615763546798</v>
       </c>
     </row>
     <row r="1444">
@@ -79134,7 +79134,7 @@
         </is>
       </c>
       <c r="G1447" s="8" t="n">
-        <v>-0.5246305418719212</v>
+        <v>-0.4866995073891626</v>
       </c>
     </row>
     <row r="1448">
@@ -79233,7 +79233,7 @@
         </is>
       </c>
       <c r="G1450" s="8" t="n">
-        <v>0.0354679802955665</v>
+        <v>0.03448275862068965</v>
       </c>
     </row>
     <row r="1451">
@@ -79299,7 +79299,7 @@
         </is>
       </c>
       <c r="G1452" s="8" t="n">
-        <v>-0.6738916256157635</v>
+        <v>-0.6502463054187192</v>
       </c>
     </row>
     <row r="1453">
@@ -79332,7 +79332,7 @@
         </is>
       </c>
       <c r="G1453" s="8" t="n">
-        <v>-0.4816236314098908</v>
+        <v>-0.4260420008398721</v>
       </c>
     </row>
     <row r="1454">
@@ -79431,7 +79431,7 @@
         </is>
       </c>
       <c r="G1456" s="8" t="n">
-        <v>0.8880986249407302</v>
+        <v>0.8911806543385491</v>
       </c>
     </row>
     <row r="1457">
@@ -79695,7 +79695,7 @@
         </is>
       </c>
       <c r="G1464" s="8" t="n">
-        <v>0.873162636320531</v>
+        <v>0.8359412043622569</v>
       </c>
     </row>
     <row r="1465">
@@ -79761,7 +79761,7 @@
         </is>
       </c>
       <c r="G1466" s="8" t="n">
-        <v>0.8715030820293979</v>
+        <v>0.8745851114272167</v>
       </c>
     </row>
     <row r="1467">
@@ -80025,7 +80025,7 @@
         </is>
       </c>
       <c r="G1474" s="8" t="n">
-        <v>0.8300142247510669</v>
+        <v>0.7788051209103841</v>
       </c>
     </row>
     <row r="1475">
@@ -80058,7 +80058,7 @@
         </is>
       </c>
       <c r="G1475" s="8" t="n">
-        <v>0.8843053579895686</v>
+        <v>0.8857278330962541</v>
       </c>
     </row>
     <row r="1476">
@@ -80322,7 +80322,7 @@
         </is>
       </c>
       <c r="G1483" s="8" t="n">
-        <v>0.8506401137980085</v>
+        <v>0.8243243243243243</v>
       </c>
     </row>
     <row r="1484">
@@ -80355,7 +80355,7 @@
         </is>
       </c>
       <c r="G1484" s="8" t="n">
-        <v>-0.3691322901849218</v>
+        <v>-0.3658131816026553</v>
       </c>
     </row>
     <row r="1485">
@@ -80388,7 +80388,7 @@
         </is>
       </c>
       <c r="G1485" s="8" t="n">
-        <v>-0.4006638217164533</v>
+        <v>-0.3982930298719772</v>
       </c>
     </row>
     <row r="1486">
@@ -80421,7 +80421,7 @@
         </is>
       </c>
       <c r="G1486" s="8" t="n">
-        <v>-0.4990516832622096</v>
+        <v>-0.4995258416311048</v>
       </c>
     </row>
     <row r="1487">
@@ -80454,7 +80454,7 @@
         </is>
       </c>
       <c r="G1487" s="8" t="n">
-        <v>-0.6884779516358464</v>
+        <v>-0.6882408724513988</v>
       </c>
     </row>
     <row r="1488">
@@ -80487,7 +80487,7 @@
         </is>
       </c>
       <c r="G1488" s="8" t="n">
-        <v>-0.1166429587482219</v>
+        <v>-0.1145092460881935</v>
       </c>
     </row>
     <row r="1489">
@@ -80553,7 +80553,7 @@
         </is>
       </c>
       <c r="G1490" s="8" t="n">
-        <v>-0.367456222673329</v>
+        <v>-0.3629461010772093</v>
       </c>
     </row>
     <row r="1491">
@@ -80586,7 +80586,7 @@
         </is>
       </c>
       <c r="G1491" s="8" t="n">
-        <v>0.9786628733997155</v>
+        <v>0.9682313892840209</v>
       </c>
     </row>
     <row r="1492">
@@ -80817,7 +80817,7 @@
         </is>
       </c>
       <c r="G1498" s="8" t="n">
-        <v>-0.3807491702228544</v>
+        <v>-0.3319108582266477</v>
       </c>
     </row>
     <row r="1499">
@@ -81015,7 +81015,7 @@
         </is>
       </c>
       <c r="G1504" s="8" t="n">
-        <v>-0.4231863442389758</v>
+        <v>-0.387624466571835</v>
       </c>
     </row>
     <row r="1505">
@@ -81180,7 +81180,7 @@
         </is>
       </c>
       <c r="G1509" s="8" t="n">
-        <v>-0.5146989094357516</v>
+        <v>-0.4736842105263158</v>
       </c>
     </row>
     <row r="1510">
@@ -81312,7 +81312,7 @@
         </is>
       </c>
       <c r="G1513" s="8" t="n">
-        <v>-0.6699857752489331</v>
+        <v>-0.6263632053105738</v>
       </c>
     </row>
     <row r="1514">
@@ -81411,7 +81411,7 @@
         </is>
       </c>
       <c r="G1516" s="8" t="n">
-        <v>-0.1427216690374585</v>
+        <v>-0.1192508297771456</v>
       </c>
     </row>
     <row r="1517">
@@ -81477,7 +81477,7 @@
         </is>
       </c>
       <c r="G1518" s="8" t="n">
-        <v>-0.7804646752015173</v>
+        <v>-0.7351825509720247</v>
       </c>
     </row>
     <row r="1519">
@@ -81510,7 +81510,7 @@
         </is>
       </c>
       <c r="G1519" s="8" t="n">
-        <v>-0.3719663442694487</v>
+        <v>-0.3117918271843783</v>
       </c>
     </row>
     <row r="1520">
@@ -81609,7 +81609,7 @@
         </is>
       </c>
       <c r="G1522" s="8" t="n">
-        <v>0.8501311188811189</v>
+        <v>0.8496066433566434</v>
       </c>
     </row>
     <row r="1523">
@@ -81873,7 +81873,7 @@
         </is>
       </c>
       <c r="G1530" s="8" t="n">
-        <v>0.8475961538461538</v>
+        <v>0.8244755244755245</v>
       </c>
     </row>
     <row r="1531">
@@ -81939,7 +81939,7 @@
         </is>
       </c>
       <c r="G1532" s="8" t="n">
-        <v>0.8238636363636364</v>
+        <v>0.82381993006993</v>
       </c>
     </row>
     <row r="1533">
@@ -82203,7 +82203,7 @@
         </is>
       </c>
       <c r="G1540" s="8" t="n">
-        <v>0.8082167832167833</v>
+        <v>0.7687062937062937</v>
       </c>
     </row>
     <row r="1541">
@@ -82236,7 +82236,7 @@
         </is>
       </c>
       <c r="G1541" s="8" t="n">
-        <v>0.916215034965035</v>
+        <v>0.9156468531468531</v>
       </c>
     </row>
     <row r="1542">
@@ -82500,7 +82500,7 @@
         </is>
       </c>
       <c r="G1549" s="8" t="n">
-        <v>0.8995629370629371</v>
+        <v>0.8576048951048951</v>
       </c>
     </row>
     <row r="1550">
@@ -82533,7 +82533,7 @@
         </is>
       </c>
       <c r="G1550" s="8" t="n">
-        <v>-0.5025786713286713</v>
+        <v>-0.5018793706293706</v>
       </c>
     </row>
     <row r="1551">
@@ -82566,7 +82566,7 @@
         </is>
       </c>
       <c r="G1551" s="8" t="n">
-        <v>-0.4948426573426574</v>
+        <v>-0.4938374125874126</v>
       </c>
     </row>
     <row r="1552">
@@ -82599,7 +82599,7 @@
         </is>
       </c>
       <c r="G1552" s="8" t="n">
-        <v>-0.5277534965034965</v>
+        <v>-0.5278846153846154</v>
       </c>
     </row>
     <row r="1553">
@@ -82632,7 +82632,7 @@
         </is>
       </c>
       <c r="G1553" s="8" t="n">
-        <v>-0.6609265734265735</v>
+        <v>-0.6601835664335665</v>
       </c>
     </row>
     <row r="1554">
@@ -82665,7 +82665,7 @@
         </is>
       </c>
       <c r="G1554" s="8" t="n">
-        <v>-0.3708479020979021</v>
+        <v>-0.3707167832167832</v>
       </c>
     </row>
     <row r="1555">
@@ -82698,7 +82698,7 @@
         </is>
       </c>
       <c r="G1555" s="8" t="n">
-        <v>-0.4953013685398998</v>
+        <v>-0.496262949029476</v>
       </c>
     </row>
     <row r="1556">
@@ -82731,7 +82731,7 @@
         </is>
       </c>
       <c r="G1556" s="8" t="n">
-        <v>-0.3742523971133446</v>
+        <v>-0.3760719231770985</v>
       </c>
     </row>
     <row r="1557">
@@ -82764,7 +82764,7 @@
         </is>
       </c>
       <c r="G1557" s="8" t="n">
-        <v>0.9780157342657343</v>
+        <v>0.9586975524475524</v>
       </c>
     </row>
     <row r="1558">
@@ -82995,7 +82995,7 @@
         </is>
       </c>
       <c r="G1564" s="8" t="n">
-        <v>-0.4701048951048951</v>
+        <v>-0.4151223776223776</v>
       </c>
     </row>
     <row r="1565">
@@ -83193,7 +83193,7 @@
         </is>
       </c>
       <c r="G1570" s="8" t="n">
-        <v>-0.4670891608391609</v>
+        <v>-0.4229458041958042</v>
       </c>
     </row>
     <row r="1571">
@@ -83358,7 +83358,7 @@
         </is>
       </c>
       <c r="G1575" s="8" t="n">
-        <v>-0.4976398601398601</v>
+        <v>-0.4392482517482518</v>
       </c>
     </row>
     <row r="1576">
@@ -83490,7 +83490,7 @@
         </is>
       </c>
       <c r="G1579" s="8" t="n">
-        <v>-0.6325611888111888</v>
+        <v>-0.58125</v>
       </c>
     </row>
     <row r="1580">
@@ -83589,7 +83589,7 @@
         </is>
       </c>
       <c r="G1582" s="8" t="n">
-        <v>-0.3456293706293706</v>
+        <v>-0.2878496503496504</v>
       </c>
     </row>
     <row r="1583">
@@ -83655,7 +83655,7 @@
         </is>
       </c>
       <c r="G1584" s="8" t="n">
-        <v>-0.5202150448607383</v>
+        <v>-0.4546090305491968</v>
       </c>
     </row>
     <row r="1585">
@@ -83688,7 +83688,7 @@
         </is>
       </c>
       <c r="G1585" s="8" t="n">
-        <v>-0.3803686353276501</v>
+        <v>-0.3525934603544421</v>
       </c>
     </row>
   </sheetData>
